--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45386</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>44876</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>44594</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44473</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>44572</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>44701</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44887</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>44601</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>44789</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44677</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>44461</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>44608</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>44622</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>44811</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>44686</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>44466</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>44524</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44522</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>44565</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>44572</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33546-2022</t>
+          <t>A 24127-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44789</v>
+        <v>45456</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2958,7 +2958,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11123-2024</t>
+          <t>A 23984-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45371</v>
+        <v>45456</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>8.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10768-2024</t>
+          <t>A 62294-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45369</v>
+        <v>44923</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3104,7 +3104,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10777-2024</t>
+          <t>A 12264-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45369</v>
+        <v>45378</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 37658-2022</t>
+          <t>A 12266-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44810</v>
+        <v>45378</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 64784-2023</t>
+          <t>A 6354-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45282</v>
+        <v>45699</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>19.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36982-2024</t>
+          <t>A 3886-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45539</v>
+        <v>45684</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3352,8 +3352,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3396,7 +3401,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60103-2022</t>
+          <t>A 39611-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3410,10 +3415,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44909</v>
+        <v>44818</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3425,8 +3430,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3469,7 +3479,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 66960-2021</t>
+          <t>A 65254-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3483,10 +3493,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44522</v>
+        <v>44515</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3499,7 +3509,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>6.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3542,7 +3552,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3074-2023</t>
+          <t>A 18612-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3556,10 +3566,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44946</v>
+        <v>45763</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3572,7 +3582,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.1</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3615,7 +3625,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11991-2022</t>
+          <t>A 34909-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3629,10 +3639,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44635</v>
+        <v>45141</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3645,7 +3655,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3688,7 +3698,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13119-2023</t>
+          <t>A 15704-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3702,10 +3712,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45002</v>
+        <v>45021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3718,7 +3728,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3761,7 +3771,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3044-2022</t>
+          <t>A 65116-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3771,14 +3781,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44582</v>
+        <v>45287</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3791,7 +3801,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3834,7 +3844,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 17126-2022</t>
+          <t>A 15181-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3848,10 +3858,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44677</v>
+        <v>45016</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3864,7 +3874,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3907,7 +3917,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 56116-2022</t>
+          <t>A 24129-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3921,10 +3931,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44889</v>
+        <v>45456</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3937,7 +3947,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3980,7 +3990,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46533-2024</t>
+          <t>A 37801-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3990,14 +4000,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45582</v>
+        <v>45543</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4010,7 +4020,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4053,7 +4063,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 53131-2022</t>
+          <t>A 11837-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4067,10 +4077,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44876</v>
+        <v>45728</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4126,7 +4136,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30486-2025</t>
+          <t>A 15645-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4140,10 +4150,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45829</v>
+        <v>45404</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4156,7 +4166,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4199,7 +4209,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7783-2023</t>
+          <t>A 24559-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4213,10 +4223,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44973</v>
+        <v>45798</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4229,7 +4239,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4272,7 +4282,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 31464-2025</t>
+          <t>A 29300-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4286,10 +4296,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45833</v>
+        <v>45483</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4302,7 +4312,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4345,7 +4355,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11460-2024</t>
+          <t>A 49062-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4359,10 +4369,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45372</v>
+        <v>45594</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4375,7 +4385,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4418,7 +4428,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15648-2025</t>
+          <t>A 45519-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4432,10 +4442,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45748</v>
+        <v>45194</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4448,7 +4458,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4491,7 +4501,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 21979-2025</t>
+          <t>A 15648-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4505,10 +4515,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45784</v>
+        <v>45748</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4521,7 +4531,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4564,7 +4574,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 62299-2022</t>
+          <t>A 63884-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4578,10 +4588,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44923</v>
+        <v>46020</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4594,7 +4604,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4637,7 +4647,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 49781-2024</t>
+          <t>A 60-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4651,10 +4661,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45597</v>
+        <v>46024</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4667,7 +4677,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4710,7 +4720,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 34909-2023</t>
+          <t>A 16487-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4724,10 +4734,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45141</v>
+        <v>45029</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4740,7 +4750,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4783,7 +4793,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55033-2023</t>
+          <t>A 27201-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4797,10 +4807,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45237</v>
+        <v>45812</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4813,7 +4823,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4856,7 +4866,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6354-2025</t>
+          <t>A 21979-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4870,10 +4880,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45699</v>
+        <v>45784</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4886,7 +4896,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>19.3</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4929,7 +4939,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 34671-2025</t>
+          <t>A 11123-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4943,10 +4953,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45847</v>
+        <v>45371</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4958,13 +4968,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5007,7 +5012,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 21363-2023</t>
+          <t>A 34435-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5021,10 +5026,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45063</v>
+        <v>45525</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5037,7 +5042,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5080,7 +5085,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 13510-2022</t>
+          <t>A 1525-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5094,10 +5099,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44648</v>
+        <v>46034</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5110,7 +5115,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>17.6</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5153,7 +5158,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 10640-2025</t>
+          <t>A 55033-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5167,10 +5172,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45721</v>
+        <v>45237</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5183,7 +5188,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5226,7 +5231,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 40896-2022</t>
+          <t>A 53401-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5240,10 +5245,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44825</v>
+        <v>44879</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5256,7 +5261,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>11.3</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5299,7 +5304,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15658-2025</t>
+          <t>A 46533-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5313,10 +5318,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45748</v>
+        <v>45582</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5329,7 +5334,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5372,7 +5377,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 36192-2025</t>
+          <t>A 3256-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5386,10 +5391,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45867</v>
+        <v>46041</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5402,7 +5407,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>8.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5445,7 +5450,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15000-2023</t>
+          <t>A 37562-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5459,10 +5464,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45015</v>
+        <v>45541</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5475,7 +5480,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5518,7 +5523,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 65254-2021</t>
+          <t>A 27652-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5532,10 +5537,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44515</v>
+        <v>44743</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5548,7 +5553,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.4</v>
+        <v>9.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5591,7 +5596,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 46364-2024</t>
+          <t>A 30486-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5605,10 +5610,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45582</v>
+        <v>45829</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5621,7 +5626,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5664,7 +5669,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6251-2023</t>
+          <t>A 31464-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5678,10 +5683,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44965</v>
+        <v>45833</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5694,7 +5699,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>15.4</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5737,7 +5742,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24127-2024</t>
+          <t>A 7628-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5751,10 +5756,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45456</v>
+        <v>44607</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5767,7 +5772,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5810,7 +5815,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23451-2023</t>
+          <t>A 59879-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5824,10 +5829,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45076</v>
+        <v>45640</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5839,13 +5844,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5888,7 +5888,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 3886-2025</t>
+          <t>A 11991-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45684</v>
+        <v>44635</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5915,11 +5915,6 @@
       <c r="G71" t="inlineStr">
         <is>
           <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -5966,7 +5961,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 47708-2025</t>
+          <t>A 4906-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5980,10 +5975,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45931</v>
+        <v>45329</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5996,7 +5991,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6039,7 +6034,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 48790-2025</t>
+          <t>A 7655-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6053,10 +6048,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45937</v>
+        <v>46062</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6069,7 +6064,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6112,7 +6107,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 48791-2025</t>
+          <t>A 34671-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6126,10 +6121,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45937</v>
+        <v>45847</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6141,8 +6136,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6185,7 +6185,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 41554-2024</t>
+          <t>A 7659-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45560</v>
+        <v>46062</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6258,7 +6258,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 48787-2025</t>
+          <t>A 47902-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6272,10 +6272,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45937</v>
+        <v>45589</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6331,7 +6331,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48788-2025</t>
+          <t>A 58330-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45937</v>
+        <v>44901</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6404,7 +6404,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61046-2024</t>
+          <t>A 10640-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6418,10 +6418,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45645</v>
+        <v>45721</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6477,7 +6477,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 32527-2024</t>
+          <t>A 13510-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45513</v>
+        <v>44648</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6506,13 +6506,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>8.699999999999999</v>
+        <v>17.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6555,7 +6550,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 50337-2025</t>
+          <t>A 13119-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6569,10 +6564,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45944</v>
+        <v>45002</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6585,7 +6580,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6628,7 +6623,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 50209-2025</t>
+          <t>A 68454-2021</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6642,10 +6637,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45943</v>
+        <v>44529</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6658,7 +6653,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6701,7 +6696,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 32541-2024</t>
+          <t>A 48788-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6715,10 +6710,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45513</v>
+        <v>45937</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6730,13 +6725,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6779,7 +6769,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 14211-2026</t>
+          <t>A 36192-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6793,10 +6783,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46099</v>
+        <v>45867</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6809,7 +6799,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6852,7 +6842,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15592-2026</t>
+          <t>A 48790-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6866,10 +6856,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46106</v>
+        <v>45937</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6882,7 +6872,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>8.4</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6925,7 +6915,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 53193-2023</t>
+          <t>A 47708-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6939,10 +6929,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45229</v>
+        <v>45931</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6955,7 +6945,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6998,7 +6988,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 16030-2026</t>
+          <t>A 48787-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7012,10 +7002,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46108</v>
+        <v>45937</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7028,7 +7018,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>15.8</v>
+        <v>3.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7071,7 +7061,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 39611-2022</t>
+          <t>A 48791-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7085,10 +7075,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44818</v>
+        <v>45937</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7100,13 +7090,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7149,7 +7134,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 54526-2025</t>
+          <t>A 57259-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7163,10 +7148,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45965</v>
+        <v>44895</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7179,7 +7164,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7222,7 +7207,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 29300-2024</t>
+          <t>A 50209-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7236,10 +7221,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45483</v>
+        <v>45943</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7252,7 +7237,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7295,7 +7280,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 7628-2022</t>
+          <t>A 50337-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7309,10 +7294,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44607</v>
+        <v>45944</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7325,7 +7310,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7368,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 56523-2025</t>
+          <t>A 10777-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7382,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45975</v>
+        <v>45369</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7398,7 +7383,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7441,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 53426-2022</t>
+          <t>A 32527-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7455,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44879</v>
+        <v>45513</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7470,8 +7455,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>13.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7514,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 62266-2022</t>
+          <t>A 32541-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7528,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44923</v>
+        <v>45513</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7543,8 +7533,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7587,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 17485-2026</t>
+          <t>A 2263-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7597,14 +7592,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46120</v>
+        <v>45310</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7616,8 +7611,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 39116-2022</t>
+          <t>A 14211-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44817</v>
+        <v>46099</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7733,7 +7733,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 57262-2025</t>
+          <t>A 15592-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45979</v>
+        <v>46106</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.9</v>
+        <v>8.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7806,7 +7806,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 57890-2025</t>
+          <t>A 16030-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7820,10 +7820,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45981</v>
+        <v>46108</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>15.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7879,7 +7879,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 57918-2022</t>
+          <t>A 54526-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44900</v>
+        <v>45965</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7952,7 +7952,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 57886-2025</t>
+          <t>A 17485-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7962,14 +7962,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45981</v>
+        <v>46120</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 57891-2025</t>
+          <t>A 53227-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45981</v>
+        <v>44468</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8098,7 +8098,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 41893-2022</t>
+          <t>A 18840-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44830</v>
+        <v>46129</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8127,13 +8127,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8176,7 +8171,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 59252-2025</t>
+          <t>A 8273-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8190,10 +8185,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45988</v>
+        <v>45352</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8206,7 +8201,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8249,7 +8244,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 18840-2026</t>
+          <t>A 52688-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8263,10 +8258,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46129</v>
+        <v>45610</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8279,7 +8274,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8322,7 +8317,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 53227-2021</t>
+          <t>A 19373-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8336,10 +8331,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44468</v>
+        <v>46133</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8352,7 +8347,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8395,7 +8390,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 18612-2025</t>
+          <t>A 56523-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8409,10 +8404,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45763</v>
+        <v>45975</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8425,7 +8420,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8468,7 +8463,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 19373-2026</t>
+          <t>A 57262-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8482,10 +8477,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46133</v>
+        <v>45979</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8498,7 +8493,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8541,7 +8536,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 7730-2023</t>
+          <t>A 20009-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8555,10 +8550,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44973</v>
+        <v>46136</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8571,7 +8566,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8614,7 +8609,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60505-2025</t>
+          <t>A 57890-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8628,10 +8623,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45995</v>
+        <v>45981</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8644,7 +8639,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8687,7 +8682,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61535-2025</t>
+          <t>A 57886-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8701,10 +8696,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46001</v>
+        <v>45981</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8717,7 +8712,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8760,7 +8755,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61539-2025</t>
+          <t>A 57891-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8774,10 +8769,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46001</v>
+        <v>45981</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8790,7 +8785,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8833,7 +8828,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 20009-2026</t>
+          <t>A 46529-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8847,10 +8842,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46136</v>
+        <v>45582</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8863,7 +8858,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>11.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8906,7 +8901,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 4307-2025</t>
+          <t>A 131-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8920,10 +8915,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45685</v>
+        <v>45294</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8936,7 +8931,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>7.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8979,7 +8974,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 63884-2025</t>
+          <t>A 75-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8993,10 +8988,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46020</v>
+        <v>45659</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9009,7 +9004,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9052,7 +9047,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 68454-2021</t>
+          <t>A 59252-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9066,10 +9061,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44529</v>
+        <v>45988</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9082,7 +9077,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9125,7 +9120,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 60-2026</t>
+          <t>A 68400-2021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9139,10 +9134,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46024</v>
+        <v>44529</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9155,7 +9150,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9198,7 +9193,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 1525-2026</t>
+          <t>A 3272-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9212,10 +9207,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46034</v>
+        <v>45679</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9228,7 +9223,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9271,7 +9266,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 7781-2023</t>
+          <t>A 54087-2021</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9285,10 +9280,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44973</v>
+        <v>44470</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9300,8 +9295,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9344,7 +9344,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 73158-2021</t>
+          <t>A 60505-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44550</v>
+        <v>45995</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 3272-2025</t>
+          <t>A 35465-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9431,10 +9431,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45679</v>
+        <v>44798</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9490,7 +9490,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 30773-2024</t>
+          <t>A 61535-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9504,10 +9504,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45496</v>
+        <v>46001</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9563,7 +9563,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 3256-2026</t>
+          <t>A 61539-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46041</v>
+        <v>46001</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>8.1</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9636,7 +9636,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 38941-2023</t>
+          <t>A 39116-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9650,10 +9650,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45163</v>
+        <v>44817</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9709,7 +9709,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 16473-2023</t>
+          <t>A 20152-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9723,10 +9723,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45029</v>
+        <v>46138</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9782,7 +9782,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 16475-2023</t>
+          <t>A 62266-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9796,10 +9796,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45029</v>
+        <v>44923</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9855,7 +9855,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 34435-2024</t>
+          <t>A 30773-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9869,10 +9869,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45525</v>
+        <v>45496</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9928,7 +9928,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 20500-2026</t>
+          <t>A 28224-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9942,10 +9942,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46140</v>
+        <v>45099</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10001,7 +10001,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 42456-2024</t>
+          <t>A 4307-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10015,10 +10015,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45565</v>
+        <v>45685</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10074,7 +10074,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 20501-2026</t>
+          <t>A 10767-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10088,10 +10088,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46140</v>
+        <v>45369</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10147,7 +10147,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 20152-2026</t>
+          <t>A 20500-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10161,10 +10161,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46138</v>
+        <v>46140</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10220,7 +10220,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 19781-2025</t>
+          <t>A 60103-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10234,10 +10234,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45771</v>
+        <v>44909</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6.1</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10293,7 +10293,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 7655-2026</t>
+          <t>A 20667-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10307,10 +10307,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46062</v>
+        <v>46141</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10366,7 +10366,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 12967-2024</t>
+          <t>A 20501-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45385</v>
+        <v>46140</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10439,7 +10439,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 7659-2026</t>
+          <t>A 13515-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10453,10 +10453,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46062</v>
+        <v>44648</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10512,7 +10512,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 37371-2023</t>
+          <t>A 4077-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10526,10 +10526,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45156</v>
+        <v>45684</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10585,7 +10585,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 28224-2023</t>
+          <t>A 2402-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10599,10 +10599,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45099</v>
+        <v>45310</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4.8</v>
+        <v>0.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10658,7 +10658,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 35969-2024</t>
+          <t>A 22207-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10672,10 +10672,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45533</v>
+        <v>46153</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10731,7 +10731,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 20667-2026</t>
+          <t>A 21929-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10745,10 +10745,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10804,7 +10804,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 7921-2024</t>
+          <t>A 73158-2021</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45350</v>
+        <v>44550</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10877,7 +10877,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 21929-2026</t>
+          <t>A 13883-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10891,10 +10891,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46150</v>
+        <v>44650</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10950,7 +10950,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 22207-2026</t>
+          <t>A 22620-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10964,10 +10964,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11023,7 +11023,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 13515-2022</t>
+          <t>A 10858-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11037,10 +11037,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44648</v>
+        <v>46078</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.3</v>
+        <v>8.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11096,7 +11096,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 22620-2026</t>
+          <t>A 59625-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46155</v>
+        <v>45254</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 75-2025</t>
+          <t>A 27441-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11183,10 +11183,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45659</v>
+        <v>46189</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11242,7 +11242,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 3795-2024</t>
+          <t>A 27586-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11252,14 +11252,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45321</v>
+        <v>46190</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11315,7 +11315,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 61884-2024</t>
+          <t>A 32804-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11329,10 +11329,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45652</v>
+        <v>46241</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11344,8 +11344,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11388,7 +11393,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 45521-2022</t>
+          <t>A 15659-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11402,10 +11407,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44845</v>
+        <v>45748</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11418,7 +11423,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11461,7 +11466,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 5927-2022</t>
+          <t>A 32797-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11475,10 +11480,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44598</v>
+        <v>46241</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11490,8 +11495,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11534,7 +11544,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 10858-2026</t>
+          <t>A 16154-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11548,10 +11558,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46078</v>
+        <v>45406</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11564,7 +11574,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>8.5</v>
+        <v>0.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11607,7 +11617,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 23984-2024</t>
+          <t>A 16155-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11621,10 +11631,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45456</v>
+        <v>45406</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11637,7 +11647,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11680,7 +11690,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24129-2024</t>
+          <t>A 33830-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11694,10 +11704,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45456</v>
+        <v>46251</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11710,7 +11720,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>8.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11753,7 +11763,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 35465-2022</t>
+          <t>A 33782-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11767,10 +11777,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44798</v>
+        <v>46251</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11783,7 +11793,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11826,7 +11836,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 65116-2023</t>
+          <t>A 30505-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11836,14 +11846,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45287</v>
+        <v>46210</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11856,7 +11866,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.1</v>
+        <v>3.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11899,7 +11909,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 59625-2023</t>
+          <t>A 35969-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11913,10 +11923,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45254</v>
+        <v>45533</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11929,7 +11939,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11972,7 +11982,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 19447-2025</t>
+          <t>A 41554-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11986,10 +11996,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45770</v>
+        <v>45560</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12002,7 +12012,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12045,7 +12055,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 131-2024</t>
+          <t>A 45983-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12059,10 +12069,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45294</v>
+        <v>45580</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12075,7 +12085,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12118,7 +12128,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 54087-2021</t>
+          <t>A 32826-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12132,10 +12142,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44470</v>
+        <v>44784</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12147,13 +12157,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12196,7 +12201,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 27441-2026</t>
+          <t>A 53426-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12210,10 +12215,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46189</v>
+        <v>44879</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12226,7 +12231,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.2</v>
+        <v>13.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12269,7 +12274,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 27586-2026</t>
+          <t>A 13220-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12279,14 +12284,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46190</v>
+        <v>44644</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12299,7 +12304,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12342,7 +12347,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 27652-2022</t>
+          <t>A 19447-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12356,10 +12361,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44743</v>
+        <v>45770</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12372,7 +12377,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>9.1</v>
+        <v>4.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12415,7 +12420,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 45983-2024</t>
+          <t>A 36033-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12429,10 +12434,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45580</v>
+        <v>46267</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12445,7 +12450,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12488,7 +12493,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 5242-2022</t>
+          <t>A 64669-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12502,10 +12507,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44594</v>
+        <v>45281</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12518,7 +12523,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12561,7 +12566,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 46529-2024</t>
+          <t>A 16473-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12575,10 +12580,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45582</v>
+        <v>45029</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12591,7 +12596,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>11.7</v>
+        <v>5.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12634,7 +12639,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 16154-2024</t>
+          <t>A 16475-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12648,10 +12653,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45406</v>
+        <v>45029</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12664,7 +12669,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12707,7 +12712,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 16155-2024</t>
+          <t>A 53131-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12721,10 +12726,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45406</v>
+        <v>44876</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12737,7 +12742,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12780,7 +12785,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 57259-2022</t>
+          <t>A 64784-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12794,10 +12799,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44895</v>
+        <v>45282</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12810,7 +12815,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12853,7 +12858,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 59879-2024</t>
+          <t>A 3044-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12867,10 +12872,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45640</v>
+        <v>44582</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12883,7 +12888,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12926,7 +12931,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 32826-2022</t>
+          <t>A 15000-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12940,10 +12945,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44784</v>
+        <v>45015</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12956,7 +12961,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -12999,7 +13004,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 58330-2022</t>
+          <t>A 49-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13013,10 +13018,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44901</v>
+        <v>46024</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13029,7 +13034,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13072,7 +13077,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 15704-2023</t>
+          <t>A 6251-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13086,10 +13091,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45021</v>
+        <v>44965</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13102,7 +13107,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>5</v>
+        <v>15.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13145,7 +13150,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 30796-2024</t>
+          <t>A 19781-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13159,10 +13164,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45497</v>
+        <v>45771</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13175,7 +13180,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.7</v>
+        <v>6.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13218,7 +13223,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 16152-2024</t>
+          <t>A 23451-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13232,10 +13237,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45406</v>
+        <v>45076</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13247,8 +13252,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13291,7 +13301,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 4906-2024</t>
+          <t>A 60498-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13305,10 +13315,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45329</v>
+        <v>45643</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13321,7 +13331,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13364,7 +13374,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 32804-2026</t>
+          <t>A 5927-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13378,10 +13388,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46241</v>
+        <v>44598</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13393,13 +13403,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13442,7 +13447,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 13883-2022</t>
+          <t>A 41893-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13456,10 +13461,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44650</v>
+        <v>44830</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13471,8 +13476,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>6.1</v>
+        <v>2.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13515,7 +13525,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 53401-2022</t>
+          <t>A 7783-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13529,10 +13539,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44879</v>
+        <v>44973</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13545,7 +13555,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13588,7 +13598,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 15181-2023</t>
+          <t>A 5242-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13602,10 +13612,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45016</v>
+        <v>44594</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13618,7 +13628,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13661,7 +13671,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 32797-2026</t>
+          <t>A 57918-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13675,10 +13685,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46241</v>
+        <v>44900</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13690,13 +13700,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13739,7 +13744,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 855-2023</t>
+          <t>A 7781-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13753,10 +13758,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44931</v>
+        <v>44973</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13769,7 +13774,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13812,7 +13817,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 47755-2022</t>
+          <t>A 7921-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13826,10 +13831,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44854</v>
+        <v>45350</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13842,7 +13847,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13885,7 +13890,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 9821-2022</t>
+          <t>A 45521-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13899,10 +13904,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44620</v>
+        <v>44845</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13915,7 +13920,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13958,7 +13963,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 13220-2022</t>
+          <t>A 17126-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13972,10 +13977,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44644</v>
+        <v>44677</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13988,7 +13993,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14031,7 +14036,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 68400-2021</t>
+          <t>A 56116-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14045,10 +14050,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44529</v>
+        <v>44889</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14061,7 +14066,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14104,7 +14109,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 25514-2022</t>
+          <t>A 40896-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14118,10 +14123,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44732</v>
+        <v>44825</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14134,7 +14139,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>11.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14177,7 +14182,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 10494-2022</t>
+          <t>A 12329-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14191,10 +14196,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44623</v>
+        <v>45378</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14207,7 +14212,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>13.3</v>
+        <v>0.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14250,7 +14255,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 33782-2026</t>
+          <t>A 37371-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14264,10 +14269,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46251</v>
+        <v>45156</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14280,7 +14285,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14323,7 +14328,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 33830-2026</t>
+          <t>A 3074-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14337,10 +14342,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46251</v>
+        <v>44946</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14353,7 +14358,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>8.9</v>
+        <v>6.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14396,7 +14401,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 52688-2024</t>
+          <t>A 7730-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14410,10 +14415,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45610</v>
+        <v>44973</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14426,7 +14431,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14469,7 +14474,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 30505-2026</t>
+          <t>A 10494-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14483,10 +14488,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46210</v>
+        <v>44623</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14499,7 +14504,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.8</v>
+        <v>13.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14542,7 +14547,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 47902-2024</t>
+          <t>A 46364-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14556,10 +14561,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45589</v>
+        <v>45582</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14572,7 +14577,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14615,7 +14620,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 2263-2024</t>
+          <t>A 33546-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14629,10 +14634,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45310</v>
+        <v>44789</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14644,13 +14649,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14693,7 +14693,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 37305-2022</t>
+          <t>A 9821-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14707,10 +14707,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44808</v>
+        <v>44620</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>9.9</v>
+        <v>2.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14766,7 +14766,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 60498-2024</t>
+          <t>A 38941-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14780,10 +14780,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45643</v>
+        <v>45163</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14839,7 +14839,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 37562-2024</t>
+          <t>A 49781-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14853,10 +14853,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45541</v>
+        <v>45597</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14912,7 +14912,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 15659-2025</t>
+          <t>A 61046-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14926,10 +14926,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45748</v>
+        <v>45645</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14985,7 +14985,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 19773-2025</t>
+          <t>A 3795-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14999,10 +14999,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45771</v>
+        <v>45321</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15058,7 +15058,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 36033-2026</t>
+          <t>A 42456-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15072,10 +15072,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46267</v>
+        <v>45565</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15131,7 +15131,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 8273-2024</t>
+          <t>A 30796-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15145,10 +15145,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45352</v>
+        <v>45497</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15204,7 +15204,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 2402-2024</t>
+          <t>A 16152-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15218,10 +15218,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45310</v>
+        <v>45406</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15277,7 +15277,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 3399-2024</t>
+          <t>A 47755-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15291,10 +15291,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45318</v>
+        <v>44854</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15350,7 +15350,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 10767-2024</t>
+          <t>A 10768-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15367,7 +15367,7 @@
         <v>45369</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15423,7 +15423,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 24432-2022</t>
+          <t>A 62299-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15433,14 +15433,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44726</v>
+        <v>44923</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15496,7 +15496,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 16487-2023</t>
+          <t>A 11460-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15510,10 +15510,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45029</v>
+        <v>45372</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15569,7 +15569,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 64669-2023</t>
+          <t>A 55303-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15583,10 +15583,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45281</v>
+        <v>44887</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15642,7 +15642,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 55303-2022</t>
+          <t>A 36982-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15656,10 +15656,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44887</v>
+        <v>45539</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15715,7 +15715,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 12329-2024</t>
+          <t>A 855-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15729,10 +15729,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45378</v>
+        <v>44931</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 49-2026</t>
+          <t>A 21363-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15802,10 +15802,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46024</v>
+        <v>45063</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15861,7 +15861,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 4077-2025</t>
+          <t>A 61884-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15875,10 +15875,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45684</v>
+        <v>45652</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15934,7 +15934,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 62294-2022</t>
+          <t>A 19773-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15948,10 +15948,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44923</v>
+        <v>45771</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16007,7 +16007,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 12264-2024</t>
+          <t>A 3399-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16021,10 +16021,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45378</v>
+        <v>45318</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16080,7 +16080,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 12266-2024</t>
+          <t>A 44708-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16094,10 +16094,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45378</v>
+        <v>45190</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16153,7 +16153,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 44708-2023</t>
+          <t>A 25514-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16167,10 +16167,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45190</v>
+        <v>44732</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16226,7 +16226,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 20955-2025</t>
+          <t>A 12967-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16240,10 +16240,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45777</v>
+        <v>45385</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 22016-2025</t>
+          <t>A 24432-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16309,14 +16309,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45784</v>
+        <v>44726</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16372,7 +16372,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 37801-2024</t>
+          <t>A 37658-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16382,14 +16382,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45543</v>
+        <v>44810</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16445,7 +16445,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 24559-2025</t>
+          <t>A 15658-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16459,10 +16459,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45798</v>
+        <v>45748</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16518,7 +16518,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 11837-2025</t>
+          <t>A 66960-2021</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16532,10 +16532,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45728</v>
+        <v>44522</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16591,7 +16591,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 15645-2024</t>
+          <t>A 37305-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16605,10 +16605,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45404</v>
+        <v>44808</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.2</v>
+        <v>9.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16664,7 +16664,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 45519-2023</t>
+          <t>A 53193-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16678,10 +16678,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45194</v>
+        <v>45229</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16737,7 +16737,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 49062-2024</t>
+          <t>A 20955-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16751,10 +16751,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45594</v>
+        <v>45777</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16810,7 +16810,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 27201-2025</t>
+          <t>A 22016-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -16824,10 +16824,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45812</v>
+        <v>45784</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>46090</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>

--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE221"/>
+  <dimension ref="A1:AE222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45386</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 53134-2022</t>
+          <t>A 38026-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44876</v>
+        <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1402,20 +1402,52 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/artfynd/A 38026-2026 artfynd.xlsx", "A 38026-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor/A 38026-2026 karta.png", "A 38026-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor_geotiff/A 38026-2026 georefererad karta.tif", "A 38026-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomål/A 38026-2026 FSC-klagomål.docx", "A 38026-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomålsmail/A 38026-2026 FSC-klagomål mail.docx", "A 38026-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsyn/A 38026-2026 tillsynsbegäran.docx", "A 38026-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsynsmail/A 38026-2026 tillsynsbegäran mail.docx", "A 38026-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5234-2022</t>
+          <t>A 53134-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1429,10 +1461,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44594</v>
+        <v>44876</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1445,7 +1477,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1488,7 +1520,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 54668-2021</t>
+          <t>A 5234-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1502,10 +1534,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44473</v>
+        <v>44594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1517,13 +1549,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1566,7 +1593,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1296-2022</t>
+          <t>A 54668-2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1580,10 +1607,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44572</v>
+        <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1595,8 +1622,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1639,7 +1671,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 20737-2022</t>
+          <t>A 1296-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1653,10 +1685,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44701</v>
+        <v>44572</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1669,7 +1701,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1712,7 +1744,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55480-2022</t>
+          <t>A 20737-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1726,10 +1758,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44887</v>
+        <v>44701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1742,7 +1774,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1785,7 +1817,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6591-2022</t>
+          <t>A 55480-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1799,10 +1831,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44601</v>
+        <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1815,7 +1847,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>9.800000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1858,7 +1890,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33547-2022</t>
+          <t>A 6591-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1872,10 +1904,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44789</v>
+        <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1888,7 +1920,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1931,7 +1963,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 17194-2022</t>
+          <t>A 33547-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1945,10 +1977,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44677</v>
+        <v>44789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1961,7 +1993,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2004,7 +2036,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 51172-2021</t>
+          <t>A 17194-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2018,10 +2050,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44461</v>
+        <v>44677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2034,7 +2066,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.7</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2077,7 +2109,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 7747-2022</t>
+          <t>A 51172-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2091,10 +2123,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44608</v>
+        <v>44461</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2107,7 +2139,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2150,7 +2182,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 10150-2022</t>
+          <t>A 7747-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2164,10 +2196,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44622</v>
+        <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2180,7 +2212,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2223,7 +2255,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38000-2022</t>
+          <t>A 10150-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2237,10 +2269,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44811</v>
+        <v>44622</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2253,7 +2285,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2296,7 +2328,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 18533-2022</t>
+          <t>A 38000-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2310,10 +2342,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44686</v>
+        <v>44811</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2326,7 +2358,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2369,7 +2401,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30157-2022</t>
+          <t>A 18533-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2383,10 +2415,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44757</v>
+        <v>44686</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2399,7 +2431,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2442,7 +2474,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 19577-2022</t>
+          <t>A 30157-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2456,10 +2488,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44693</v>
+        <v>44757</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2472,7 +2504,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2515,7 +2547,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52687-2021</t>
+          <t>A 67535-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2529,10 +2561,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44466</v>
+        <v>44524</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2544,8 +2576,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2588,7 +2625,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 67535-2021</t>
+          <t>A 66971-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2602,10 +2639,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44524</v>
+        <v>44522</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2617,13 +2654,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2666,7 +2698,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 66971-2021</t>
+          <t>A 33546-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2680,10 +2712,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44522</v>
+        <v>44789</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2739,7 +2771,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 318-2022</t>
+          <t>A 19577-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2753,10 +2785,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44565</v>
+        <v>44693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2769,7 +2801,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8.6</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2812,7 +2844,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1295-2022</t>
+          <t>A 318-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2826,10 +2858,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44572</v>
+        <v>44565</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2842,7 +2874,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>8.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2885,7 +2917,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24127-2024</t>
+          <t>A 11123-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2899,10 +2931,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45456</v>
+        <v>45371</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2915,7 +2947,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2958,7 +2990,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23984-2024</t>
+          <t>A 10768-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2972,10 +3004,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45456</v>
+        <v>45369</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2988,7 +3020,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3031,7 +3063,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62294-2022</t>
+          <t>A 10777-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3045,10 +3077,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44923</v>
+        <v>45369</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3061,7 +3093,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3104,7 +3136,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12264-2024</t>
+          <t>A 37658-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3118,10 +3150,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45378</v>
+        <v>44810</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3134,7 +3166,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3177,7 +3209,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12266-2024</t>
+          <t>A 1295-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3191,10 +3223,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45378</v>
+        <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3207,7 +3239,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3250,7 +3282,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 6354-2025</t>
+          <t>A 52687-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3264,10 +3296,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45699</v>
+        <v>44466</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3280,7 +3312,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>19.3</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3323,7 +3355,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3886-2025</t>
+          <t>A 35465-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3337,10 +3369,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45684</v>
+        <v>44798</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3352,13 +3384,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3401,7 +3428,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 39611-2022</t>
+          <t>A 65116-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3411,14 +3438,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44818</v>
+        <v>45287</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3430,13 +3457,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3479,7 +3501,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 65254-2021</t>
+          <t>A 59625-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3493,10 +3515,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44515</v>
+        <v>45254</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3509,7 +3531,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3552,7 +3574,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18612-2025</t>
+          <t>A 19447-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3566,10 +3588,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45763</v>
+        <v>45770</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3582,7 +3604,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3625,7 +3647,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34909-2023</t>
+          <t>A 131-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3639,10 +3661,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45141</v>
+        <v>45294</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3655,7 +3677,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3698,7 +3720,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15704-2023</t>
+          <t>A 54087-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3712,10 +3734,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45021</v>
+        <v>44470</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3727,8 +3749,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3771,7 +3798,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 65116-2023</t>
+          <t>A 60103-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3781,14 +3808,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45287</v>
+        <v>44909</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3801,7 +3828,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3844,7 +3871,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15181-2023</t>
+          <t>A 3044-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3858,10 +3885,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45016</v>
+        <v>44582</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3874,7 +3901,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3917,7 +3944,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 24129-2024</t>
+          <t>A 56116-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3931,10 +3958,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45456</v>
+        <v>44889</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3947,7 +3974,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3990,7 +4017,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37801-2024</t>
+          <t>A 64784-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4000,14 +4027,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45543</v>
+        <v>45282</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4020,7 +4047,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4063,7 +4090,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11837-2025</t>
+          <t>A 15648-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4077,10 +4104,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45728</v>
+        <v>45748</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4093,7 +4120,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4136,7 +4163,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15645-2024</t>
+          <t>A 36982-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4150,10 +4177,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45404</v>
+        <v>45539</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4166,7 +4193,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4209,7 +4236,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24559-2025</t>
+          <t>A 32527-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4223,10 +4250,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45798</v>
+        <v>45513</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4238,8 +4265,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>6.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4282,7 +4314,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 29300-2024</t>
+          <t>A 32541-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4296,10 +4328,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45483</v>
+        <v>45513</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4311,8 +4343,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4355,7 +4392,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 49062-2024</t>
+          <t>A 21979-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4369,10 +4406,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45594</v>
+        <v>45784</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4385,7 +4422,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4428,7 +4465,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45519-2023</t>
+          <t>A 27652-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4442,10 +4479,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45194</v>
+        <v>44743</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4458,7 +4495,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.5</v>
+        <v>9.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4501,7 +4538,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15648-2025</t>
+          <t>A 66960-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4515,10 +4552,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45748</v>
+        <v>44522</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4531,7 +4568,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4574,7 +4611,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 63884-2025</t>
+          <t>A 14211-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4588,10 +4625,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46020</v>
+        <v>46099</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4604,7 +4641,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4647,7 +4684,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60-2026</t>
+          <t>A 45983-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4661,10 +4698,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46024</v>
+        <v>45580</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4677,7 +4714,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4720,7 +4757,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16487-2023</t>
+          <t>A 5242-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4734,10 +4771,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45029</v>
+        <v>44594</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4750,7 +4787,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4793,7 +4830,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 27201-2025</t>
+          <t>A 11991-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4807,10 +4844,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45812</v>
+        <v>44635</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4823,7 +4860,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4866,7 +4903,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 21979-2025</t>
+          <t>A 15592-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4880,10 +4917,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45784</v>
+        <v>46106</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4896,7 +4933,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4939,7 +4976,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11123-2024</t>
+          <t>A 3074-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4953,10 +4990,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45371</v>
+        <v>44946</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4969,7 +5006,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.199999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5012,7 +5049,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34435-2024</t>
+          <t>A 13119-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5026,10 +5063,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45525</v>
+        <v>45002</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5042,7 +5079,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5085,7 +5122,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 1525-2026</t>
+          <t>A 16030-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5099,10 +5136,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46034</v>
+        <v>46108</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5115,7 +5152,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>15.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5158,7 +5195,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55033-2023</t>
+          <t>A 46529-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5172,10 +5209,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45237</v>
+        <v>45582</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5188,7 +5225,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>11.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5231,7 +5268,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 53401-2022</t>
+          <t>A 16154-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5245,10 +5282,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44879</v>
+        <v>45406</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5261,7 +5298,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5304,7 +5341,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 46533-2024</t>
+          <t>A 16155-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5318,10 +5355,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45582</v>
+        <v>45406</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5334,7 +5371,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5377,7 +5414,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3256-2026</t>
+          <t>A 57259-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5391,10 +5428,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46041</v>
+        <v>44895</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5407,7 +5444,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>8.1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5450,7 +5487,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37562-2024</t>
+          <t>A 17126-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5464,10 +5501,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45541</v>
+        <v>44677</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5480,7 +5517,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5523,7 +5560,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 27652-2022</t>
+          <t>A 17485-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5533,14 +5570,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44743</v>
+        <v>46120</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5553,7 +5590,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>9.1</v>
+        <v>3.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5596,7 +5633,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30486-2025</t>
+          <t>A 59879-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5610,10 +5647,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45829</v>
+        <v>45640</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5626,7 +5663,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5669,7 +5706,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 31464-2025</t>
+          <t>A 32826-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5683,10 +5720,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45833</v>
+        <v>44784</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5699,7 +5736,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5742,7 +5779,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7628-2022</t>
+          <t>A 58330-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5756,10 +5793,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44607</v>
+        <v>44901</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5815,7 +5852,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 59879-2024</t>
+          <t>A 46533-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5829,10 +5866,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45640</v>
+        <v>45582</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5845,7 +5882,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5888,7 +5925,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11991-2022</t>
+          <t>A 15704-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5902,10 +5939,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44635</v>
+        <v>45021</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5918,7 +5955,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5961,7 +5998,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4906-2024</t>
+          <t>A 30796-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5975,10 +6012,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45329</v>
+        <v>45497</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5991,7 +6028,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6034,7 +6071,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7655-2026</t>
+          <t>A 18840-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6048,10 +6085,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46062</v>
+        <v>46129</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6064,7 +6101,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6107,7 +6144,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34671-2025</t>
+          <t>A 16152-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6121,10 +6158,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45847</v>
+        <v>45406</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6136,13 +6173,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6185,7 +6217,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7659-2026</t>
+          <t>A 4906-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6199,10 +6231,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46062</v>
+        <v>45329</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6215,7 +6247,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6258,7 +6290,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 47902-2024</t>
+          <t>A 47708-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6272,10 +6304,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45589</v>
+        <v>45931</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6288,7 +6320,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6331,7 +6363,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 58330-2022</t>
+          <t>A 48790-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6345,10 +6377,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44901</v>
+        <v>45937</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6361,7 +6393,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6404,7 +6436,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 10640-2025</t>
+          <t>A 19373-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6418,10 +6450,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45721</v>
+        <v>46133</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6434,7 +6466,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6477,7 +6509,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13510-2022</t>
+          <t>A 48791-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6491,10 +6523,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44648</v>
+        <v>45937</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6507,7 +6539,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>17.6</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6550,7 +6582,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13119-2023</t>
+          <t>A 53131-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6564,10 +6596,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45002</v>
+        <v>44876</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6580,7 +6612,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6623,7 +6655,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 68454-2021</t>
+          <t>A 48787-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6637,10 +6669,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44529</v>
+        <v>45937</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6653,7 +6685,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6713,7 +6745,7 @@
         <v>45937</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6769,7 +6801,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 36192-2025</t>
+          <t>A 7783-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6783,10 +6815,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45867</v>
+        <v>44973</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6799,7 +6831,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6842,7 +6874,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48790-2025</t>
+          <t>A 11460-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6856,10 +6888,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45937</v>
+        <v>45372</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6872,7 +6904,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6915,7 +6947,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47708-2025</t>
+          <t>A 50337-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6929,10 +6961,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45931</v>
+        <v>45944</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6945,7 +6977,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6988,7 +7020,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 48787-2025</t>
+          <t>A 50209-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7002,10 +7034,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45937</v>
+        <v>45943</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7018,7 +7050,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7061,7 +7093,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 48791-2025</t>
+          <t>A 62299-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7075,10 +7107,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45937</v>
+        <v>44923</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7091,7 +7123,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7134,7 +7166,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 57259-2022</t>
+          <t>A 20009-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7148,10 +7180,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44895</v>
+        <v>46136</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7164,7 +7196,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7207,7 +7239,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 50209-2025</t>
+          <t>A 49781-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7221,10 +7253,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45943</v>
+        <v>45597</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7237,7 +7269,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7280,7 +7312,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 50337-2025</t>
+          <t>A 34909-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7294,10 +7326,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45944</v>
+        <v>45141</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7310,7 +7342,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7385,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10777-2024</t>
+          <t>A 13883-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7399,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45369</v>
+        <v>44650</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7383,7 +7415,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7458,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32527-2024</t>
+          <t>A 55033-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7472,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45513</v>
+        <v>45237</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7455,13 +7487,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>8.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7531,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 32541-2024</t>
+          <t>A 6354-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7545,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45513</v>
+        <v>45699</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7533,13 +7560,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>19.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7604,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 2263-2024</t>
+          <t>A 4307-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7618,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45310</v>
+        <v>45685</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7611,13 +7633,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7677,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 14211-2026</t>
+          <t>A 21363-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7691,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46099</v>
+        <v>45063</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7690,7 +7707,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7733,7 +7750,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 15592-2026</t>
+          <t>A 53401-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7747,10 +7764,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46106</v>
+        <v>44879</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7763,7 +7780,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>8.4</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7806,7 +7823,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 16030-2026</t>
+          <t>A 40896-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7820,10 +7837,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46108</v>
+        <v>44825</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7836,7 +7853,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>15.8</v>
+        <v>11.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7879,7 +7896,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 54526-2025</t>
+          <t>A 15658-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7893,10 +7910,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45965</v>
+        <v>45748</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7909,7 +7926,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7952,7 +7969,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 17485-2026</t>
+          <t>A 15000-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7962,14 +7979,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46120</v>
+        <v>45015</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7982,7 +7999,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8025,7 +8042,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 53227-2021</t>
+          <t>A 65254-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8039,10 +8056,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44468</v>
+        <v>44515</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8055,7 +8072,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8098,7 +8115,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 18840-2026</t>
+          <t>A 3272-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8112,10 +8129,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46129</v>
+        <v>45679</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8128,7 +8145,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8171,7 +8188,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 8273-2024</t>
+          <t>A 30773-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8185,10 +8202,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45352</v>
+        <v>45496</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8201,7 +8218,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8244,7 +8261,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 52688-2024</t>
+          <t>A 46364-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8258,10 +8275,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45610</v>
+        <v>45582</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8317,7 +8334,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 19373-2026</t>
+          <t>A 6251-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8331,10 +8348,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46133</v>
+        <v>44965</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8347,7 +8364,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>15.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8390,7 +8407,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56523-2025</t>
+          <t>A 54526-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8404,10 +8421,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45975</v>
+        <v>45965</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8420,7 +8437,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8463,7 +8480,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 57262-2025</t>
+          <t>A 24127-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8477,10 +8494,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45979</v>
+        <v>45456</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8493,7 +8510,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8536,7 +8553,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20009-2026</t>
+          <t>A 15181-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8550,10 +8567,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46136</v>
+        <v>45016</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8566,7 +8583,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8609,7 +8626,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 57890-2025</t>
+          <t>A 23451-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8623,10 +8640,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45981</v>
+        <v>45076</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8638,8 +8655,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8682,7 +8704,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 57886-2025</t>
+          <t>A 56523-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8696,10 +8718,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45981</v>
+        <v>45975</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8712,7 +8734,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>8</v>
+        <v>1.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8755,7 +8777,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 57891-2025</t>
+          <t>A 3886-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8769,10 +8791,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45981</v>
+        <v>45684</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8784,8 +8806,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8828,7 +8855,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 46529-2024</t>
+          <t>A 20500-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8842,10 +8869,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45582</v>
+        <v>46140</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8858,7 +8885,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>11.7</v>
+        <v>2.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8901,7 +8928,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 131-2024</t>
+          <t>A 20501-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8915,10 +8942,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45294</v>
+        <v>46140</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8931,7 +8958,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8974,7 +9001,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 75-2025</t>
+          <t>A 20152-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8988,10 +9015,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45659</v>
+        <v>46138</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9004,7 +9031,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9047,7 +9074,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 59252-2025</t>
+          <t>A 57262-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9061,10 +9088,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45988</v>
+        <v>45979</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9077,7 +9104,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9120,7 +9147,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 68400-2021</t>
+          <t>A 855-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9134,10 +9161,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44529</v>
+        <v>44931</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9150,7 +9177,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9193,7 +9220,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 3272-2025</t>
+          <t>A 57890-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9207,10 +9234,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45679</v>
+        <v>45981</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9223,7 +9250,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9266,7 +9293,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 54087-2021</t>
+          <t>A 47755-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9280,10 +9307,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44470</v>
+        <v>44854</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9295,13 +9322,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9344,7 +9366,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 60505-2025</t>
+          <t>A 57886-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9358,10 +9380,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45995</v>
+        <v>45981</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9374,7 +9396,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9417,7 +9439,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 35465-2022</t>
+          <t>A 9821-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9431,10 +9453,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44798</v>
+        <v>44620</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9447,7 +9469,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9490,7 +9512,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61535-2025</t>
+          <t>A 57891-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9504,10 +9526,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46001</v>
+        <v>45981</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9520,7 +9542,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9563,7 +9585,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61539-2025</t>
+          <t>A 41554-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9577,10 +9599,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46001</v>
+        <v>45560</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9593,7 +9615,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9636,7 +9658,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 39116-2022</t>
+          <t>A 28224-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9650,10 +9672,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44817</v>
+        <v>45099</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9666,7 +9688,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9709,7 +9731,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 20152-2026</t>
+          <t>A 61046-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9723,10 +9745,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46138</v>
+        <v>45645</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9739,7 +9761,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9782,7 +9804,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 62266-2022</t>
+          <t>A 59252-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9796,10 +9818,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44923</v>
+        <v>45988</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9812,7 +9834,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9855,7 +9877,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 30773-2024</t>
+          <t>A 13220-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9869,10 +9891,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45496</v>
+        <v>44644</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9885,7 +9907,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9928,7 +9950,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 28224-2023</t>
+          <t>A 68400-2021</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9942,10 +9964,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45099</v>
+        <v>44529</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9958,7 +9980,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10001,7 +10023,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 4307-2025</t>
+          <t>A 60505-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10015,10 +10037,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45685</v>
+        <v>45995</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10031,7 +10053,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10074,7 +10096,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 10767-2024</t>
+          <t>A 21929-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10088,10 +10110,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45369</v>
+        <v>46150</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10104,7 +10126,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10147,7 +10169,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 20500-2026</t>
+          <t>A 61535-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10161,10 +10183,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46140</v>
+        <v>46001</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10177,7 +10199,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10220,7 +10242,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 60103-2022</t>
+          <t>A 61539-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10234,10 +10256,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44909</v>
+        <v>46001</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10250,7 +10272,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10293,7 +10315,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 20667-2026</t>
+          <t>A 22207-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10307,10 +10329,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46141</v>
+        <v>46153</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10323,7 +10345,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10366,7 +10388,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 20501-2026</t>
+          <t>A 53193-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10380,10 +10402,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46140</v>
+        <v>45229</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10396,7 +10418,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10439,7 +10461,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 13515-2022</t>
+          <t>A 22620-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10453,10 +10475,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44648</v>
+        <v>46155</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10469,7 +10491,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10512,7 +10534,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 4077-2025</t>
+          <t>A 39611-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10526,10 +10548,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45684</v>
+        <v>44818</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10541,8 +10563,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10585,7 +10612,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 2402-2024</t>
+          <t>A 29300-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10599,10 +10626,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45310</v>
+        <v>45483</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10615,7 +10642,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10658,7 +10685,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 22207-2026</t>
+          <t>A 7628-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10672,10 +10699,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46153</v>
+        <v>44607</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10688,7 +10715,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10731,7 +10758,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 21929-2026</t>
+          <t>A 63884-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10745,10 +10772,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46150</v>
+        <v>46020</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10761,7 +10788,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10804,7 +10831,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 73158-2021</t>
+          <t>A 53426-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10818,10 +10845,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44550</v>
+        <v>44879</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10834,7 +10861,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>13.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10877,7 +10904,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 13883-2022</t>
+          <t>A 60-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10891,10 +10918,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44650</v>
+        <v>46024</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10907,7 +10934,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10950,7 +10977,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 22620-2026</t>
+          <t>A 62266-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10964,10 +10991,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46155</v>
+        <v>44923</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10980,7 +11007,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11023,7 +11050,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 10858-2026</t>
+          <t>A 39116-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11037,10 +11064,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46078</v>
+        <v>44817</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11053,7 +11080,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>8.5</v>
+        <v>3.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11096,7 +11123,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 59625-2023</t>
+          <t>A 57918-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11110,10 +11137,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45254</v>
+        <v>44900</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11126,7 +11153,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11169,7 +11196,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 27441-2026</t>
+          <t>A 25514-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11183,10 +11210,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46189</v>
+        <v>44732</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11199,7 +11226,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11242,7 +11269,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 27586-2026</t>
+          <t>A 41893-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11252,14 +11279,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46190</v>
+        <v>44830</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11271,8 +11298,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11315,7 +11347,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 32804-2026</t>
+          <t>A 1525-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11329,10 +11361,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46241</v>
+        <v>46034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11342,11 +11374,6 @@
       <c r="G145" t="inlineStr">
         <is>
           <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -11393,7 +11420,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 15659-2025</t>
+          <t>A 53227-2021</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11407,10 +11434,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45748</v>
+        <v>44468</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11423,7 +11450,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11466,7 +11493,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 32797-2026</t>
+          <t>A 18612-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11480,10 +11507,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46241</v>
+        <v>45763</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11495,13 +11522,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11544,7 +11566,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 16154-2024</t>
+          <t>A 3256-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11558,10 +11580,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45406</v>
+        <v>46041</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11574,7 +11596,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11617,7 +11639,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 16155-2024</t>
+          <t>A 10858-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11631,10 +11653,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45406</v>
+        <v>46078</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11647,7 +11669,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11690,7 +11712,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 33830-2026</t>
+          <t>A 10494-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11704,10 +11726,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46251</v>
+        <v>44623</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11720,7 +11742,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>8.9</v>
+        <v>13.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11763,7 +11785,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33782-2026</t>
+          <t>A 7730-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11777,10 +11799,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46251</v>
+        <v>44973</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11793,7 +11815,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11836,7 +11858,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 30505-2026</t>
+          <t>A 52688-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11850,10 +11872,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46210</v>
+        <v>45610</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11866,7 +11888,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11909,7 +11931,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 35969-2024</t>
+          <t>A 47902-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11923,10 +11945,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45533</v>
+        <v>45589</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11939,7 +11961,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11982,7 +12004,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 41554-2024</t>
+          <t>A 7655-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11996,10 +12018,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45560</v>
+        <v>46062</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12012,7 +12034,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12055,7 +12077,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 45983-2024</t>
+          <t>A 7659-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12069,10 +12091,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45580</v>
+        <v>46062</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12085,7 +12107,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12128,7 +12150,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 32826-2022</t>
+          <t>A 68454-2021</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12142,10 +12164,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44784</v>
+        <v>44529</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12158,7 +12180,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12201,7 +12223,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 53426-2022</t>
+          <t>A 7781-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12215,10 +12237,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44879</v>
+        <v>44973</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12231,7 +12253,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>13.2</v>
+        <v>0.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12274,7 +12296,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 13220-2022</t>
+          <t>A 73158-2021</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12288,10 +12310,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44644</v>
+        <v>44550</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12347,7 +12369,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 19447-2025</t>
+          <t>A 27441-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12361,10 +12383,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45770</v>
+        <v>46189</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12377,7 +12399,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12420,7 +12442,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 36033-2026</t>
+          <t>A 38941-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12434,10 +12456,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46267</v>
+        <v>45163</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12450,7 +12472,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12493,7 +12515,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 64669-2023</t>
+          <t>A 27586-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12503,14 +12525,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45281</v>
+        <v>46190</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12523,7 +12545,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12583,7 +12605,7 @@
         <v>45029</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12656,7 +12678,7 @@
         <v>45029</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12712,7 +12734,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 53131-2022</t>
+          <t>A 34435-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12726,10 +12748,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44876</v>
+        <v>45525</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12742,7 +12764,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12785,7 +12807,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 64784-2023</t>
+          <t>A 2263-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12799,10 +12821,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45282</v>
+        <v>45310</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12814,8 +12836,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12858,7 +12885,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 3044-2022</t>
+          <t>A 37305-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12872,10 +12899,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44582</v>
+        <v>44808</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12888,7 +12915,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.3</v>
+        <v>9.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12931,7 +12958,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 15000-2023</t>
+          <t>A 60498-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12945,10 +12972,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45015</v>
+        <v>45643</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12961,7 +12988,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13004,7 +13031,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 49-2026</t>
+          <t>A 42456-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13018,10 +13045,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46024</v>
+        <v>45565</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13034,7 +13061,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13077,7 +13104,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 6251-2023</t>
+          <t>A 37562-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13091,10 +13118,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44965</v>
+        <v>45541</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13107,7 +13134,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>15.4</v>
+        <v>4.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13150,7 +13177,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 19781-2025</t>
+          <t>A 32804-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13164,10 +13191,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45771</v>
+        <v>46241</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13179,8 +13206,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>6.1</v>
+        <v>1.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13223,7 +13255,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 23451-2023</t>
+          <t>A 15659-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13237,10 +13269,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45076</v>
+        <v>45748</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13252,13 +13284,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13301,7 +13328,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 60498-2024</t>
+          <t>A 19781-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13315,10 +13342,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45643</v>
+        <v>45771</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13331,7 +13358,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.1</v>
+        <v>6.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13374,7 +13401,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 5927-2022</t>
+          <t>A 12967-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13388,10 +13415,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44598</v>
+        <v>45385</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13404,7 +13431,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13447,7 +13474,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 41893-2022</t>
+          <t>A 32797-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13461,10 +13488,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44830</v>
+        <v>46241</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13478,11 +13505,11 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13525,7 +13552,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 7783-2023</t>
+          <t>A 37371-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13539,10 +13566,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44973</v>
+        <v>45156</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13555,7 +13582,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13598,7 +13625,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 5242-2022</t>
+          <t>A 35969-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13612,10 +13639,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44594</v>
+        <v>45533</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13628,7 +13655,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>8.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13671,7 +13698,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 57918-2022</t>
+          <t>A 7921-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13685,10 +13712,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44900</v>
+        <v>45350</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13701,7 +13728,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13744,7 +13771,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 7781-2023</t>
+          <t>A 13515-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13758,10 +13785,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44973</v>
+        <v>44648</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13774,7 +13801,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13817,7 +13844,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 7921-2024</t>
+          <t>A 33782-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13831,10 +13858,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45350</v>
+        <v>46251</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13847,7 +13874,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13890,7 +13917,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 45521-2022</t>
+          <t>A 33830-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13904,10 +13931,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44845</v>
+        <v>46251</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13920,7 +13947,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>4</v>
+        <v>8.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13963,7 +13990,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 17126-2022</t>
+          <t>A 75-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13977,10 +14004,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44677</v>
+        <v>45659</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13993,7 +14020,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14036,7 +14063,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 56116-2022</t>
+          <t>A 30505-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14050,10 +14077,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44889</v>
+        <v>46210</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14066,7 +14093,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14109,7 +14136,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 40896-2022</t>
+          <t>A 3795-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14123,10 +14150,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44825</v>
+        <v>45321</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14139,7 +14166,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>11.3</v>
+        <v>1.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14182,7 +14209,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 12329-2024</t>
+          <t>A 19773-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14196,10 +14223,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45378</v>
+        <v>45771</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14212,7 +14239,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14255,7 +14282,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 37371-2023</t>
+          <t>A 61884-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14269,10 +14296,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45156</v>
+        <v>45652</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14285,7 +14312,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14328,7 +14355,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 3074-2023</t>
+          <t>A 45521-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14342,10 +14369,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44946</v>
+        <v>44845</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14358,7 +14385,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14401,7 +14428,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 7730-2023</t>
+          <t>A 8273-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14415,10 +14442,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44973</v>
+        <v>45352</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14431,7 +14458,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14474,7 +14501,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 10494-2022</t>
+          <t>A 5927-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14488,10 +14515,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44623</v>
+        <v>44598</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14504,7 +14531,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>13.3</v>
+        <v>6.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14547,7 +14574,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 46364-2024</t>
+          <t>A 23984-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14561,10 +14588,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45582</v>
+        <v>45456</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14577,7 +14604,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14620,7 +14647,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 33546-2022</t>
+          <t>A 24129-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14634,10 +14661,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44789</v>
+        <v>45456</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14650,7 +14677,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14693,7 +14720,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 9821-2022</t>
+          <t>A 2402-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14707,10 +14734,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44620</v>
+        <v>45310</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14723,7 +14750,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14766,7 +14793,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 38941-2023</t>
+          <t>A 3399-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14780,10 +14807,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45163</v>
+        <v>45318</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14796,7 +14823,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14839,7 +14866,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 49781-2024</t>
+          <t>A 10767-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14853,10 +14880,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45597</v>
+        <v>45369</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14869,7 +14896,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>5.7</v>
+        <v>1.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14912,7 +14939,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 61046-2024</t>
+          <t>A 24432-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14922,14 +14949,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45645</v>
+        <v>44726</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14942,7 +14969,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -14985,7 +15012,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 3795-2024</t>
+          <t>A 36033-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14999,10 +15026,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45321</v>
+        <v>46267</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15058,7 +15085,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 42456-2024</t>
+          <t>A 16487-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15072,10 +15099,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45565</v>
+        <v>45029</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15088,7 +15115,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15131,7 +15158,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 30796-2024</t>
+          <t>A 64669-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15145,10 +15172,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45497</v>
+        <v>45281</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15161,7 +15188,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15204,7 +15231,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 16152-2024</t>
+          <t>A 55303-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15218,10 +15245,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45406</v>
+        <v>44887</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15234,7 +15261,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15277,7 +15304,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 47755-2022</t>
+          <t>A 12329-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15291,10 +15318,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44854</v>
+        <v>45378</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15307,7 +15334,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15350,7 +15377,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 10768-2024</t>
+          <t>A 4077-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15364,10 +15391,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45369</v>
+        <v>45684</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15380,7 +15407,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15423,7 +15450,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 62299-2022</t>
+          <t>A 62294-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15440,7 +15467,7 @@
         <v>44923</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15453,7 +15480,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15496,7 +15523,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 11460-2024</t>
+          <t>A 49-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15510,10 +15537,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45372</v>
+        <v>46024</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15526,7 +15553,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15569,7 +15596,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 55303-2022</t>
+          <t>A 12264-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15583,10 +15610,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44887</v>
+        <v>45378</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15642,7 +15669,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 36982-2024</t>
+          <t>A 12266-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15656,10 +15683,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45539</v>
+        <v>45378</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15672,7 +15699,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15715,7 +15742,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 855-2023</t>
+          <t>A 44708-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15729,10 +15756,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44931</v>
+        <v>45190</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15745,7 +15772,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15788,7 +15815,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 21363-2023</t>
+          <t>A 20955-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15802,10 +15829,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45063</v>
+        <v>45777</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15818,7 +15845,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15861,7 +15888,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 61884-2024</t>
+          <t>A 20667-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15875,10 +15902,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45652</v>
+        <v>46141</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15891,7 +15918,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15934,7 +15961,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 19773-2025</t>
+          <t>A 22016-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15948,10 +15975,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45771</v>
+        <v>45784</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15964,7 +15991,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16007,7 +16034,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 3399-2024</t>
+          <t>A 37801-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16017,14 +16044,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45318</v>
+        <v>45543</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16037,7 +16064,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16080,7 +16107,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 44708-2023</t>
+          <t>A 24559-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16094,10 +16121,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45190</v>
+        <v>45798</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16110,7 +16137,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16153,7 +16180,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 25514-2022</t>
+          <t>A 11837-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16167,10 +16194,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44732</v>
+        <v>45728</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16183,7 +16210,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16226,7 +16253,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 12967-2024</t>
+          <t>A 15645-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16240,10 +16267,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45385</v>
+        <v>45404</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16256,7 +16283,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16299,7 +16326,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 24432-2022</t>
+          <t>A 45519-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16309,14 +16336,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44726</v>
+        <v>45194</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16329,7 +16356,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16372,7 +16399,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 37658-2022</t>
+          <t>A 49062-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16386,10 +16413,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44810</v>
+        <v>45594</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16402,7 +16429,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16445,7 +16472,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 15658-2025</t>
+          <t>A 27201-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16459,10 +16486,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45748</v>
+        <v>45812</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16475,7 +16502,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16518,7 +16545,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 66960-2021</t>
+          <t>A 30486-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16532,10 +16559,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44522</v>
+        <v>45829</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16591,7 +16618,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 37305-2022</t>
+          <t>A 31464-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16605,10 +16632,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44808</v>
+        <v>45833</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16621,7 +16648,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>9.9</v>
+        <v>1.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16664,7 +16691,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 53193-2023</t>
+          <t>A 34671-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16678,10 +16705,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45229</v>
+        <v>45847</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16693,8 +16720,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16737,7 +16769,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 20955-2025</t>
+          <t>A 13510-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16751,10 +16783,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45777</v>
+        <v>44648</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16767,7 +16799,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.2</v>
+        <v>17.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16810,7 +16842,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 22016-2025</t>
+          <t>A 10640-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -16824,10 +16856,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45784</v>
+        <v>45721</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16840,7 +16872,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -16880,78 +16912,151 @@
       </c>
       <c r="V220" s="2" t="inlineStr"/>
     </row>
-    <row r="221">
+    <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
+          <t>A 36192-2025</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D221" s="1" t="n">
+        <v>45867</v>
+      </c>
+      <c r="E221" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>TROLLHÄTTAN</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="n">
+        <v>0</v>
+      </c>
+      <c r="T221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="n">
+        <v>0</v>
+      </c>
+      <c r="V221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
           <t>S 643-2026</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C222" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D221" s="1" t="n">
+      <c r="D222" s="1" t="n">
         <v>46090</v>
       </c>
-      <c r="E221" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="I221" t="n">
+      <c r="E222" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>TROLLHÄTTAN</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
         <v>0.8</v>
       </c>
-      <c r="J221" t="n">
-        <v>0</v>
-      </c>
-      <c r="K221" t="n">
-        <v>0</v>
-      </c>
-      <c r="L221" t="n">
-        <v>0</v>
-      </c>
-      <c r="M221" t="n">
-        <v>0</v>
-      </c>
-      <c r="N221" t="n">
-        <v>0</v>
-      </c>
-      <c r="O221" t="n">
-        <v>0</v>
-      </c>
-      <c r="P221" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0</v>
-      </c>
-      <c r="S221" t="n">
-        <v>0</v>
-      </c>
-      <c r="T221" t="n">
-        <v>0</v>
-      </c>
-      <c r="U221" t="n">
-        <v>0</v>
-      </c>
-      <c r="V221" s="2" t="inlineStr"/>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="n">
+        <v>0</v>
+      </c>
+      <c r="T222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="n">
+        <v>0</v>
+      </c>
+      <c r="V222" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45386</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44876</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44572</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44461</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44622</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44811</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>44686</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>44757</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 67535-2021</t>
+          <t>A 19577-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44524</v>
+        <v>44693</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2576,13 +2576,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2625,7 +2620,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 66971-2021</t>
+          <t>A 52687-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2639,10 +2634,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44522</v>
+        <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2655,7 +2650,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2698,7 +2693,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33546-2022</t>
+          <t>A 67535-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2712,10 +2707,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44789</v>
+        <v>44524</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2727,8 +2722,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 19577-2022</t>
+          <t>A 66971-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44693</v>
+        <v>44522</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2861,7 +2861,7 @@
         <v>44565</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 11123-2024</t>
+          <t>A 1295-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45371</v>
+        <v>44572</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10768-2024</t>
+          <t>A 24127-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45369</v>
+        <v>45456</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10777-2024</t>
+          <t>A 23984-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45369</v>
+        <v>45456</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37658-2022</t>
+          <t>A 62294-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44810</v>
+        <v>44923</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1295-2022</t>
+          <t>A 12264-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44572</v>
+        <v>45378</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 52687-2021</t>
+          <t>A 12266-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44466</v>
+        <v>45378</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 35465-2022</t>
+          <t>A 6354-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44798</v>
+        <v>45699</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>19.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 65116-2023</t>
+          <t>A 3886-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3438,14 +3438,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45287</v>
+        <v>45684</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3457,8 +3457,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3501,7 +3506,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59625-2023</t>
+          <t>A 65254-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3515,10 +3520,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45254</v>
+        <v>44515</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3531,7 +3536,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3574,7 +3579,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19447-2025</t>
+          <t>A 18612-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3588,10 +3593,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45770</v>
+        <v>45763</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3604,7 +3609,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3647,7 +3652,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 131-2024</t>
+          <t>A 39611-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3661,10 +3666,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45294</v>
+        <v>44818</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3676,8 +3681,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>7.5</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3720,7 +3730,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 54087-2021</t>
+          <t>A 34909-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3734,10 +3744,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44470</v>
+        <v>45141</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3749,13 +3759,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3798,7 +3803,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60103-2022</t>
+          <t>A 15704-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3812,10 +3817,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44909</v>
+        <v>45021</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3828,7 +3833,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3871,7 +3876,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3044-2022</t>
+          <t>A 15181-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3885,10 +3890,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44582</v>
+        <v>45016</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3901,7 +3906,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3944,7 +3949,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 56116-2022</t>
+          <t>A 65116-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3954,14 +3959,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44889</v>
+        <v>45287</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3974,7 +3979,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4017,7 +4022,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 64784-2023</t>
+          <t>A 24129-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4031,10 +4036,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45282</v>
+        <v>45456</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4047,7 +4052,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4090,7 +4095,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15648-2025</t>
+          <t>A 29300-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4104,10 +4109,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45748</v>
+        <v>45483</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4120,7 +4125,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4163,7 +4168,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 36982-2024</t>
+          <t>A 16487-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4177,10 +4182,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45539</v>
+        <v>45029</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4193,7 +4198,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4236,7 +4241,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32527-2024</t>
+          <t>A 15645-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,10 +4255,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45513</v>
+        <v>45404</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4265,13 +4270,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>8.699999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32541-2024</t>
+          <t>A 11123-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45513</v>
+        <v>45371</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4343,13 +4343,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4392,7 +4387,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 21979-2025</t>
+          <t>A 24559-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4406,10 +4401,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45784</v>
+        <v>45798</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4422,7 +4417,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4465,7 +4460,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27652-2022</t>
+          <t>A 60-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4479,10 +4474,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44743</v>
+        <v>46024</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4495,7 +4490,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>9.1</v>
+        <v>3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4538,7 +4533,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 66960-2021</t>
+          <t>A 34435-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4552,10 +4547,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44522</v>
+        <v>45525</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4568,7 +4563,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4611,7 +4606,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 14211-2026</t>
+          <t>A 55033-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4625,10 +4620,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46099</v>
+        <v>45237</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4641,7 +4636,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4684,7 +4679,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45983-2024</t>
+          <t>A 53401-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4698,10 +4693,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45580</v>
+        <v>44879</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4714,7 +4709,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4757,7 +4752,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 5242-2022</t>
+          <t>A 46533-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4771,10 +4766,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44594</v>
+        <v>45582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4787,7 +4782,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4830,7 +4825,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11991-2022</t>
+          <t>A 37562-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4844,10 +4839,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44635</v>
+        <v>45541</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4860,7 +4855,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4903,7 +4898,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15592-2026</t>
+          <t>A 27652-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4917,10 +4912,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46106</v>
+        <v>44743</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4933,7 +4928,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4976,7 +4971,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3074-2023</t>
+          <t>A 49062-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4990,10 +4985,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44946</v>
+        <v>45594</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5006,7 +5001,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.1</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5049,7 +5044,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13119-2023</t>
+          <t>A 45519-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5063,10 +5058,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45002</v>
+        <v>45194</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5079,7 +5074,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5122,7 +5117,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16030-2026</t>
+          <t>A 15648-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5136,10 +5131,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46108</v>
+        <v>45748</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5152,7 +5147,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>15.8</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5195,7 +5190,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 46529-2024</t>
+          <t>A 27201-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5209,10 +5204,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45582</v>
+        <v>45812</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5225,7 +5220,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5268,7 +5263,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16154-2024</t>
+          <t>A 7628-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5282,10 +5277,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45406</v>
+        <v>44607</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5298,7 +5293,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5341,7 +5336,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 16155-2024</t>
+          <t>A 21979-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5355,10 +5350,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45406</v>
+        <v>45784</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5371,7 +5366,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5414,7 +5409,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 57259-2022</t>
+          <t>A 59879-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5428,10 +5423,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44895</v>
+        <v>45640</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5444,7 +5439,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5487,7 +5482,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 17126-2022</t>
+          <t>A 1525-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5501,10 +5496,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44677</v>
+        <v>46034</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5517,7 +5512,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5560,7 +5555,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17485-2026</t>
+          <t>A 11991-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5570,14 +5565,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46120</v>
+        <v>44635</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5590,7 +5585,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5633,7 +5628,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59879-2024</t>
+          <t>A 4906-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5647,10 +5642,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45640</v>
+        <v>45329</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5663,7 +5658,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5706,7 +5701,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32826-2022</t>
+          <t>A 30486-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5720,10 +5715,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44784</v>
+        <v>45829</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5736,7 +5731,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5779,7 +5774,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 58330-2022</t>
+          <t>A 47902-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5793,10 +5788,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44901</v>
+        <v>45589</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5809,7 +5804,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5852,7 +5847,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 46533-2024</t>
+          <t>A 31464-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5866,10 +5861,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45582</v>
+        <v>45833</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5882,7 +5877,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5925,7 +5920,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15704-2023</t>
+          <t>A 58330-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5939,10 +5934,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45021</v>
+        <v>44901</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5955,7 +5950,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5998,7 +5993,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30796-2024</t>
+          <t>A 13119-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6012,10 +6007,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45497</v>
+        <v>45002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6028,7 +6023,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6071,7 +6066,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18840-2026</t>
+          <t>A 68454-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6085,10 +6080,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46129</v>
+        <v>44529</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6101,7 +6096,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6144,7 +6139,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 16152-2024</t>
+          <t>A 57259-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6158,10 +6153,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45406</v>
+        <v>44895</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6174,7 +6169,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6217,7 +6212,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4906-2024</t>
+          <t>A 10777-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6231,10 +6226,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45329</v>
+        <v>45369</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6247,7 +6242,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6290,7 +6285,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 47708-2025</t>
+          <t>A 34671-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6304,10 +6299,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45931</v>
+        <v>45847</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6319,8 +6314,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48790-2025</t>
+          <t>A 10640-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45937</v>
+        <v>45721</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 19373-2026</t>
+          <t>A 13510-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46133</v>
+        <v>44648</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>17.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48791-2025</t>
+          <t>A 3256-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45937</v>
+        <v>46041</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>8.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 53131-2022</t>
+          <t>A 36192-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44876</v>
+        <v>45867</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 48787-2025</t>
+          <t>A 48788-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6672,7 +6672,7 @@
         <v>45937</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 48788-2025</t>
+          <t>A 48790-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6745,7 +6745,7 @@
         <v>45937</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7783-2023</t>
+          <t>A 47708-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44973</v>
+        <v>45931</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11460-2024</t>
+          <t>A 48787-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45372</v>
+        <v>45937</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50337-2025</t>
+          <t>A 48791-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45944</v>
+        <v>45937</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7037,7 +7037,7 @@
         <v>45943</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 62299-2022</t>
+          <t>A 50337-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44923</v>
+        <v>45944</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 20009-2026</t>
+          <t>A 2263-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46136</v>
+        <v>45310</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7195,8 +7195,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7239,7 +7244,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 49781-2024</t>
+          <t>A 7655-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7253,10 +7258,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45597</v>
+        <v>46062</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7269,7 +7274,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7312,7 +7317,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34909-2023</t>
+          <t>A 53227-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7326,10 +7331,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45141</v>
+        <v>44468</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7342,7 +7347,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7385,7 +7390,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13883-2022</t>
+          <t>A 54526-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7399,10 +7404,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44650</v>
+        <v>45965</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7415,7 +7420,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7458,7 +7463,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 55033-2023</t>
+          <t>A 7659-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7472,10 +7477,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45237</v>
+        <v>46062</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7488,7 +7493,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7531,7 +7536,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 6354-2025</t>
+          <t>A 8273-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7545,10 +7550,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45699</v>
+        <v>45352</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7561,7 +7566,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>19.3</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7604,7 +7609,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4307-2025</t>
+          <t>A 52688-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7618,10 +7623,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45685</v>
+        <v>45610</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7634,7 +7639,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7677,7 +7682,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21363-2023</t>
+          <t>A 46529-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7691,10 +7696,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45063</v>
+        <v>45582</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7707,7 +7712,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.2</v>
+        <v>11.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7750,7 +7755,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 53401-2022</t>
+          <t>A 56523-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7764,10 +7769,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44879</v>
+        <v>45975</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7780,7 +7785,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7823,7 +7828,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 40896-2022</t>
+          <t>A 57262-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7837,10 +7842,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44825</v>
+        <v>45979</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7853,7 +7858,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>11.3</v>
+        <v>3.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7896,7 +7901,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 15658-2025</t>
+          <t>A 131-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7910,10 +7915,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45748</v>
+        <v>45294</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7926,7 +7931,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>7.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7969,7 +7974,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 15000-2023</t>
+          <t>A 75-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7983,10 +7988,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45015</v>
+        <v>45659</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7999,7 +8004,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8042,7 +8047,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 65254-2021</t>
+          <t>A 57890-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8056,10 +8061,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44515</v>
+        <v>45981</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8072,7 +8077,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8115,7 +8120,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 3272-2025</t>
+          <t>A 57886-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8129,10 +8134,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45679</v>
+        <v>45981</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8145,7 +8150,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.1</v>
+        <v>8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8188,7 +8193,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 30773-2024</t>
+          <t>A 57891-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8202,10 +8207,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45496</v>
+        <v>45981</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8218,7 +8223,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8261,7 +8266,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 46364-2024</t>
+          <t>A 68400-2021</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8275,10 +8280,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45582</v>
+        <v>44529</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8291,7 +8296,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8334,7 +8339,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6251-2023</t>
+          <t>A 54087-2021</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8348,10 +8353,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44965</v>
+        <v>44470</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8363,8 +8368,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>15.4</v>
+        <v>2.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8407,7 +8417,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 54526-2025</t>
+          <t>A 35465-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8421,10 +8431,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45965</v>
+        <v>44798</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8437,7 +8447,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8480,7 +8490,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 24127-2024</t>
+          <t>A 59252-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8494,10 +8504,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45456</v>
+        <v>45988</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8510,7 +8520,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8553,7 +8563,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 15181-2023</t>
+          <t>A 39116-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8567,10 +8577,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45016</v>
+        <v>44817</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8583,7 +8593,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8626,7 +8636,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 23451-2023</t>
+          <t>A 60505-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8640,10 +8650,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45076</v>
+        <v>45995</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8655,13 +8665,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8704,7 +8709,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56523-2025</t>
+          <t>A 61535-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8718,10 +8723,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45975</v>
+        <v>46001</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8734,7 +8739,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8777,7 +8782,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 3886-2025</t>
+          <t>A 61539-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8791,10 +8796,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45684</v>
+        <v>46001</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8806,13 +8811,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8855,7 +8855,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 20500-2026</t>
+          <t>A 62266-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46140</v>
+        <v>44923</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8928,7 +8928,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20501-2026</t>
+          <t>A 32527-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46140</v>
+        <v>45513</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8957,8 +8957,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9001,7 +9006,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 20152-2026</t>
+          <t>A 32541-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9015,10 +9020,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46138</v>
+        <v>45513</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9030,8 +9035,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9074,7 +9084,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 57262-2025</t>
+          <t>A 10767-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9088,10 +9098,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45979</v>
+        <v>45369</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9104,7 +9114,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9147,7 +9157,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 855-2023</t>
+          <t>A 60103-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9161,10 +9171,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44931</v>
+        <v>44909</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9177,7 +9187,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9220,7 +9230,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 57890-2025</t>
+          <t>A 63884-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9234,10 +9244,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45981</v>
+        <v>46020</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9250,7 +9260,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9293,7 +9303,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 47755-2022</t>
+          <t>A 14211-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9307,10 +9317,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44854</v>
+        <v>46099</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9323,7 +9333,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9366,7 +9376,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 57886-2025</t>
+          <t>A 13515-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9380,10 +9390,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45981</v>
+        <v>44648</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9396,7 +9406,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9439,7 +9449,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 9821-2022</t>
+          <t>A 4077-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9453,10 +9463,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44620</v>
+        <v>45684</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9469,7 +9479,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9512,7 +9522,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 57891-2025</t>
+          <t>A 15592-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9526,10 +9536,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45981</v>
+        <v>46106</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9542,7 +9552,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.8</v>
+        <v>8.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9585,7 +9595,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 41554-2024</t>
+          <t>A 2402-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9599,10 +9609,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45560</v>
+        <v>45310</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9615,7 +9625,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9658,7 +9668,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28224-2023</t>
+          <t>A 73158-2021</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9672,10 +9682,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45099</v>
+        <v>44550</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9688,7 +9698,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9731,7 +9741,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 61046-2024</t>
+          <t>A 13883-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9745,10 +9755,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45645</v>
+        <v>44650</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9761,7 +9771,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9804,7 +9814,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 59252-2025</t>
+          <t>A 16030-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9818,10 +9828,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45988</v>
+        <v>46108</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9834,7 +9844,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.6</v>
+        <v>15.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9877,7 +9887,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 13220-2022</t>
+          <t>A 17485-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9887,14 +9897,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44644</v>
+        <v>46120</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9907,7 +9917,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9950,7 +9960,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 68400-2021</t>
+          <t>A 18840-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9964,10 +9974,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44529</v>
+        <v>46129</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9980,7 +9990,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10023,7 +10033,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 60505-2025</t>
+          <t>A 59625-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10037,10 +10047,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45995</v>
+        <v>45254</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10053,7 +10063,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10096,7 +10106,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 21929-2026</t>
+          <t>A 15659-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10110,10 +10120,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46150</v>
+        <v>45748</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10126,7 +10136,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10169,7 +10179,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 61535-2025</t>
+          <t>A 16154-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10183,10 +10193,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46001</v>
+        <v>45406</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10199,7 +10209,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10242,7 +10252,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61539-2025</t>
+          <t>A 16155-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10256,10 +10266,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46001</v>
+        <v>45406</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10272,7 +10282,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10315,7 +10325,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 22207-2026</t>
+          <t>A 19373-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10329,10 +10339,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46153</v>
+        <v>46133</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10388,7 +10398,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 53193-2023</t>
+          <t>A 20009-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10402,10 +10412,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45229</v>
+        <v>46136</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10418,7 +10428,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10461,7 +10471,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 22620-2026</t>
+          <t>A 35969-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10475,10 +10485,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46155</v>
+        <v>45533</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10491,7 +10501,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10534,7 +10544,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 39611-2022</t>
+          <t>A 41554-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10548,10 +10558,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44818</v>
+        <v>45560</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10563,13 +10573,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10612,7 +10617,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 29300-2024</t>
+          <t>A 3272-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10626,10 +10631,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45483</v>
+        <v>45679</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10642,7 +10647,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10685,7 +10690,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 7628-2022</t>
+          <t>A 45983-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10699,10 +10704,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44607</v>
+        <v>45580</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10715,7 +10720,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10758,7 +10763,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 63884-2025</t>
+          <t>A 32826-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10772,10 +10777,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46020</v>
+        <v>44784</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10788,7 +10793,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10848,7 +10853,7 @@
         <v>44879</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10904,7 +10909,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 60-2026</t>
+          <t>A 13220-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10918,10 +10923,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46024</v>
+        <v>44644</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10934,7 +10939,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10977,7 +10982,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 62266-2022</t>
+          <t>A 19447-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10991,10 +10996,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44923</v>
+        <v>45770</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11007,7 +11012,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11050,7 +11055,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 39116-2022</t>
+          <t>A 64669-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11064,10 +11069,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44817</v>
+        <v>45281</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11080,7 +11085,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11123,7 +11128,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 57918-2022</t>
+          <t>A 20152-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11137,10 +11142,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44900</v>
+        <v>46138</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11153,7 +11158,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11196,7 +11201,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 25514-2022</t>
+          <t>A 16473-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11210,10 +11215,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44732</v>
+        <v>45029</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11226,7 +11231,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11269,7 +11274,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 41893-2022</t>
+          <t>A 16475-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11283,10 +11288,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44830</v>
+        <v>45029</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11298,13 +11303,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11347,7 +11347,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 1525-2026</t>
+          <t>A 53131-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11361,10 +11361,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46034</v>
+        <v>44876</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11420,7 +11420,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 53227-2021</t>
+          <t>A 30773-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11434,10 +11434,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44468</v>
+        <v>45496</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11493,7 +11493,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 18612-2025</t>
+          <t>A 28224-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11507,10 +11507,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45763</v>
+        <v>45099</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11566,7 +11566,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 3256-2026</t>
+          <t>A 4307-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11580,10 +11580,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46041</v>
+        <v>45685</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>8.1</v>
+        <v>1.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11639,7 +11639,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 10858-2026</t>
+          <t>A 64784-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11653,10 +11653,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46078</v>
+        <v>45282</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>8.5</v>
+        <v>2.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11712,7 +11712,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 10494-2022</t>
+          <t>A 20500-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11726,10 +11726,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44623</v>
+        <v>46140</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>13.3</v>
+        <v>2.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 7730-2023</t>
+          <t>A 3044-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11799,10 +11799,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44973</v>
+        <v>44582</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 52688-2024</t>
+          <t>A 15000-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11872,10 +11872,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45610</v>
+        <v>45015</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11931,7 +11931,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 47902-2024</t>
+          <t>A 20501-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11945,10 +11945,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45589</v>
+        <v>46140</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12004,7 +12004,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 7655-2026</t>
+          <t>A 6251-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12018,10 +12018,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46062</v>
+        <v>44965</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.5</v>
+        <v>15.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12077,7 +12077,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 7659-2026</t>
+          <t>A 19781-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46062</v>
+        <v>45771</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12150,7 +12150,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 68454-2021</t>
+          <t>A 22207-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12164,10 +12164,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44529</v>
+        <v>46153</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12223,7 +12223,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 7781-2023</t>
+          <t>A 21929-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12237,10 +12237,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44973</v>
+        <v>46150</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12296,7 +12296,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 73158-2021</t>
+          <t>A 23451-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12310,10 +12310,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44550</v>
+        <v>45076</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12325,8 +12325,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12369,7 +12374,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 27441-2026</t>
+          <t>A 60498-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12383,10 +12388,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46189</v>
+        <v>45643</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12399,7 +12404,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12442,7 +12447,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 38941-2023</t>
+          <t>A 5927-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12456,10 +12461,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45163</v>
+        <v>44598</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12472,7 +12477,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12515,7 +12520,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 27586-2026</t>
+          <t>A 22620-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12525,14 +12530,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46190</v>
+        <v>46155</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12545,7 +12550,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12588,7 +12593,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 16473-2023</t>
+          <t>A 41893-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12602,10 +12607,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45029</v>
+        <v>44830</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12617,8 +12622,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12661,7 +12671,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 16475-2023</t>
+          <t>A 7783-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12675,10 +12685,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45029</v>
+        <v>44973</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12691,7 +12701,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12734,7 +12744,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 34435-2024</t>
+          <t>A 5242-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12748,10 +12758,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45525</v>
+        <v>44594</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12764,7 +12774,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12807,7 +12817,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 2263-2024</t>
+          <t>A 57918-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12821,10 +12831,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45310</v>
+        <v>44900</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12836,13 +12846,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12885,7 +12890,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 37305-2022</t>
+          <t>A 7781-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12899,10 +12904,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44808</v>
+        <v>44973</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12915,7 +12920,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>9.9</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12958,7 +12963,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 60498-2024</t>
+          <t>A 7921-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12972,10 +12977,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45643</v>
+        <v>45350</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12988,7 +12993,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13031,7 +13036,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 42456-2024</t>
+          <t>A 45521-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13045,10 +13050,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45565</v>
+        <v>44845</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13061,7 +13066,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13104,7 +13109,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 37562-2024</t>
+          <t>A 10858-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13118,10 +13123,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45541</v>
+        <v>46078</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13134,7 +13139,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.2</v>
+        <v>8.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13177,7 +13182,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 32804-2026</t>
+          <t>A 17126-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13191,10 +13196,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46241</v>
+        <v>44677</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13206,13 +13211,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13255,7 +13255,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 15659-2025</t>
+          <t>A 56116-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13269,10 +13269,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45748</v>
+        <v>44889</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13328,7 +13328,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 19781-2025</t>
+          <t>A 40896-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13342,10 +13342,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45771</v>
+        <v>44825</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>6.1</v>
+        <v>11.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13401,7 +13401,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 12967-2024</t>
+          <t>A 12329-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13415,10 +13415,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45385</v>
+        <v>45378</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13474,7 +13474,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 32797-2026</t>
+          <t>A 37371-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13488,10 +13488,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46241</v>
+        <v>45156</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13503,13 +13503,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13552,7 +13547,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 37371-2023</t>
+          <t>A 3074-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13566,10 +13561,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45156</v>
+        <v>44946</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13582,7 +13577,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13625,7 +13620,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 35969-2024</t>
+          <t>A 7730-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13639,10 +13634,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45533</v>
+        <v>44973</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13698,7 +13693,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 7921-2024</t>
+          <t>A 10494-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13712,10 +13707,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45350</v>
+        <v>44623</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13728,7 +13723,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.6</v>
+        <v>13.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13771,7 +13766,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 13515-2022</t>
+          <t>A 46364-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13785,10 +13780,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44648</v>
+        <v>45582</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13801,7 +13796,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13844,7 +13839,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 33782-2026</t>
+          <t>A 33546-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13858,10 +13853,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46251</v>
+        <v>44789</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13874,7 +13869,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13917,7 +13912,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 33830-2026</t>
+          <t>A 9821-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13931,10 +13926,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46251</v>
+        <v>44620</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13947,7 +13942,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>8.9</v>
+        <v>2.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13990,7 +13985,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 75-2025</t>
+          <t>A 38941-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14004,10 +13999,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45659</v>
+        <v>45163</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14020,7 +14015,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14063,7 +14058,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 30505-2026</t>
+          <t>A 49781-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14077,10 +14072,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46210</v>
+        <v>45597</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14093,7 +14088,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14136,7 +14131,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 3795-2024</t>
+          <t>A 27441-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14150,10 +14145,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45321</v>
+        <v>46189</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14166,7 +14161,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14209,7 +14204,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 19773-2025</t>
+          <t>A 61046-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14223,10 +14218,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45771</v>
+        <v>45645</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14239,7 +14234,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14282,7 +14277,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 61884-2024</t>
+          <t>A 27586-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14292,14 +14287,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45652</v>
+        <v>46190</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14312,7 +14307,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14355,7 +14350,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 45521-2022</t>
+          <t>A 3795-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14369,10 +14364,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44845</v>
+        <v>45321</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14385,7 +14380,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14428,7 +14423,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 8273-2024</t>
+          <t>A 32804-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14442,10 +14437,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45352</v>
+        <v>46241</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14457,8 +14452,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14501,7 +14501,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 5927-2022</t>
+          <t>A 32797-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14515,10 +14515,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44598</v>
+        <v>46241</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14530,8 +14530,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14574,7 +14579,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 23984-2024</t>
+          <t>A 42456-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14588,10 +14593,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45456</v>
+        <v>45565</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14604,7 +14609,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14647,7 +14652,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 24129-2024</t>
+          <t>A 30796-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14661,10 +14666,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45456</v>
+        <v>45497</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14677,7 +14682,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14720,7 +14725,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 2402-2024</t>
+          <t>A 33830-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14734,10 +14739,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45310</v>
+        <v>46251</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14750,7 +14755,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.3</v>
+        <v>8.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14793,7 +14798,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 3399-2024</t>
+          <t>A 33782-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14807,10 +14812,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45318</v>
+        <v>46251</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14823,7 +14828,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14866,7 +14871,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 10767-2024</t>
+          <t>A 30505-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14880,10 +14885,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45369</v>
+        <v>46210</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14896,7 +14901,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14939,7 +14944,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 24432-2022</t>
+          <t>A 16152-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14949,14 +14954,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44726</v>
+        <v>45406</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14969,7 +14974,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15012,7 +15017,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 36033-2026</t>
+          <t>A 47755-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15026,10 +15031,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46267</v>
+        <v>44854</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15042,7 +15047,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15085,7 +15090,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 16487-2023</t>
+          <t>A 10768-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15099,10 +15104,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45029</v>
+        <v>45369</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15115,7 +15120,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15158,7 +15163,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 64669-2023</t>
+          <t>A 62299-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15172,10 +15177,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45281</v>
+        <v>44923</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15188,7 +15193,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15231,7 +15236,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 55303-2022</t>
+          <t>A 11460-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15245,10 +15250,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44887</v>
+        <v>45372</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15261,7 +15266,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15304,7 +15309,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 12329-2024</t>
+          <t>A 55303-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15318,10 +15323,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45378</v>
+        <v>44887</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15334,7 +15339,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15377,7 +15382,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 4077-2025</t>
+          <t>A 36982-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15391,10 +15396,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45684</v>
+        <v>45539</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15407,7 +15412,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15450,7 +15455,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 62294-2022</t>
+          <t>A 855-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15464,10 +15469,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44923</v>
+        <v>44931</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15480,7 +15485,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15523,7 +15528,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 49-2026</t>
+          <t>A 21363-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15537,10 +15542,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46024</v>
+        <v>45063</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15553,7 +15558,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15596,7 +15601,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 12264-2024</t>
+          <t>A 61884-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15610,10 +15615,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45378</v>
+        <v>45652</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15626,7 +15631,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15669,7 +15674,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 12266-2024</t>
+          <t>A 36033-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15683,10 +15688,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45378</v>
+        <v>46267</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15699,7 +15704,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15742,7 +15747,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 44708-2023</t>
+          <t>A 19773-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15756,10 +15761,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45190</v>
+        <v>45771</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15772,7 +15777,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15815,7 +15820,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 20955-2025</t>
+          <t>A 3399-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15829,10 +15834,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45777</v>
+        <v>45318</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15845,7 +15850,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15888,7 +15893,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 20667-2026</t>
+          <t>A 44708-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15902,10 +15907,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46141</v>
+        <v>45190</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15918,7 +15923,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15961,7 +15966,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 22016-2025</t>
+          <t>A 25514-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15975,10 +15980,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45784</v>
+        <v>44732</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15991,7 +15996,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16034,7 +16039,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 37801-2024</t>
+          <t>A 12967-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16044,14 +16049,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45543</v>
+        <v>45385</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16064,7 +16069,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16107,7 +16112,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 24559-2025</t>
+          <t>A 24432-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16117,14 +16122,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45798</v>
+        <v>44726</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16137,7 +16142,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16180,7 +16185,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 11837-2025</t>
+          <t>A 37658-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16194,10 +16199,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45728</v>
+        <v>44810</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16210,7 +16215,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16253,7 +16258,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 15645-2024</t>
+          <t>A 15658-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16267,10 +16272,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45404</v>
+        <v>45748</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16283,7 +16288,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16326,7 +16331,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 45519-2023</t>
+          <t>A 66960-2021</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16340,10 +16345,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45194</v>
+        <v>44522</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16356,7 +16361,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16399,7 +16404,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 49062-2024</t>
+          <t>A 37305-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16413,10 +16418,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45594</v>
+        <v>44808</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16429,7 +16434,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.6</v>
+        <v>9.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16472,7 +16477,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 27201-2025</t>
+          <t>A 53193-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16486,10 +16491,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45812</v>
+        <v>45229</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16502,7 +16507,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16545,7 +16550,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 30486-2025</t>
+          <t>A 20955-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16559,10 +16564,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45829</v>
+        <v>45777</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16618,7 +16623,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 31464-2025</t>
+          <t>A 20667-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16632,10 +16637,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45833</v>
+        <v>46141</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16648,7 +16653,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16691,7 +16696,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 34671-2025</t>
+          <t>A 49-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16705,10 +16710,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45847</v>
+        <v>46024</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16720,13 +16725,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16769,7 +16769,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 13510-2022</t>
+          <t>A 22016-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16783,10 +16783,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44648</v>
+        <v>45784</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>17.6</v>
+        <v>2.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16842,7 +16842,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 10640-2025</t>
+          <t>A 37801-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -16852,14 +16852,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45721</v>
+        <v>45543</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -16915,7 +16915,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 36192-2025</t>
+          <t>A 11837-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -16929,10 +16929,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45867</v>
+        <v>45728</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17005,7 +17005,7 @@
         <v>46090</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>

--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE222"/>
+  <dimension ref="A1:AE221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45386</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44876</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44572</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44461</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44622</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44811</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>44686</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>44757</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>44693</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>44524</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44522</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44565</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44572</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 24127-2024</t>
+          <t>A 11123-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45456</v>
+        <v>45371</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23984-2024</t>
+          <t>A 10768-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45456</v>
+        <v>45369</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62294-2022</t>
+          <t>A 37658-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44923</v>
+        <v>44810</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12264-2024</t>
+          <t>A 10777-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45378</v>
+        <v>45369</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12266-2024</t>
+          <t>A 60103-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45378</v>
+        <v>44909</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 6354-2025</t>
+          <t>A 33546-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45699</v>
+        <v>44789</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>19.3</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3886-2025</t>
+          <t>A 3044-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45684</v>
+        <v>44582</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3457,13 +3457,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3506,7 +3501,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 65254-2021</t>
+          <t>A 64784-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3520,10 +3515,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44515</v>
+        <v>45282</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3536,7 +3531,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3579,7 +3574,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18612-2025</t>
+          <t>A 36982-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3593,10 +3588,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45763</v>
+        <v>45539</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3609,7 +3604,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3652,7 +3647,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 39611-2022</t>
+          <t>A 56116-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3666,10 +3661,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44818</v>
+        <v>44889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3681,13 +3676,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3730,7 +3720,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34909-2023</t>
+          <t>A 66960-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3744,10 +3734,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45141</v>
+        <v>44522</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3760,7 +3750,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3803,7 +3793,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15704-2023</t>
+          <t>A 11991-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3817,10 +3807,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45021</v>
+        <v>44635</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3833,7 +3823,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3876,7 +3866,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15181-2023</t>
+          <t>A 3074-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3890,10 +3880,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45016</v>
+        <v>44946</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3906,7 +3896,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3949,7 +3939,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 65116-2023</t>
+          <t>A 13119-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3959,14 +3949,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45287</v>
+        <v>45002</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3979,7 +3969,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4022,7 +4012,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 24129-2024</t>
+          <t>A 17126-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4036,10 +4026,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45456</v>
+        <v>44677</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4052,7 +4042,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4095,7 +4085,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 29300-2024</t>
+          <t>A 46533-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4109,10 +4099,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45483</v>
+        <v>45582</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4125,7 +4115,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4168,7 +4158,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16487-2023</t>
+          <t>A 53131-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4182,10 +4172,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45029</v>
+        <v>44876</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4198,7 +4188,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4241,7 +4231,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15645-2024</t>
+          <t>A 7783-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4255,10 +4245,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45404</v>
+        <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4271,7 +4261,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4314,7 +4304,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11123-2024</t>
+          <t>A 30486-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4328,10 +4318,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45371</v>
+        <v>45829</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4344,7 +4334,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4387,7 +4377,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24559-2025</t>
+          <t>A 11460-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4401,10 +4391,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45798</v>
+        <v>45372</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4417,7 +4407,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4460,7 +4450,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 60-2026</t>
+          <t>A 31464-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4474,10 +4464,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46024</v>
+        <v>45833</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4490,7 +4480,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4533,7 +4523,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34435-2024</t>
+          <t>A 62299-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4547,10 +4537,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45525</v>
+        <v>44923</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4563,7 +4553,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4606,7 +4596,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 55033-2023</t>
+          <t>A 49781-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4620,10 +4610,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45237</v>
+        <v>45597</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4636,7 +4626,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4679,7 +4669,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 53401-2022</t>
+          <t>A 34909-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4693,10 +4683,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44879</v>
+        <v>45141</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4709,7 +4699,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4752,7 +4742,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46533-2024</t>
+          <t>A 15648-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4766,10 +4756,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45582</v>
+        <v>45748</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4782,7 +4772,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4825,7 +4815,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 37562-2024</t>
+          <t>A 32527-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4839,10 +4829,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45541</v>
+        <v>45513</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4854,8 +4844,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4898,7 +4893,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 27652-2022</t>
+          <t>A 55033-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4912,10 +4907,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44743</v>
+        <v>45237</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4928,7 +4923,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>9.1</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4971,7 +4966,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 49062-2024</t>
+          <t>A 6354-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4985,10 +4980,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45594</v>
+        <v>45699</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5001,7 +4996,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>19.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5044,7 +5039,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45519-2023</t>
+          <t>A 32541-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5058,10 +5053,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45194</v>
+        <v>45513</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5073,8 +5068,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 15648-2025</t>
+          <t>A 21363-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45748</v>
+        <v>45063</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 27201-2025</t>
+          <t>A 34671-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45812</v>
+        <v>45847</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5219,8 +5219,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5263,7 +5268,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7628-2022</t>
+          <t>A 40896-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5277,10 +5282,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44607</v>
+        <v>44825</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5293,7 +5298,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>11.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5336,7 +5341,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 21979-2025</t>
+          <t>A 15658-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5350,10 +5355,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45784</v>
+        <v>45748</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5366,7 +5371,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5409,7 +5414,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 59879-2024</t>
+          <t>A 14211-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5423,10 +5428,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45640</v>
+        <v>46099</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5439,7 +5444,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5482,7 +5487,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1525-2026</t>
+          <t>A 15000-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5496,10 +5501,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46034</v>
+        <v>45015</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5512,7 +5517,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5555,7 +5560,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 11991-2022</t>
+          <t>A 65254-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5569,10 +5574,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44635</v>
+        <v>44515</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5585,7 +5590,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>6.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5628,7 +5633,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 4906-2024</t>
+          <t>A 46364-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5642,10 +5647,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45329</v>
+        <v>45582</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5658,7 +5663,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5701,7 +5706,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 30486-2025</t>
+          <t>A 6251-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5715,10 +5720,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45829</v>
+        <v>44965</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5731,7 +5736,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>15.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5774,7 +5779,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47902-2024</t>
+          <t>A 13510-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5788,10 +5793,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45589</v>
+        <v>44648</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5804,7 +5809,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>17.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5847,7 +5852,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31464-2025</t>
+          <t>A 10640-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5861,10 +5866,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45833</v>
+        <v>45721</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5877,7 +5882,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5920,7 +5925,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 58330-2022</t>
+          <t>A 21979-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5934,10 +5939,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44901</v>
+        <v>45784</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5950,7 +5955,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5993,7 +5998,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13119-2023</t>
+          <t>A 15592-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6007,10 +6012,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45002</v>
+        <v>46106</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6023,7 +6028,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>8.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6066,7 +6071,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 68454-2021</t>
+          <t>A 24127-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6080,10 +6085,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44529</v>
+        <v>45456</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6096,7 +6101,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6139,7 +6144,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 57259-2022</t>
+          <t>A 36192-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6153,10 +6158,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44895</v>
+        <v>45867</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6169,7 +6174,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6212,7 +6217,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 10777-2024</t>
+          <t>A 16030-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6226,10 +6231,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45369</v>
+        <v>46108</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6242,7 +6247,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>15.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6285,7 +6290,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34671-2025</t>
+          <t>A 23451-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6299,10 +6304,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45847</v>
+        <v>45076</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6316,11 +6321,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6363,7 +6368,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 10640-2025</t>
+          <t>A 3886-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6377,10 +6382,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45721</v>
+        <v>45684</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6392,8 +6397,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6436,7 +6446,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13510-2022</t>
+          <t>A 17485-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6446,14 +6456,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44648</v>
+        <v>46120</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6466,7 +6476,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>17.6</v>
+        <v>3.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6509,7 +6519,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 3256-2026</t>
+          <t>A 41554-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6523,10 +6533,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46041</v>
+        <v>45560</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6539,7 +6549,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8.1</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6582,7 +6592,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36192-2025</t>
+          <t>A 61046-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6596,10 +6606,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45867</v>
+        <v>45645</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6612,7 +6622,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6655,7 +6665,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 48788-2025</t>
+          <t>A 18840-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6669,10 +6679,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45937</v>
+        <v>46129</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6685,7 +6695,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6728,7 +6738,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 48790-2025</t>
+          <t>A 19373-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6742,10 +6752,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45937</v>
+        <v>46133</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6801,7 +6811,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 47708-2025</t>
+          <t>A 20009-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6815,10 +6825,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45931</v>
+        <v>46136</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6831,7 +6841,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6874,7 +6884,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48787-2025</t>
+          <t>A 4307-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6888,10 +6898,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45937</v>
+        <v>45685</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6904,7 +6914,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6947,7 +6957,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 48791-2025</t>
+          <t>A 53193-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6961,10 +6971,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45937</v>
+        <v>45229</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6977,7 +6987,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7020,7 +7030,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50209-2025</t>
+          <t>A 39611-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7034,10 +7044,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45943</v>
+        <v>44818</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7049,8 +7059,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7093,7 +7108,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 50337-2025</t>
+          <t>A 29300-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7107,10 +7122,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45944</v>
+        <v>45483</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7123,7 +7138,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7166,7 +7181,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2263-2024</t>
+          <t>A 3272-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7180,10 +7195,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45310</v>
+        <v>45679</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7195,13 +7210,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7244,7 +7254,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 7655-2026</t>
+          <t>A 7628-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7258,10 +7268,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46062</v>
+        <v>44607</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7274,7 +7284,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7317,7 +7327,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 53227-2021</t>
+          <t>A 30773-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7331,10 +7341,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44468</v>
+        <v>45496</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7347,7 +7357,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7390,7 +7400,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 54526-2025</t>
+          <t>A 53426-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7404,10 +7414,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45965</v>
+        <v>44879</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7420,7 +7430,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.5</v>
+        <v>13.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7463,7 +7473,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 7659-2026</t>
+          <t>A 62266-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7477,10 +7487,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46062</v>
+        <v>44923</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7493,7 +7503,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7536,7 +7546,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8273-2024</t>
+          <t>A 39116-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7550,10 +7560,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45352</v>
+        <v>44817</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7566,7 +7576,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7609,7 +7619,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 52688-2024</t>
+          <t>A 20500-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7623,10 +7633,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45610</v>
+        <v>46140</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7639,7 +7649,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7682,7 +7692,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46529-2024</t>
+          <t>A 57918-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7696,10 +7706,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45582</v>
+        <v>44900</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7712,7 +7722,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>11.7</v>
+        <v>3.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7755,7 +7765,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56523-2025</t>
+          <t>A 20501-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7769,10 +7779,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45975</v>
+        <v>46140</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7785,7 +7795,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7828,7 +7838,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 57262-2025</t>
+          <t>A 41893-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7842,10 +7852,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45979</v>
+        <v>44830</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7857,8 +7867,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7901,7 +7916,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 131-2024</t>
+          <t>A 20152-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7915,10 +7930,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45294</v>
+        <v>46138</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7931,7 +7946,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7.5</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7974,7 +7989,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 75-2025</t>
+          <t>A 53227-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7988,10 +8003,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45659</v>
+        <v>44468</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8004,7 +8019,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.4</v>
+        <v>2.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8047,7 +8062,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 57890-2025</t>
+          <t>A 18612-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8061,10 +8076,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45981</v>
+        <v>45763</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8077,7 +8092,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8120,7 +8135,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 57886-2025</t>
+          <t>A 28224-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8134,10 +8149,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45981</v>
+        <v>45099</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8150,7 +8165,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8193,7 +8208,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 57891-2025</t>
+          <t>A 7730-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8207,10 +8222,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45981</v>
+        <v>44973</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8223,7 +8238,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8266,7 +8281,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 68400-2021</t>
+          <t>A 21929-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8280,10 +8295,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44529</v>
+        <v>46150</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8296,7 +8311,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8339,7 +8354,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 54087-2021</t>
+          <t>A 22207-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8353,10 +8368,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44470</v>
+        <v>46153</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8368,13 +8383,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8417,7 +8427,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 35465-2022</t>
+          <t>A 22620-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8431,10 +8441,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44798</v>
+        <v>46155</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8447,7 +8457,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8490,7 +8500,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 59252-2025</t>
+          <t>A 47708-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8504,10 +8514,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45988</v>
+        <v>45931</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8520,7 +8530,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8563,7 +8573,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 39116-2022</t>
+          <t>A 68454-2021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8577,10 +8587,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44817</v>
+        <v>44529</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8593,7 +8603,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8636,7 +8646,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60505-2025</t>
+          <t>A 48790-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8650,10 +8660,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45995</v>
+        <v>45937</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8666,7 +8676,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8709,7 +8719,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61535-2025</t>
+          <t>A 48791-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8723,10 +8733,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46001</v>
+        <v>45937</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8739,7 +8749,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8782,7 +8792,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61539-2025</t>
+          <t>A 48787-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8796,10 +8806,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46001</v>
+        <v>45937</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8812,7 +8822,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8855,7 +8865,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 62266-2022</t>
+          <t>A 48788-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8869,10 +8879,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44923</v>
+        <v>45937</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8885,7 +8895,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8928,7 +8938,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 32527-2024</t>
+          <t>A 7781-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8942,10 +8952,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45513</v>
+        <v>44973</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8957,13 +8967,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>8.699999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9006,7 +9011,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 32541-2024</t>
+          <t>A 73158-2021</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9020,10 +9025,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45513</v>
+        <v>44550</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9035,13 +9040,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9084,7 +9084,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 10767-2024</t>
+          <t>A 50337-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9098,10 +9098,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45369</v>
+        <v>45944</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9157,7 +9157,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 60103-2022</t>
+          <t>A 50209-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9171,10 +9171,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44909</v>
+        <v>45943</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9230,7 +9230,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 63884-2025</t>
+          <t>A 38941-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9244,10 +9244,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46020</v>
+        <v>45163</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9303,7 +9303,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 14211-2026</t>
+          <t>A 16473-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9317,10 +9317,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46099</v>
+        <v>45029</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9376,7 +9376,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 13515-2022</t>
+          <t>A 16475-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44648</v>
+        <v>45029</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9449,7 +9449,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 4077-2025</t>
+          <t>A 34435-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9463,10 +9463,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45684</v>
+        <v>45525</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9522,7 +9522,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 15592-2026</t>
+          <t>A 10858-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9536,10 +9536,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46106</v>
+        <v>46078</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9595,7 +9595,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 2402-2024</t>
+          <t>A 42456-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9609,10 +9609,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45310</v>
+        <v>45565</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9668,7 +9668,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 73158-2021</t>
+          <t>A 19781-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9682,10 +9682,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44550</v>
+        <v>45771</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9741,7 +9741,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 13883-2022</t>
+          <t>A 12967-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9755,10 +9755,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44650</v>
+        <v>45385</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.1</v>
+        <v>1.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9814,7 +9814,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 16030-2026</t>
+          <t>A 37371-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46108</v>
+        <v>45156</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>15.8</v>
+        <v>2.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9887,7 +9887,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 17485-2026</t>
+          <t>A 35969-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9897,14 +9897,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46120</v>
+        <v>45533</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9960,7 +9960,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 18840-2026</t>
+          <t>A 7921-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9974,10 +9974,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46129</v>
+        <v>45350</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10033,7 +10033,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 59625-2023</t>
+          <t>A 27441-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45254</v>
+        <v>46189</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 15659-2025</t>
+          <t>A 27586-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10116,14 +10116,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45748</v>
+        <v>46190</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 16154-2024</t>
+          <t>A 13515-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10193,10 +10193,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45406</v>
+        <v>44648</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10252,7 +10252,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16155-2024</t>
+          <t>A 54526-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10266,10 +10266,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45406</v>
+        <v>45965</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10325,7 +10325,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 19373-2026</t>
+          <t>A 75-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10339,10 +10339,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46133</v>
+        <v>45659</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10398,7 +10398,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 20009-2026</t>
+          <t>A 3795-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10412,10 +10412,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46136</v>
+        <v>45321</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10471,7 +10471,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 35969-2024</t>
+          <t>A 32804-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45533</v>
+        <v>46241</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10500,8 +10500,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10544,7 +10549,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 41554-2024</t>
+          <t>A 56523-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10558,10 +10563,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45560</v>
+        <v>45975</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10574,7 +10579,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10617,7 +10622,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 3272-2025</t>
+          <t>A 32797-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10631,10 +10636,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45679</v>
+        <v>46241</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10646,8 +10651,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10690,7 +10700,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 45983-2024</t>
+          <t>A 57262-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10704,10 +10714,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45580</v>
+        <v>45979</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10720,7 +10730,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10763,7 +10773,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 32826-2022</t>
+          <t>A 61884-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10777,10 +10787,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44784</v>
+        <v>45652</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10793,7 +10803,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10836,7 +10846,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 53426-2022</t>
+          <t>A 57890-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10850,10 +10860,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44879</v>
+        <v>45981</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10866,7 +10876,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>13.2</v>
+        <v>2.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10909,7 +10919,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 13220-2022</t>
+          <t>A 57886-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10923,10 +10933,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44644</v>
+        <v>45981</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10939,7 +10949,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.3</v>
+        <v>8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10982,7 +10992,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 19447-2025</t>
+          <t>A 57891-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10996,10 +11006,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45770</v>
+        <v>45981</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11012,7 +11022,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11055,7 +11065,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 64669-2023</t>
+          <t>A 45521-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11069,10 +11079,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45281</v>
+        <v>44845</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11085,7 +11095,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11128,7 +11138,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 20152-2026</t>
+          <t>A 5927-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11142,10 +11152,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46138</v>
+        <v>44598</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11158,7 +11168,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11201,7 +11211,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 16473-2023</t>
+          <t>A 23984-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11215,10 +11225,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45029</v>
+        <v>45456</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11231,7 +11241,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11274,7 +11284,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 16475-2023</t>
+          <t>A 24129-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11288,10 +11298,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45029</v>
+        <v>45456</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11304,7 +11314,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11347,7 +11357,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 53131-2022</t>
+          <t>A 33782-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11361,10 +11371,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44876</v>
+        <v>46251</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11377,7 +11387,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11420,7 +11430,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 30773-2024</t>
+          <t>A 33830-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11434,10 +11444,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45496</v>
+        <v>46251</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11450,7 +11460,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.9</v>
+        <v>8.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11493,7 +11503,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 28224-2023</t>
+          <t>A 30505-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11507,10 +11517,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45099</v>
+        <v>46210</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11523,7 +11533,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11566,7 +11576,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 4307-2025</t>
+          <t>A 59252-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11580,10 +11590,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45685</v>
+        <v>45988</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11596,7 +11606,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11639,7 +11649,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 64784-2023</t>
+          <t>A 35465-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11653,10 +11663,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45282</v>
+        <v>44798</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11669,7 +11679,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11712,7 +11722,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 20500-2026</t>
+          <t>A 65116-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11722,14 +11732,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46140</v>
+        <v>45287</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11742,7 +11752,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11785,7 +11795,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 3044-2022</t>
+          <t>A 59625-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11799,10 +11809,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44582</v>
+        <v>45254</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11815,7 +11825,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11858,7 +11868,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 15000-2023</t>
+          <t>A 60505-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11872,10 +11882,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45015</v>
+        <v>45995</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11888,7 +11898,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11931,7 +11941,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 20501-2026</t>
+          <t>A 19447-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11945,10 +11955,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46140</v>
+        <v>45770</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11961,7 +11971,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12004,7 +12014,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 6251-2023</t>
+          <t>A 131-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12018,10 +12028,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44965</v>
+        <v>45294</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12034,7 +12044,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>15.4</v>
+        <v>7.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12077,7 +12087,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 19781-2025</t>
+          <t>A 54087-2021</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12091,10 +12101,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45771</v>
+        <v>44470</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12106,8 +12116,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>6.1</v>
+        <v>2.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12150,7 +12165,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 22207-2026</t>
+          <t>A 61535-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12164,10 +12179,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46153</v>
+        <v>46001</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12180,7 +12195,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12223,7 +12238,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 21929-2026</t>
+          <t>A 61539-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12237,10 +12252,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46150</v>
+        <v>46001</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12253,7 +12268,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12296,7 +12311,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 23451-2023</t>
+          <t>A 36033-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12310,10 +12325,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45076</v>
+        <v>46267</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12325,13 +12340,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12374,7 +12384,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 60498-2024</t>
+          <t>A 27652-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12388,10 +12398,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45643</v>
+        <v>44743</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12404,7 +12414,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>9.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12447,7 +12457,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 5927-2022</t>
+          <t>A 45983-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12461,10 +12471,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44598</v>
+        <v>45580</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12477,7 +12487,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12520,7 +12530,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 22620-2026</t>
+          <t>A 5242-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12534,10 +12544,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46155</v>
+        <v>44594</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12550,7 +12560,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12593,7 +12603,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 41893-2022</t>
+          <t>A 46529-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12607,10 +12617,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44830</v>
+        <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12622,13 +12632,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>2.5</v>
+        <v>11.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12671,7 +12676,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 7783-2023</t>
+          <t>A 16154-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12685,10 +12690,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44973</v>
+        <v>45406</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12701,7 +12706,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12744,7 +12749,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 5242-2022</t>
+          <t>A 16155-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12758,10 +12763,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44594</v>
+        <v>45406</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12774,7 +12779,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>8.800000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12817,7 +12822,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 57918-2022</t>
+          <t>A 57259-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12831,10 +12836,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44900</v>
+        <v>44895</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12847,7 +12852,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12890,7 +12895,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 7781-2023</t>
+          <t>A 59879-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12904,10 +12909,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44973</v>
+        <v>45640</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12920,7 +12925,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12963,7 +12968,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 7921-2024</t>
+          <t>A 32826-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12977,10 +12982,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45350</v>
+        <v>44784</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12993,7 +12998,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13036,7 +13041,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 45521-2022</t>
+          <t>A 58330-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13050,10 +13055,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44845</v>
+        <v>44901</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13066,7 +13071,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13109,7 +13114,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 10858-2026</t>
+          <t>A 15704-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13123,10 +13128,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46078</v>
+        <v>45021</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13139,7 +13144,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13182,7 +13187,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 17126-2022</t>
+          <t>A 30796-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13196,10 +13201,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44677</v>
+        <v>45497</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13212,7 +13217,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13255,7 +13260,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 56116-2022</t>
+          <t>A 16152-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13269,10 +13274,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44889</v>
+        <v>45406</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13285,7 +13290,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13328,7 +13333,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 40896-2022</t>
+          <t>A 4906-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13342,10 +13347,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44825</v>
+        <v>45329</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13358,7 +13363,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>11.3</v>
+        <v>1.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13401,7 +13406,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 12329-2024</t>
+          <t>A 63884-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13415,10 +13420,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45378</v>
+        <v>46020</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13431,7 +13436,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13474,7 +13479,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 37371-2023</t>
+          <t>A 13883-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13488,10 +13493,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45156</v>
+        <v>44650</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13504,7 +13509,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13547,7 +13552,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 3074-2023</t>
+          <t>A 53401-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13561,10 +13566,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44946</v>
+        <v>44879</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13577,7 +13582,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13620,7 +13625,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 7730-2023</t>
+          <t>A 15181-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13634,10 +13639,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44973</v>
+        <v>45016</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13650,7 +13655,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13693,7 +13698,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 10494-2022</t>
+          <t>A 60-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13707,10 +13712,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44623</v>
+        <v>46024</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13723,7 +13728,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>13.3</v>
+        <v>3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13766,7 +13771,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 46364-2024</t>
+          <t>A 20667-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13780,10 +13785,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45582</v>
+        <v>46141</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13796,7 +13801,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13839,7 +13844,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 33546-2022</t>
+          <t>A 855-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13853,10 +13858,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44789</v>
+        <v>44931</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13869,7 +13874,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13912,7 +13917,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 9821-2022</t>
+          <t>A 47755-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13926,10 +13931,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44620</v>
+        <v>44854</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13942,7 +13947,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13985,7 +13990,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 38941-2023</t>
+          <t>A 9821-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13999,10 +14004,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45163</v>
+        <v>44620</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14015,7 +14020,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14058,7 +14063,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 49781-2024</t>
+          <t>A 13220-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14072,10 +14077,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45597</v>
+        <v>44644</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14088,7 +14093,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14131,7 +14136,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 27441-2026</t>
+          <t>A 68400-2021</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14145,10 +14150,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46189</v>
+        <v>44529</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14161,7 +14166,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14204,7 +14209,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 61046-2024</t>
+          <t>A 1525-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14218,10 +14223,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45645</v>
+        <v>46034</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14234,7 +14239,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14277,7 +14282,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 27586-2026</t>
+          <t>A 25514-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14287,14 +14292,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46190</v>
+        <v>44732</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14307,7 +14312,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14350,7 +14355,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 3795-2024</t>
+          <t>A 10494-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14364,10 +14369,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45321</v>
+        <v>44623</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14380,7 +14385,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.4</v>
+        <v>13.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14423,7 +14428,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 32804-2026</t>
+          <t>A 3256-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14437,10 +14442,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46241</v>
+        <v>46041</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14452,13 +14457,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>1.4</v>
+        <v>8.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14501,7 +14501,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 32797-2026</t>
+          <t>A 52688-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14515,10 +14515,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46241</v>
+        <v>45610</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14530,13 +14530,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14579,7 +14574,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 42456-2024</t>
+          <t>A 47902-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14593,10 +14588,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45565</v>
+        <v>45589</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14609,7 +14604,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14652,7 +14647,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 30796-2024</t>
+          <t>A 2263-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14666,10 +14661,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45497</v>
+        <v>45310</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14681,8 +14676,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14725,7 +14725,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 33830-2026</t>
+          <t>A 37305-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14739,10 +14739,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46251</v>
+        <v>44808</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>8.9</v>
+        <v>9.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14798,7 +14798,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 33782-2026</t>
+          <t>A 60498-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14812,10 +14812,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46251</v>
+        <v>45643</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14871,7 +14871,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 30505-2026</t>
+          <t>A 7655-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14885,10 +14885,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46210</v>
+        <v>46062</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14944,7 +14944,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 16152-2024</t>
+          <t>A 7659-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14958,10 +14958,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45406</v>
+        <v>46062</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15017,7 +15017,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 47755-2022</t>
+          <t>A 37562-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44854</v>
+        <v>45541</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15090,7 +15090,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 10768-2024</t>
+          <t>A 15659-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15104,10 +15104,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45369</v>
+        <v>45748</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15163,7 +15163,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 62299-2022</t>
+          <t>A 19773-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15177,10 +15177,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44923</v>
+        <v>45771</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15236,7 +15236,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 11460-2024</t>
+          <t>A 8273-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15250,10 +15250,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45372</v>
+        <v>45352</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 55303-2022</t>
+          <t>A 2402-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15323,10 +15323,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44887</v>
+        <v>45310</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15382,7 +15382,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 36982-2024</t>
+          <t>A 3399-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15396,10 +15396,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45539</v>
+        <v>45318</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15455,7 +15455,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 855-2023</t>
+          <t>A 10767-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15469,10 +15469,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44931</v>
+        <v>45369</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 21363-2023</t>
+          <t>A 24432-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15538,14 +15538,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45063</v>
+        <v>44726</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15601,7 +15601,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 61884-2024</t>
+          <t>A 16487-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15615,10 +15615,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45652</v>
+        <v>45029</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15674,7 +15674,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 36033-2026</t>
+          <t>A 64669-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15688,10 +15688,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46267</v>
+        <v>45281</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15747,7 +15747,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 19773-2025</t>
+          <t>A 55303-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15761,10 +15761,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45771</v>
+        <v>44887</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15820,7 +15820,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 3399-2024</t>
+          <t>A 12329-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15834,10 +15834,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45318</v>
+        <v>45378</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15893,7 +15893,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 44708-2023</t>
+          <t>A 4077-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15907,10 +15907,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45190</v>
+        <v>45684</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15966,7 +15966,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 25514-2022</t>
+          <t>A 62294-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15980,10 +15980,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44732</v>
+        <v>44923</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16039,7 +16039,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 12967-2024</t>
+          <t>A 12264-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16053,10 +16053,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45385</v>
+        <v>45378</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16112,7 +16112,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 24432-2022</t>
+          <t>A 12266-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16122,14 +16122,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44726</v>
+        <v>45378</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16185,7 +16185,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 37658-2022</t>
+          <t>A 44708-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16199,10 +16199,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44810</v>
+        <v>45190</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16258,7 +16258,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 15658-2025</t>
+          <t>A 20955-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16272,10 +16272,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45748</v>
+        <v>45777</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 66960-2021</t>
+          <t>A 22016-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16345,10 +16345,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44522</v>
+        <v>45784</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16404,7 +16404,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 37305-2022</t>
+          <t>A 37801-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16414,14 +16414,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44808</v>
+        <v>45543</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>9.9</v>
+        <v>2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16477,7 +16477,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 53193-2023</t>
+          <t>A 24559-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16491,10 +16491,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45229</v>
+        <v>45798</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16550,7 +16550,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 20955-2025</t>
+          <t>A 11837-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16564,10 +16564,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45777</v>
+        <v>45728</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16623,7 +16623,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 20667-2026</t>
+          <t>A 15645-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16637,10 +16637,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46141</v>
+        <v>45404</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 49-2026</t>
+          <t>A 45519-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16710,10 +16710,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46024</v>
+        <v>45194</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16769,7 +16769,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 22016-2025</t>
+          <t>A 49062-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16783,10 +16783,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45784</v>
+        <v>45594</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16842,7 +16842,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 37801-2024</t>
+          <t>A 27201-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -16852,14 +16852,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45543</v>
+        <v>45812</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -16912,27 +16912,27 @@
       </c>
       <c r="V220" s="2" t="inlineStr"/>
     </row>
-    <row r="221" ht="15" customHeight="1">
+    <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 11837-2025</t>
+          <t>S 643-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45728</v>
+        <v>46090</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -16984,79 +16984,6 @@
         <v>0</v>
       </c>
       <c r="V221" s="2" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>S 643-2026</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D222" s="1" t="n">
-        <v>46090</v>
-      </c>
-      <c r="E222" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="I222" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J222" t="n">
-        <v>0</v>
-      </c>
-      <c r="K222" t="n">
-        <v>0</v>
-      </c>
-      <c r="L222" t="n">
-        <v>0</v>
-      </c>
-      <c r="M222" t="n">
-        <v>0</v>
-      </c>
-      <c r="N222" t="n">
-        <v>0</v>
-      </c>
-      <c r="O222" t="n">
-        <v>0</v>
-      </c>
-      <c r="P222" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0</v>
-      </c>
-      <c r="S222" t="n">
-        <v>0</v>
-      </c>
-      <c r="T222" t="n">
-        <v>0</v>
-      </c>
-      <c r="U222" t="n">
-        <v>0</v>
-      </c>
-      <c r="V222" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE221"/>
+  <dimension ref="A1:AE222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 15069-2026</t>
+          <t>A 13131-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46104</v>
+        <v>45386</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -835,20 +835,25 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -863,7 +868,7 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -876,150 +881,145 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Svinrot
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/artfynd/A 13131-2024 artfynd.xlsx", "A 13131-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor/A 13131-2024 karta.png", "A 13131-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor_geotiff/A 13131-2024 georefererad karta.tif", "A 13131-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomål/A 13131-2024 FSC-klagomål.docx", "A 13131-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomålsmail/A 13131-2024 FSC-klagomål mail.docx", "A 13131-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsyn/A 13131-2024 tillsynsbegäran.docx", "A 13131-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsynsmail/A 13131-2024 tillsynsbegäran mail.docx", "A 13131-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 15069-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TROLLHÄTTAN</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Kortskaftad parasitspik
 Rostfläck</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/artfynd/A 15069-2026 artfynd.xlsx", "A 15069-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor/A 15069-2026 karta.png", "A 15069-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor_geotiff/A 15069-2026 georefererad karta.tif", "A 15069-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomål/A 15069-2026 FSC-klagomål.docx", "A 15069-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomålsmail/A 15069-2026 FSC-klagomål mail.docx", "A 15069-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsyn/A 15069-2026 tillsynsbegäran.docx", "A 15069-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsynsmail/A 15069-2026 tillsynsbegäran mail.docx", "A 15069-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 13131-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45386</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Svinrot
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/artfynd/A 13131-2024 artfynd.xlsx", "A 13131-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor/A 13131-2024 karta.png", "A 13131-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor_geotiff/A 13131-2024 georefererad karta.tif", "A 13131-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomål/A 13131-2024 FSC-klagomål.docx", "A 13131-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomålsmail/A 13131-2024 FSC-klagomål mail.docx", "A 13131-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsyn/A 13131-2024 tillsynsbegäran.docx", "A 13131-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsynsmail/A 13131-2024 tillsynsbegäran mail.docx", "A 13131-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44876</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44572</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44461</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44622</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44811</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>44686</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>44757</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>44693</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>44524</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44522</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44565</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44572</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11123-2024</t>
+          <t>A 24127-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45371</v>
+        <v>45456</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>8.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10768-2024</t>
+          <t>A 23984-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45369</v>
+        <v>45456</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37658-2022</t>
+          <t>A 62294-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44810</v>
+        <v>44923</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10777-2024</t>
+          <t>A 12264-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45369</v>
+        <v>45378</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60103-2022</t>
+          <t>A 12266-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44909</v>
+        <v>45378</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33546-2022</t>
+          <t>A 6354-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44789</v>
+        <v>45699</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>19.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3044-2022</t>
+          <t>A 3886-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44582</v>
+        <v>45684</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3457,8 +3457,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3501,7 +3506,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 64784-2023</t>
+          <t>A 39611-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3515,10 +3520,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45282</v>
+        <v>44818</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3530,8 +3535,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3574,7 +3584,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 36982-2024</t>
+          <t>A 18612-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3588,10 +3598,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45539</v>
+        <v>45763</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3604,7 +3614,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3647,7 +3657,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 56116-2022</t>
+          <t>A 65254-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3661,10 +3671,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44889</v>
+        <v>44515</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3677,7 +3687,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3720,7 +3730,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 66960-2021</t>
+          <t>A 34909-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3734,10 +3744,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44522</v>
+        <v>45141</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3750,7 +3760,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3793,7 +3803,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 11991-2022</t>
+          <t>A 15704-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3807,10 +3817,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44635</v>
+        <v>45021</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3823,7 +3833,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3866,7 +3876,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3074-2023</t>
+          <t>A 15181-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3880,10 +3890,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44946</v>
+        <v>45016</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3896,7 +3906,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3939,7 +3949,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13119-2023</t>
+          <t>A 24129-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3953,10 +3963,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45002</v>
+        <v>45456</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3969,7 +3979,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4012,7 +4022,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 17126-2022</t>
+          <t>A 65116-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4022,14 +4032,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44677</v>
+        <v>45287</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4042,7 +4052,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.4</v>
+        <v>0.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4085,7 +4095,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46533-2024</t>
+          <t>A 29300-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4099,10 +4109,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45582</v>
+        <v>45483</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4115,7 +4125,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4158,7 +4168,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 53131-2022</t>
+          <t>A 16487-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4172,10 +4182,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44876</v>
+        <v>45029</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4188,7 +4198,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4231,7 +4241,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7783-2023</t>
+          <t>A 11123-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4245,10 +4255,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44973</v>
+        <v>45371</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4261,7 +4271,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4304,7 +4314,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30486-2025</t>
+          <t>A 55033-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4318,10 +4328,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45829</v>
+        <v>45237</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4334,7 +4344,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4377,7 +4387,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11460-2024</t>
+          <t>A 53401-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4391,10 +4401,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45372</v>
+        <v>44879</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4407,7 +4417,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4450,7 +4460,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 31464-2025</t>
+          <t>A 46533-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4464,10 +4474,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45833</v>
+        <v>45582</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4480,7 +4490,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4523,7 +4533,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62299-2022</t>
+          <t>A 34435-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4537,10 +4547,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44923</v>
+        <v>45525</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4553,7 +4563,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4596,7 +4606,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 49781-2024</t>
+          <t>A 37562-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4610,10 +4620,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45597</v>
+        <v>45541</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4626,7 +4636,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4669,7 +4679,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 34909-2023</t>
+          <t>A 27652-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4683,10 +4693,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45141</v>
+        <v>44743</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4699,7 +4709,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>9.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4742,7 +4752,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 15648-2025</t>
+          <t>A 7628-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4756,10 +4766,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45748</v>
+        <v>44607</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4772,7 +4782,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4815,7 +4825,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32527-2024</t>
+          <t>A 59879-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4829,10 +4839,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45513</v>
+        <v>45640</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4844,13 +4854,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>8.699999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4893,7 +4898,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 55033-2023</t>
+          <t>A 11991-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4907,10 +4912,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45237</v>
+        <v>44635</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4923,7 +4928,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4966,7 +4971,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 6354-2025</t>
+          <t>A 58330-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4980,10 +4985,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45699</v>
+        <v>44901</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4996,7 +5001,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>19.3</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5039,7 +5044,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32541-2024</t>
+          <t>A 4906-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5053,10 +5058,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45513</v>
+        <v>45329</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5068,13 +5073,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 21363-2023</t>
+          <t>A 13119-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45063</v>
+        <v>45002</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 34671-2025</t>
+          <t>A 47902-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45847</v>
+        <v>45589</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5219,13 +5219,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5268,7 +5263,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 40896-2022</t>
+          <t>A 68454-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5282,10 +5277,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44825</v>
+        <v>44529</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5298,7 +5293,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>11.3</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5341,7 +5336,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15658-2025</t>
+          <t>A 57259-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5355,10 +5350,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45748</v>
+        <v>44895</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5371,7 +5366,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5414,7 +5409,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14211-2026</t>
+          <t>A 10777-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5428,10 +5423,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46099</v>
+        <v>45369</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5444,7 +5439,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5487,7 +5482,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15000-2023</t>
+          <t>A 2263-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5501,10 +5496,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45015</v>
+        <v>45310</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5516,8 +5511,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 65254-2021</t>
+          <t>A 53227-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44515</v>
+        <v>44468</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.4</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 46364-2024</t>
+          <t>A 8273-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45582</v>
+        <v>45352</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6251-2023</t>
+          <t>A 52688-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44965</v>
+        <v>45610</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>15.4</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13510-2022</t>
+          <t>A 46529-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44648</v>
+        <v>45582</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>17.6</v>
+        <v>11.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 10640-2025</t>
+          <t>A 131-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45721</v>
+        <v>45294</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.1</v>
+        <v>7.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 21979-2025</t>
+          <t>A 75-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45784</v>
+        <v>45659</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15592-2026</t>
+          <t>A 3272-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46106</v>
+        <v>45679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>8.4</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24127-2024</t>
+          <t>A 68400-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45456</v>
+        <v>44529</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36192-2025</t>
+          <t>A 15648-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45867</v>
+        <v>45748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16030-2026</t>
+          <t>A 54087-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46108</v>
+        <v>44470</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6246,8 +6246,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>15.8</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6290,7 +6295,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23451-2023</t>
+          <t>A 35465-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6304,10 +6309,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45076</v>
+        <v>44798</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6319,13 +6324,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6368,7 +6368,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3886-2025</t>
+          <t>A 21979-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45684</v>
+        <v>45784</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6397,13 +6397,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6446,7 +6441,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 17485-2026</t>
+          <t>A 39116-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6456,14 +6451,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46120</v>
+        <v>44817</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6476,7 +6471,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6519,7 +6514,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41554-2024</t>
+          <t>A 20152-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6533,10 +6528,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45560</v>
+        <v>46138</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6549,7 +6544,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6592,7 +6587,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61046-2024</t>
+          <t>A 62266-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6606,10 +6601,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45645</v>
+        <v>44923</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6622,7 +6617,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6665,7 +6660,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18840-2026</t>
+          <t>A 30773-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6679,10 +6674,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46129</v>
+        <v>45496</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6695,7 +6690,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6738,7 +6733,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19373-2026</t>
+          <t>A 28224-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6752,10 +6747,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46133</v>
+        <v>45099</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6768,7 +6763,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6811,7 +6806,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20009-2026</t>
+          <t>A 4307-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6825,10 +6820,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46136</v>
+        <v>45685</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6841,7 +6836,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6884,7 +6879,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4307-2025</t>
+          <t>A 10767-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6898,10 +6893,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45685</v>
+        <v>45369</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6914,7 +6909,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6957,7 +6952,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 53193-2023</t>
+          <t>A 20500-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6971,10 +6966,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45229</v>
+        <v>46140</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6987,7 +6982,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7030,7 +7025,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 39611-2022</t>
+          <t>A 60103-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7044,10 +7039,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44818</v>
+        <v>44909</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7059,13 +7054,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7108,7 +7098,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 29300-2024</t>
+          <t>A 20501-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7122,10 +7112,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45483</v>
+        <v>46140</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7138,7 +7128,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7181,7 +7171,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3272-2025</t>
+          <t>A 13515-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7195,10 +7185,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45679</v>
+        <v>44648</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7211,7 +7201,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7254,7 +7244,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 7628-2022</t>
+          <t>A 4077-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7268,10 +7258,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44607</v>
+        <v>45684</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7284,7 +7274,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7327,7 +7317,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 30773-2024</t>
+          <t>A 2402-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7341,10 +7331,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45496</v>
+        <v>45310</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7357,7 +7347,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7400,7 +7390,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 53426-2022</t>
+          <t>A 73158-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7414,10 +7404,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44879</v>
+        <v>44550</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7430,7 +7420,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>13.2</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7473,7 +7463,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 62266-2022</t>
+          <t>A 13883-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7487,10 +7477,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44923</v>
+        <v>44650</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7503,7 +7493,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>6.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7546,7 +7536,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 39116-2022</t>
+          <t>A 48788-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7560,10 +7550,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44817</v>
+        <v>45937</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7576,7 +7566,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7619,7 +7609,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 20500-2026</t>
+          <t>A 48790-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7633,10 +7623,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46140</v>
+        <v>45937</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7649,7 +7639,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7692,7 +7682,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 57918-2022</t>
+          <t>A 47708-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7706,10 +7696,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44900</v>
+        <v>45931</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7722,7 +7712,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7765,7 +7755,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 20501-2026</t>
+          <t>A 48787-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7779,10 +7769,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46140</v>
+        <v>45937</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7795,7 +7785,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7838,7 +7828,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 41893-2022</t>
+          <t>A 48791-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7852,10 +7842,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44830</v>
+        <v>45937</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7867,13 +7857,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7916,7 +7901,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 20152-2026</t>
+          <t>A 50209-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7930,10 +7915,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46138</v>
+        <v>45943</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7946,7 +7931,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7989,7 +7974,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 53227-2021</t>
+          <t>A 50337-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8003,10 +7988,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44468</v>
+        <v>45944</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8019,7 +8004,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8062,7 +8047,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 18612-2025</t>
+          <t>A 59625-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8076,10 +8061,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45763</v>
+        <v>45254</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8092,7 +8077,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8135,7 +8120,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28224-2023</t>
+          <t>A 22207-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8149,10 +8134,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45099</v>
+        <v>46153</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8165,7 +8150,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8208,7 +8193,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 7730-2023</t>
+          <t>A 21929-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8222,10 +8207,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44973</v>
+        <v>46150</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8238,7 +8223,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8281,7 +8266,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 21929-2026</t>
+          <t>A 15659-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8295,10 +8280,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46150</v>
+        <v>45748</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8311,7 +8296,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8354,7 +8339,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 22207-2026</t>
+          <t>A 16154-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8368,10 +8353,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46153</v>
+        <v>45406</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8384,7 +8369,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8427,7 +8412,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 22620-2026</t>
+          <t>A 16155-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8441,10 +8426,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46155</v>
+        <v>45406</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8457,7 +8442,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8500,7 +8485,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 47708-2025</t>
+          <t>A 35969-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8514,10 +8499,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45931</v>
+        <v>45533</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8530,7 +8515,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8573,7 +8558,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 68454-2021</t>
+          <t>A 54526-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8587,10 +8572,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44529</v>
+        <v>45965</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8603,7 +8588,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8646,7 +8631,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 48790-2025</t>
+          <t>A 41554-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8660,10 +8645,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45937</v>
+        <v>45560</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8719,7 +8704,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 48791-2025</t>
+          <t>A 56523-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8733,10 +8718,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45937</v>
+        <v>45975</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8749,7 +8734,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8792,7 +8777,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 48787-2025</t>
+          <t>A 57262-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8806,10 +8791,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45937</v>
+        <v>45979</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8822,7 +8807,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8865,7 +8850,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 48788-2025</t>
+          <t>A 45983-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8879,10 +8864,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45937</v>
+        <v>45580</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8895,7 +8880,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8938,7 +8923,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 7781-2023</t>
+          <t>A 32826-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8952,10 +8937,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44973</v>
+        <v>44784</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8968,7 +8953,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9011,7 +8996,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 73158-2021</t>
+          <t>A 53426-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9025,10 +9010,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44550</v>
+        <v>44879</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9041,7 +9026,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>13.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9084,7 +9069,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 50337-2025</t>
+          <t>A 57890-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9098,10 +9083,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45944</v>
+        <v>45981</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9114,7 +9099,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9157,7 +9142,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 50209-2025</t>
+          <t>A 22620-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9171,10 +9156,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45943</v>
+        <v>46155</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9187,7 +9172,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9230,7 +9215,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 38941-2023</t>
+          <t>A 57886-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9244,10 +9229,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45163</v>
+        <v>45981</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9260,7 +9245,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9303,7 +9288,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 16473-2023</t>
+          <t>A 57891-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9317,10 +9302,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45029</v>
+        <v>45981</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9333,7 +9318,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9376,7 +9361,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 16475-2023</t>
+          <t>A 13220-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9390,10 +9375,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45029</v>
+        <v>44644</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9406,7 +9391,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9449,7 +9434,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 34435-2024</t>
+          <t>A 19447-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9463,10 +9448,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45525</v>
+        <v>45770</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9479,7 +9464,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9522,7 +9507,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 10858-2026</t>
+          <t>A 64669-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9536,10 +9521,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46078</v>
+        <v>45281</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9552,7 +9537,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>8.5</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9595,7 +9580,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 42456-2024</t>
+          <t>A 16473-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9609,10 +9594,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45565</v>
+        <v>45029</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9625,7 +9610,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9668,7 +9653,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 19781-2025</t>
+          <t>A 16475-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9682,10 +9667,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45771</v>
+        <v>45029</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9698,7 +9683,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>6.1</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9741,7 +9726,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 12967-2024</t>
+          <t>A 53131-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9755,10 +9740,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45385</v>
+        <v>44876</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9771,7 +9756,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9814,7 +9799,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 37371-2023</t>
+          <t>A 59252-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9828,10 +9813,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45156</v>
+        <v>45988</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9844,7 +9829,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9887,7 +9872,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 35969-2024</t>
+          <t>A 64784-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9901,10 +9886,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45533</v>
+        <v>45282</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9917,7 +9902,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9960,7 +9945,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 7921-2024</t>
+          <t>A 3044-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9974,10 +9959,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45350</v>
+        <v>44582</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9990,7 +9975,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10033,7 +10018,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 27441-2026</t>
+          <t>A 15000-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10047,10 +10032,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46189</v>
+        <v>45015</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10063,7 +10048,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10106,7 +10091,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 27586-2026</t>
+          <t>A 60505-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10116,14 +10101,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46190</v>
+        <v>45995</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10136,7 +10121,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10179,7 +10164,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 13515-2022</t>
+          <t>A 6251-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10193,10 +10178,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44648</v>
+        <v>44965</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10209,7 +10194,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.3</v>
+        <v>15.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10252,7 +10237,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 54526-2025</t>
+          <t>A 61535-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10266,10 +10251,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45965</v>
+        <v>46001</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10282,7 +10267,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10325,7 +10310,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 75-2025</t>
+          <t>A 61539-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10339,10 +10324,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45659</v>
+        <v>46001</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10355,7 +10340,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10398,7 +10383,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 3795-2024</t>
+          <t>A 19781-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10412,10 +10397,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45321</v>
+        <v>45771</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10428,7 +10413,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>6.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10471,7 +10456,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 32804-2026</t>
+          <t>A 10858-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10485,10 +10470,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46241</v>
+        <v>46078</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10500,13 +10485,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10549,7 +10529,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56523-2025</t>
+          <t>A 23451-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10563,10 +10543,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45975</v>
+        <v>45076</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10578,8 +10558,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10622,7 +10607,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 32797-2026</t>
+          <t>A 63884-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10636,10 +10621,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46241</v>
+        <v>46020</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10651,13 +10636,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10700,7 +10680,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 57262-2025</t>
+          <t>A 60498-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10714,10 +10694,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45979</v>
+        <v>45643</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10730,7 +10710,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10773,7 +10753,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 61884-2024</t>
+          <t>A 5927-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10787,10 +10767,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45652</v>
+        <v>44598</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10803,7 +10783,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10846,7 +10826,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 57890-2025</t>
+          <t>A 60-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10860,10 +10840,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45981</v>
+        <v>46024</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10876,7 +10856,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10919,7 +10899,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 57886-2025</t>
+          <t>A 41893-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10933,10 +10913,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45981</v>
+        <v>44830</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10948,8 +10928,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10992,7 +10977,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 57891-2025</t>
+          <t>A 7783-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11006,10 +10991,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45981</v>
+        <v>44973</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11022,7 +11007,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11065,7 +11050,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 45521-2022</t>
+          <t>A 1525-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11079,10 +11064,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44845</v>
+        <v>46034</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11095,7 +11080,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11138,7 +11123,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 5927-2022</t>
+          <t>A 5242-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11152,10 +11137,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44598</v>
+        <v>44594</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11168,7 +11153,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11211,7 +11196,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 23984-2024</t>
+          <t>A 57918-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11225,10 +11210,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45456</v>
+        <v>44900</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11241,7 +11226,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11284,7 +11269,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 24129-2024</t>
+          <t>A 7781-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11298,10 +11283,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45456</v>
+        <v>44973</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11314,7 +11299,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11357,7 +11342,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 33782-2026</t>
+          <t>A 7921-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11371,10 +11356,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46251</v>
+        <v>45350</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11387,7 +11372,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11430,7 +11415,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 33830-2026</t>
+          <t>A 3256-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11444,10 +11429,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46251</v>
+        <v>46041</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11460,7 +11445,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11503,7 +11488,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 30505-2026</t>
+          <t>A 45521-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11517,10 +11502,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46210</v>
+        <v>44845</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11533,7 +11518,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11576,7 +11561,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 59252-2025</t>
+          <t>A 17126-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11590,10 +11575,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45988</v>
+        <v>44677</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11606,7 +11591,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11649,7 +11634,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 35465-2022</t>
+          <t>A 56116-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11663,10 +11648,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44798</v>
+        <v>44889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11679,7 +11664,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11722,7 +11707,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 65116-2023</t>
+          <t>A 40896-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11732,14 +11717,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45287</v>
+        <v>44825</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11752,7 +11737,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.1</v>
+        <v>11.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11795,7 +11780,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 59625-2023</t>
+          <t>A 12329-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11809,10 +11794,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45254</v>
+        <v>45378</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11825,7 +11810,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11868,7 +11853,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 60505-2025</t>
+          <t>A 37371-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11882,10 +11867,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45995</v>
+        <v>45156</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11898,7 +11883,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11941,7 +11926,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 19447-2025</t>
+          <t>A 7655-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11955,10 +11940,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45770</v>
+        <v>46062</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11971,7 +11956,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12014,7 +11999,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 131-2024</t>
+          <t>A 7659-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12028,10 +12013,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45294</v>
+        <v>46062</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12044,7 +12029,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>7.5</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12087,7 +12072,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 54087-2021</t>
+          <t>A 3074-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12101,10 +12086,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44470</v>
+        <v>44946</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12116,13 +12101,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12165,7 +12145,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 61535-2025</t>
+          <t>A 7730-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12179,10 +12159,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46001</v>
+        <v>44973</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12195,7 +12175,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12238,7 +12218,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 61539-2025</t>
+          <t>A 10494-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12252,10 +12232,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46001</v>
+        <v>44623</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12268,7 +12248,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>13.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12311,7 +12291,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 36033-2026</t>
+          <t>A 46364-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12325,10 +12305,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46267</v>
+        <v>45582</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12384,7 +12364,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 27652-2022</t>
+          <t>A 33546-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12398,10 +12378,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44743</v>
+        <v>44789</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12414,7 +12394,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>9.1</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12457,7 +12437,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 45983-2024</t>
+          <t>A 9821-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12471,10 +12451,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45580</v>
+        <v>44620</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12487,7 +12467,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12530,7 +12510,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 5242-2022</t>
+          <t>A 38941-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12544,10 +12524,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44594</v>
+        <v>45163</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12560,7 +12540,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>8.800000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12603,7 +12583,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 46529-2024</t>
+          <t>A 32527-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12617,10 +12597,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45582</v>
+        <v>45513</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12632,8 +12612,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>11.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12676,7 +12661,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 16154-2024</t>
+          <t>A 49781-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12690,10 +12675,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45406</v>
+        <v>45597</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12706,7 +12691,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.8</v>
+        <v>5.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12749,7 +12734,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 16155-2024</t>
+          <t>A 32541-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12763,10 +12748,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45406</v>
+        <v>45513</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12778,8 +12763,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12822,7 +12812,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 57259-2022</t>
+          <t>A 27441-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12836,10 +12826,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44895</v>
+        <v>46189</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12852,7 +12842,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12895,7 +12885,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 59879-2024</t>
+          <t>A 61046-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12909,10 +12899,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45640</v>
+        <v>45645</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12925,7 +12915,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12968,7 +12958,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 32826-2022</t>
+          <t>A 27586-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12978,14 +12968,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44784</v>
+        <v>46190</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12998,7 +12988,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13041,7 +13031,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 58330-2022</t>
+          <t>A 14211-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13055,10 +13045,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44901</v>
+        <v>46099</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13071,7 +13061,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13114,7 +13104,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 15704-2023</t>
+          <t>A 3795-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13128,10 +13118,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45021</v>
+        <v>45321</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13144,7 +13134,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13187,7 +13177,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 30796-2024</t>
+          <t>A 15592-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13201,10 +13191,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45497</v>
+        <v>46106</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13217,7 +13207,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13260,7 +13250,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 16152-2024</t>
+          <t>A 16030-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13274,10 +13264,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45406</v>
+        <v>46108</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13290,7 +13280,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>15.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13333,7 +13323,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 4906-2024</t>
+          <t>A 42456-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13347,10 +13337,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45329</v>
+        <v>45565</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13363,7 +13353,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13406,7 +13396,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 63884-2025</t>
+          <t>A 17485-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13416,14 +13406,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46020</v>
+        <v>46120</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13436,7 +13426,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13479,7 +13469,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 13883-2022</t>
+          <t>A 30796-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13493,10 +13483,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44650</v>
+        <v>45497</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13509,7 +13499,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>6.1</v>
+        <v>3.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13552,7 +13542,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 53401-2022</t>
+          <t>A 18840-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13566,10 +13556,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44879</v>
+        <v>46129</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13582,7 +13572,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13625,7 +13615,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 15181-2023</t>
+          <t>A 19373-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13639,10 +13629,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45016</v>
+        <v>46133</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13655,7 +13645,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13698,7 +13688,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 60-2026</t>
+          <t>A 20009-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13712,10 +13702,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46024</v>
+        <v>46136</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13728,7 +13718,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13771,7 +13761,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 20667-2026</t>
+          <t>A 16152-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13785,10 +13775,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46141</v>
+        <v>45406</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13801,7 +13791,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13844,7 +13834,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 855-2023</t>
+          <t>A 47755-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13858,10 +13848,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44931</v>
+        <v>44854</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13874,7 +13864,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13917,7 +13907,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 47755-2022</t>
+          <t>A 10768-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13931,10 +13921,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44854</v>
+        <v>45369</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13947,7 +13937,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13990,7 +13980,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 9821-2022</t>
+          <t>A 62299-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14004,10 +13994,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44620</v>
+        <v>44923</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14020,7 +14010,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14063,7 +14053,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 13220-2022</t>
+          <t>A 11460-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14077,10 +14067,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44644</v>
+        <v>45372</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14093,7 +14083,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14136,7 +14126,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 68400-2021</t>
+          <t>A 33830-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14150,10 +14140,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44529</v>
+        <v>46251</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14166,7 +14156,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.8</v>
+        <v>8.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14209,7 +14199,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 1525-2026</t>
+          <t>A 55303-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14223,10 +14213,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46034</v>
+        <v>44887</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14239,7 +14229,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14282,7 +14272,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 25514-2022</t>
+          <t>A 33782-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14296,10 +14286,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44732</v>
+        <v>46251</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14312,7 +14302,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14355,7 +14345,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 10494-2022</t>
+          <t>A 36982-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14369,10 +14359,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44623</v>
+        <v>45539</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14385,7 +14375,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>13.3</v>
+        <v>3.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14428,7 +14418,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 3256-2026</t>
+          <t>A 855-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14442,10 +14432,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46041</v>
+        <v>44931</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14458,7 +14448,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>8.1</v>
+        <v>3.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14501,7 +14491,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 52688-2024</t>
+          <t>A 21363-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14515,10 +14505,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45610</v>
+        <v>45063</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14531,7 +14521,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14574,7 +14564,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 47902-2024</t>
+          <t>A 30505-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14588,10 +14578,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45589</v>
+        <v>46210</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14604,7 +14594,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14647,7 +14637,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 2263-2024</t>
+          <t>A 61884-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14661,10 +14651,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45310</v>
+        <v>45652</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14676,13 +14666,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14725,7 +14710,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 37305-2022</t>
+          <t>A 19773-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14739,10 +14724,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44808</v>
+        <v>45771</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14755,7 +14740,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>9.9</v>
+        <v>1.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14798,7 +14783,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 60498-2024</t>
+          <t>A 3399-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14812,10 +14797,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45643</v>
+        <v>45318</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14828,7 +14813,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14871,7 +14856,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 7655-2026</t>
+          <t>A 44708-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14885,10 +14870,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46062</v>
+        <v>45190</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14901,7 +14886,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14944,7 +14929,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 7659-2026</t>
+          <t>A 25514-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14958,10 +14943,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46062</v>
+        <v>44732</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14974,7 +14959,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15017,7 +15002,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 37562-2024</t>
+          <t>A 12967-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15031,10 +15016,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45541</v>
+        <v>45385</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15047,7 +15032,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15090,7 +15075,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 15659-2025</t>
+          <t>A 24432-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15100,14 +15085,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45748</v>
+        <v>44726</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15120,7 +15105,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15163,7 +15148,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 19773-2025</t>
+          <t>A 37658-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15177,10 +15162,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45771</v>
+        <v>44810</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15236,7 +15221,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 8273-2024</t>
+          <t>A 15658-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15250,10 +15235,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45352</v>
+        <v>45748</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15266,7 +15251,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15309,7 +15294,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 2402-2024</t>
+          <t>A 66960-2021</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15323,10 +15308,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45310</v>
+        <v>44522</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15339,7 +15324,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15382,7 +15367,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 3399-2024</t>
+          <t>A 37305-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15396,10 +15381,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45318</v>
+        <v>44808</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15412,7 +15397,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1</v>
+        <v>9.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15455,7 +15440,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 10767-2024</t>
+          <t>A 36033-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15469,10 +15454,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45369</v>
+        <v>46267</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15485,7 +15470,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15528,7 +15513,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 24432-2022</t>
+          <t>A 53193-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15538,14 +15523,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44726</v>
+        <v>45229</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15558,7 +15543,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15601,7 +15586,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 16487-2023</t>
+          <t>A 20955-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15615,10 +15600,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45029</v>
+        <v>45777</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15631,7 +15616,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15674,7 +15659,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 64669-2023</t>
+          <t>A 22016-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15688,10 +15673,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45281</v>
+        <v>45784</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15704,7 +15689,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15747,7 +15732,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 55303-2022</t>
+          <t>A 20667-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15761,10 +15746,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44887</v>
+        <v>46141</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15777,7 +15762,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15820,7 +15805,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 12329-2024</t>
+          <t>A 37801-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15830,14 +15815,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45378</v>
+        <v>45543</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15850,7 +15835,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15893,7 +15878,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 4077-2025</t>
+          <t>A 32797-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15907,10 +15892,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45684</v>
+        <v>46241</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15922,8 +15907,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15966,7 +15956,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 62294-2022</t>
+          <t>A 11837-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15980,10 +15970,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44923</v>
+        <v>45728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15996,7 +15986,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16039,7 +16029,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 12264-2024</t>
+          <t>A 15645-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16053,10 +16043,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45378</v>
+        <v>45404</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16069,7 +16059,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16112,7 +16102,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 12266-2024</t>
+          <t>A 38535-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16126,10 +16116,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45378</v>
+        <v>46283</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16142,7 +16132,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16185,7 +16175,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 44708-2023</t>
+          <t>A 24559-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16199,10 +16189,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45190</v>
+        <v>45798</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16215,7 +16205,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16258,7 +16248,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 20955-2025</t>
+          <t>A 32804-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16272,10 +16262,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45777</v>
+        <v>46241</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16287,8 +16277,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16331,7 +16326,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 22016-2025</t>
+          <t>A 49062-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16345,10 +16340,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45784</v>
+        <v>45594</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16361,7 +16356,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16404,7 +16399,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 37801-2024</t>
+          <t>A 45519-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16414,14 +16409,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45543</v>
+        <v>45194</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16434,7 +16429,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16477,7 +16472,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 24559-2025</t>
+          <t>A 27201-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16491,10 +16486,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45798</v>
+        <v>45812</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16507,7 +16502,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16550,7 +16545,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 11837-2025</t>
+          <t>A 30486-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16564,10 +16559,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45728</v>
+        <v>45829</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16580,7 +16575,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16623,7 +16618,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 15645-2024</t>
+          <t>A 31464-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16637,10 +16632,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45404</v>
+        <v>45833</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16653,7 +16648,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16696,7 +16691,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 45519-2023</t>
+          <t>A 34671-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16710,10 +16705,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45194</v>
+        <v>45847</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16725,8 +16720,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16769,7 +16769,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 49062-2024</t>
+          <t>A 10640-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16783,10 +16783,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45594</v>
+        <v>45721</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16842,7 +16842,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 27201-2025</t>
+          <t>A 13510-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -16856,10 +16856,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45812</v>
+        <v>44648</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.1</v>
+        <v>17.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -16912,78 +16912,151 @@
       </c>
       <c r="V220" s="2" t="inlineStr"/>
     </row>
-    <row r="221">
+    <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
+          <t>A 36192-2025</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D221" s="1" t="n">
+        <v>45867</v>
+      </c>
+      <c r="E221" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>TROLLHÄTTAN</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="n">
+        <v>0</v>
+      </c>
+      <c r="T221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="n">
+        <v>0</v>
+      </c>
+      <c r="V221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
           <t>S 643-2026</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C222" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D221" s="1" t="n">
+      <c r="D222" s="1" t="n">
         <v>46090</v>
       </c>
-      <c r="E221" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="I221" t="n">
+      <c r="E222" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>TROLLHÄTTAN</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
         <v>0.8</v>
       </c>
-      <c r="J221" t="n">
-        <v>0</v>
-      </c>
-      <c r="K221" t="n">
-        <v>0</v>
-      </c>
-      <c r="L221" t="n">
-        <v>0</v>
-      </c>
-      <c r="M221" t="n">
-        <v>0</v>
-      </c>
-      <c r="N221" t="n">
-        <v>0</v>
-      </c>
-      <c r="O221" t="n">
-        <v>0</v>
-      </c>
-      <c r="P221" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0</v>
-      </c>
-      <c r="S221" t="n">
-        <v>0</v>
-      </c>
-      <c r="T221" t="n">
-        <v>0</v>
-      </c>
-      <c r="U221" t="n">
-        <v>0</v>
-      </c>
-      <c r="V221" s="2" t="inlineStr"/>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="n">
+        <v>0</v>
+      </c>
+      <c r="T222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="n">
+        <v>0</v>
+      </c>
+      <c r="V222" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>45386</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>46104</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44876</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44572</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44461</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44622</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44811</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>44686</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>44757</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>44693</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>44524</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44522</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44565</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44572</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>45456</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45456</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44923</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>45378</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45378</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>45699</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>45684</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>44818</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>45763</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44515</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45141</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>45021</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>45016</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45456</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45287</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>45483</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>45029</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>45371</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>45237</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44879</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>45582</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>45525</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>45541</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44743</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>44607</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45640</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44635</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>44901</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>45329</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>45002</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45589</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44529</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44895</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>45369</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45310</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>44468</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45352</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45610</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>45582</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>45294</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>45659</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>45679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>44529</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>45748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44470</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>44798</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>45784</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>44817</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>46138</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44923</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>45496</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>45099</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>45685</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>45369</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>46140</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>44909</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>46140</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>44648</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>45684</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>45310</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44550</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>44650</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>45937</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>45937</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>45931</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>45937</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>45937</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>45943</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>45944</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>45254</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>46153</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>46150</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>45748</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>45406</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45406</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>45533</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45965</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>45560</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45975</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>45979</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>45580</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>44784</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>44879</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>45981</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>46155</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>45981</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>45981</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>44644</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>45770</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>45281</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>45029</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>45029</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>44876</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>45988</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>45282</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>44582</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>45015</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>45995</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>44965</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>46001</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>46001</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>45771</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>46078</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>45076</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>46020</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>45643</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>44598</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>46024</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>44830</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44973</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>46034</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>44594</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>44900</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>44973</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>45350</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>46041</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>44845</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44677</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>44889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>44825</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45378</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45156</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>46062</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>46062</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>44946</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>44973</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>44623</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>45582</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>44789</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>44620</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45163</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>45513</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45597</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45513</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>46189</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45645</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>46190</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>46099</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45321</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>46106</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>46108</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45565</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>46120</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45497</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>46129</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>46133</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>46136</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45406</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>44854</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45369</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>44923</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>45372</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>46251</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>44887</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>46251</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45539</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>44931</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>45063</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>46210</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45652</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45771</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45318</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45190</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>44732</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>45385</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>44726</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>44810</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45748</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>44522</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>44808</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>46267</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45229</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45777</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45784</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>46141</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>45543</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>46241</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45404</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>46283</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45798</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>46241</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>45594</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45194</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45812</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>45829</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>45833</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>45847</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45721</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>44648</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45867</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>46090</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>

--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE222"/>
+  <dimension ref="A1:AE220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 13131-2024</t>
+          <t>A 15069-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45386</v>
+        <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -835,25 +835,20 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -868,7 +863,7 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -881,145 +876,150 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Kortskaftad parasitspik
+Rostfläck</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/artfynd/A 15069-2026 artfynd.xlsx", "A 15069-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor/A 15069-2026 karta.png", "A 15069-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor_geotiff/A 15069-2026 georefererad karta.tif", "A 15069-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomål/A 15069-2026 FSC-klagomål.docx", "A 15069-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomålsmail/A 15069-2026 FSC-klagomål mail.docx", "A 15069-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsyn/A 15069-2026 tillsynsbegäran.docx", "A 15069-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsynsmail/A 15069-2026 tillsynsbegäran mail.docx", "A 15069-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 13131-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45386</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TROLLHÄTTAN</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Svinrot
 Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/artfynd/A 13131-2024 artfynd.xlsx", "A 13131-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor/A 13131-2024 karta.png", "A 13131-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor_geotiff/A 13131-2024 georefererad karta.tif", "A 13131-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomål/A 13131-2024 FSC-klagomål.docx", "A 13131-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomålsmail/A 13131-2024 FSC-klagomål mail.docx", "A 13131-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsyn/A 13131-2024 tillsynsbegäran.docx", "A 13131-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsynsmail/A 13131-2024 tillsynsbegäran mail.docx", "A 13131-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 15069-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46104</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Kortskaftad parasitspik
-Rostfläck</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/artfynd/A 15069-2026 artfynd.xlsx", "A 15069-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor/A 15069-2026 karta.png", "A 15069-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor_geotiff/A 15069-2026 georefererad karta.tif", "A 15069-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomål/A 15069-2026 FSC-klagomål.docx", "A 15069-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomålsmail/A 15069-2026 FSC-klagomål mail.docx", "A 15069-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsyn/A 15069-2026 tillsynsbegäran.docx", "A 15069-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsynsmail/A 15069-2026 tillsynsbegäran mail.docx", "A 15069-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44876</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44572</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 51172-2021</t>
+          <t>A 7747-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44461</v>
+        <v>44608</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2182,7 +2182,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7747-2022</t>
+          <t>A 10150-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44608</v>
+        <v>44622</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2255,7 +2255,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10150-2022</t>
+          <t>A 38000-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44622</v>
+        <v>44811</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38000-2022</t>
+          <t>A 18533-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44811</v>
+        <v>44686</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2401,7 +2401,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 18533-2022</t>
+          <t>A 30157-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44686</v>
+        <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2474,7 +2474,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30157-2022</t>
+          <t>A 19577-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44757</v>
+        <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19577-2022</t>
+          <t>A 52687-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44693</v>
+        <v>44466</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 52687-2021</t>
+          <t>A 67535-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44466</v>
+        <v>44524</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2649,8 +2649,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2693,7 +2698,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 67535-2021</t>
+          <t>A 66971-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2707,10 +2712,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44524</v>
+        <v>44522</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2722,13 +2727,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 66971-2021</t>
+          <t>A 318-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44522</v>
+        <v>44565</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>8.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 318-2022</t>
+          <t>A 1295-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44565</v>
+        <v>44572</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8.6</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2917,7 +2917,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1295-2022</t>
+          <t>A 24127-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44572</v>
+        <v>45456</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 24127-2024</t>
+          <t>A 23984-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3007,7 +3007,7 @@
         <v>45456</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23984-2024</t>
+          <t>A 62294-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45456</v>
+        <v>44923</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62294-2022</t>
+          <t>A 12264-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44923</v>
+        <v>45378</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12264-2024</t>
+          <t>A 12266-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3226,7 +3226,7 @@
         <v>45378</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12266-2024</t>
+          <t>A 6354-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45378</v>
+        <v>45699</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>19.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 6354-2025</t>
+          <t>A 3886-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45699</v>
+        <v>45684</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3384,8 +3384,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>19.3</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3428,7 +3433,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3886-2025</t>
+          <t>A 39611-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3442,10 +3447,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45684</v>
+        <v>44818</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3463,7 +3468,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3506,7 +3511,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 39611-2022</t>
+          <t>A 65254-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3520,10 +3525,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44818</v>
+        <v>44515</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3535,13 +3540,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3601,7 +3601,7 @@
         <v>45763</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 65254-2021</t>
+          <t>A 34909-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44515</v>
+        <v>45141</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.4</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3730,7 +3730,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34909-2023</t>
+          <t>A 65116-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3740,14 +3740,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45141</v>
+        <v>45287</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>45021</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>45016</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45456</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 65116-2023</t>
+          <t>A 29300-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4032,14 +4032,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45287</v>
+        <v>45483</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4095,7 +4095,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 29300-2024</t>
+          <t>A 16487-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45483</v>
+        <v>45029</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16487-2023</t>
+          <t>A 11123-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45029</v>
+        <v>45371</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4241,7 +4241,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11123-2024</t>
+          <t>A 37562-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45371</v>
+        <v>45541</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 55033-2023</t>
+          <t>A 27652-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45237</v>
+        <v>44743</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>9.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 53401-2022</t>
+          <t>A 34435-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44879</v>
+        <v>45525</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 46533-2024</t>
+          <t>A 7628-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45582</v>
+        <v>44607</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4533,7 +4533,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34435-2024</t>
+          <t>A 55033-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45525</v>
+        <v>45237</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 37562-2024</t>
+          <t>A 53401-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45541</v>
+        <v>44879</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27652-2022</t>
+          <t>A 59879-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44743</v>
+        <v>45640</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>9.1</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7628-2022</t>
+          <t>A 11991-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44607</v>
+        <v>44635</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59879-2024</t>
+          <t>A 58330-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45640</v>
+        <v>44901</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11991-2022</t>
+          <t>A 4906-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44635</v>
+        <v>45329</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58330-2022</t>
+          <t>A 13119-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44901</v>
+        <v>45002</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4906-2024</t>
+          <t>A 46533-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45329</v>
+        <v>45582</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 13119-2023</t>
+          <t>A 47902-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45002</v>
+        <v>45589</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 47902-2024</t>
+          <t>A 68454-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45589</v>
+        <v>44529</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 68454-2021</t>
+          <t>A 57259-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44529</v>
+        <v>44895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 57259-2022</t>
+          <t>A 10777-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44895</v>
+        <v>45369</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 10777-2024</t>
+          <t>A 2263-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45369</v>
+        <v>45310</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5438,8 +5438,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5482,7 +5487,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2263-2024</t>
+          <t>A 20009-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5496,10 +5501,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45310</v>
+        <v>46136</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5511,13 +5516,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53227-2021</t>
+          <t>A 15648-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44468</v>
+        <v>45748</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8273-2024</t>
+          <t>A 53227-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45352</v>
+        <v>44468</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52688-2024</t>
+          <t>A 21979-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45610</v>
+        <v>45784</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 46529-2024</t>
+          <t>A 8273-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45582</v>
+        <v>45352</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>11.7</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 131-2024</t>
+          <t>A 52688-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45294</v>
+        <v>45610</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 75-2025</t>
+          <t>A 3272-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45659</v>
+        <v>45679</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.4</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 3272-2025</t>
+          <t>A 46529-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45679</v>
+        <v>45582</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>11.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 68400-2021</t>
+          <t>A 20152-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44529</v>
+        <v>46138</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15648-2025</t>
+          <t>A 131-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45748</v>
+        <v>45294</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 54087-2021</t>
+          <t>A 75-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44470</v>
+        <v>45659</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6246,13 +6246,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6295,7 +6290,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35465-2022</t>
+          <t>A 68400-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6309,10 +6304,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44798</v>
+        <v>44529</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6325,7 +6320,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6368,7 +6363,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 21979-2025</t>
+          <t>A 30773-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6382,10 +6377,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45784</v>
+        <v>45496</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6398,7 +6393,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6441,7 +6436,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39116-2022</t>
+          <t>A 54087-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6455,10 +6450,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44817</v>
+        <v>44470</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6470,8 +6465,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6514,7 +6514,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 20152-2026</t>
+          <t>A 35465-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6528,10 +6528,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46138</v>
+        <v>44798</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6587,7 +6587,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62266-2022</t>
+          <t>A 39116-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44923</v>
+        <v>44817</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6660,7 +6660,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 30773-2024</t>
+          <t>A 28224-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6674,10 +6674,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45496</v>
+        <v>45099</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6733,7 +6733,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 28224-2023</t>
+          <t>A 4307-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45099</v>
+        <v>45685</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6806,7 +6806,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4307-2025</t>
+          <t>A 20500-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45685</v>
+        <v>46140</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6879,7 +6879,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 10767-2024</t>
+          <t>A 48788-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45369</v>
+        <v>45937</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20500-2026</t>
+          <t>A 62266-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46140</v>
+        <v>44923</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7025,7 +7025,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 60103-2022</t>
+          <t>A 20501-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7039,10 +7039,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44909</v>
+        <v>46140</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7098,7 +7098,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20501-2026</t>
+          <t>A 48790-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7112,10 +7112,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46140</v>
+        <v>45937</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7171,7 +7171,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13515-2022</t>
+          <t>A 47708-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7185,10 +7185,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44648</v>
+        <v>45931</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7244,7 +7244,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4077-2025</t>
+          <t>A 48787-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7258,10 +7258,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45684</v>
+        <v>45937</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7317,7 +7317,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 2402-2024</t>
+          <t>A 48791-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45310</v>
+        <v>45937</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7390,7 +7390,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 73158-2021</t>
+          <t>A 22207-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7404,10 +7404,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44550</v>
+        <v>46153</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7463,7 +7463,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13883-2022</t>
+          <t>A 21929-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7477,10 +7477,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44650</v>
+        <v>46150</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7536,7 +7536,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 48788-2025</t>
+          <t>A 50209-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7550,10 +7550,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45937</v>
+        <v>45943</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7609,7 +7609,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 48790-2025</t>
+          <t>A 10767-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7623,10 +7623,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45937</v>
+        <v>45369</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7682,7 +7682,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 47708-2025</t>
+          <t>A 50337-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45931</v>
+        <v>45944</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7755,7 +7755,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48787-2025</t>
+          <t>A 60103-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45937</v>
+        <v>44909</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7828,7 +7828,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48791-2025</t>
+          <t>A 22620-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7842,10 +7842,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45937</v>
+        <v>46155</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7901,7 +7901,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 50209-2025</t>
+          <t>A 13515-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45943</v>
+        <v>44648</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7974,7 +7974,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 50337-2025</t>
+          <t>A 54526-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7988,10 +7988,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45944</v>
+        <v>45965</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8047,7 +8047,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 59625-2023</t>
+          <t>A 4077-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45254</v>
+        <v>45684</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 22207-2026</t>
+          <t>A 2402-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46153</v>
+        <v>45310</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8193,7 +8193,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 21929-2026</t>
+          <t>A 73158-2021</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8207,10 +8207,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46150</v>
+        <v>44550</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8266,7 +8266,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 15659-2025</t>
+          <t>A 13883-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45748</v>
+        <v>44650</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.3</v>
+        <v>6.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8339,7 +8339,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 16154-2024</t>
+          <t>A 56523-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8353,10 +8353,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45406</v>
+        <v>45975</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8412,7 +8412,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 16155-2024</t>
+          <t>A 57262-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8426,10 +8426,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45406</v>
+        <v>45979</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8485,7 +8485,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 35969-2024</t>
+          <t>A 10858-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8499,10 +8499,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45533</v>
+        <v>46078</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>8.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 54526-2025</t>
+          <t>A 57890-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8572,10 +8572,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45965</v>
+        <v>45981</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 41554-2024</t>
+          <t>A 57886-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8645,10 +8645,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45560</v>
+        <v>45981</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8704,7 +8704,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56523-2025</t>
+          <t>A 57891-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8718,10 +8718,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8777,7 +8777,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 57262-2025</t>
+          <t>A 59625-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45979</v>
+        <v>45254</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8850,7 +8850,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 45983-2024</t>
+          <t>A 59252-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45580</v>
+        <v>45988</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8923,7 +8923,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 32826-2022</t>
+          <t>A 15659-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8937,10 +8937,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44784</v>
+        <v>45748</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8996,7 +8996,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 53426-2022</t>
+          <t>A 60505-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44879</v>
+        <v>45995</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>13.2</v>
+        <v>2.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 57890-2025</t>
+          <t>A 16154-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9083,10 +9083,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45981</v>
+        <v>45406</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9142,7 +9142,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 22620-2026</t>
+          <t>A 16155-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9156,10 +9156,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46155</v>
+        <v>45406</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9215,7 +9215,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 57886-2025</t>
+          <t>A 61535-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9229,10 +9229,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45981</v>
+        <v>46001</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9288,7 +9288,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 57891-2025</t>
+          <t>A 61539-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9302,10 +9302,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45981</v>
+        <v>46001</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9361,7 +9361,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 13220-2022</t>
+          <t>A 35969-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44644</v>
+        <v>45533</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 19447-2025</t>
+          <t>A 41554-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9448,10 +9448,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45770</v>
+        <v>45560</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9507,7 +9507,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 64669-2023</t>
+          <t>A 45983-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9521,10 +9521,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45281</v>
+        <v>45580</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9580,7 +9580,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 16473-2023</t>
+          <t>A 32826-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45029</v>
+        <v>44784</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9653,7 +9653,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 16475-2023</t>
+          <t>A 63884-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9667,10 +9667,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45029</v>
+        <v>46020</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9726,7 +9726,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 53131-2022</t>
+          <t>A 60-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9740,10 +9740,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44876</v>
+        <v>46024</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9799,7 +9799,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 59252-2025</t>
+          <t>A 53426-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45988</v>
+        <v>44879</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.6</v>
+        <v>13.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9872,7 +9872,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 64784-2023</t>
+          <t>A 13220-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9886,10 +9886,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45282</v>
+        <v>44644</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9945,7 +9945,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 3044-2022</t>
+          <t>A 19447-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9959,10 +9959,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44582</v>
+        <v>45770</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10018,7 +10018,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 15000-2023</t>
+          <t>A 64669-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45015</v>
+        <v>45281</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10091,7 +10091,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 60505-2025</t>
+          <t>A 16473-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10105,10 +10105,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45995</v>
+        <v>45029</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10164,7 +10164,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 6251-2023</t>
+          <t>A 16475-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10178,10 +10178,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44965</v>
+        <v>45029</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>15.4</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10237,7 +10237,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61535-2025</t>
+          <t>A 53131-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46001</v>
+        <v>44876</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10310,7 +10310,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 61539-2025</t>
+          <t>A 1525-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10324,10 +10324,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46001</v>
+        <v>46034</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10383,7 +10383,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 19781-2025</t>
+          <t>A 3256-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10397,10 +10397,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45771</v>
+        <v>46041</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10456,7 +10456,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 10858-2026</t>
+          <t>A 27441-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46078</v>
+        <v>46189</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>8.5</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10529,7 +10529,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 23451-2023</t>
+          <t>A 64784-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10543,10 +10543,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45076</v>
+        <v>45282</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10558,13 +10558,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10607,7 +10602,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 63884-2025</t>
+          <t>A 27586-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10617,14 +10612,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46020</v>
+        <v>46190</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10637,7 +10632,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10680,7 +10675,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 60498-2024</t>
+          <t>A 3044-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10694,10 +10689,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45643</v>
+        <v>44582</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10710,7 +10705,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10753,7 +10748,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 5927-2022</t>
+          <t>A 15000-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10767,10 +10762,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44598</v>
+        <v>45015</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10783,7 +10778,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10826,7 +10821,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 60-2026</t>
+          <t>A 6251-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10840,10 +10835,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46024</v>
+        <v>44965</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10856,7 +10851,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3</v>
+        <v>15.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10899,7 +10894,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 41893-2022</t>
+          <t>A 7655-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10913,10 +10908,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44830</v>
+        <v>46062</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10928,13 +10923,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10977,7 +10967,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7783-2023</t>
+          <t>A 19781-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10991,10 +10981,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44973</v>
+        <v>45771</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11007,7 +10997,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.2</v>
+        <v>6.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11050,7 +11040,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 1525-2026</t>
+          <t>A 23451-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11064,10 +11054,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46034</v>
+        <v>45076</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11079,8 +11069,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11123,7 +11118,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 5242-2022</t>
+          <t>A 60498-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11137,10 +11132,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44594</v>
+        <v>45643</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11153,7 +11148,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11196,7 +11191,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 57918-2022</t>
+          <t>A 5927-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11210,10 +11205,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44900</v>
+        <v>44598</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11226,7 +11221,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11269,7 +11264,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 7781-2023</t>
+          <t>A 32527-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11283,10 +11278,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44973</v>
+        <v>45513</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11298,8 +11293,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>0.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11342,7 +11342,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 7921-2024</t>
+          <t>A 32541-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11356,10 +11356,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45350</v>
+        <v>45513</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11371,8 +11371,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11415,7 +11420,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 3256-2026</t>
+          <t>A 41893-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11429,10 +11434,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46041</v>
+        <v>44830</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11444,8 +11449,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>8.1</v>
+        <v>2.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11488,7 +11498,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 45521-2022</t>
+          <t>A 7783-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11502,10 +11512,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44845</v>
+        <v>44973</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11518,7 +11528,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11561,7 +11571,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 17126-2022</t>
+          <t>A 14211-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11575,10 +11585,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44677</v>
+        <v>46099</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11591,7 +11601,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11634,7 +11644,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 56116-2022</t>
+          <t>A 5242-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11648,10 +11658,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44889</v>
+        <v>44594</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11664,7 +11674,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11707,7 +11717,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 40896-2022</t>
+          <t>A 57918-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11721,10 +11731,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44825</v>
+        <v>44900</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11737,7 +11747,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>11.3</v>
+        <v>3.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11780,7 +11790,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 12329-2024</t>
+          <t>A 7781-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11794,10 +11804,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45378</v>
+        <v>44973</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11810,7 +11820,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11853,7 +11863,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37371-2023</t>
+          <t>A 7921-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11867,10 +11877,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45156</v>
+        <v>45350</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11883,7 +11893,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11926,7 +11936,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 7655-2026</t>
+          <t>A 15592-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11940,10 +11950,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46062</v>
+        <v>46106</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11956,7 +11966,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -11999,7 +12009,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 7659-2026</t>
+          <t>A 45521-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12013,10 +12023,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46062</v>
+        <v>44845</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12029,7 +12039,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12072,7 +12082,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 3074-2023</t>
+          <t>A 16030-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12086,10 +12096,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44946</v>
+        <v>46108</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12102,7 +12112,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>6.1</v>
+        <v>15.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12145,7 +12155,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 7730-2023</t>
+          <t>A 17126-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12159,10 +12169,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44973</v>
+        <v>44677</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12175,7 +12185,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12218,7 +12228,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 10494-2022</t>
+          <t>A 56116-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12232,10 +12242,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44623</v>
+        <v>44889</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12248,7 +12258,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>13.3</v>
+        <v>2.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12291,7 +12301,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 46364-2024</t>
+          <t>A 17485-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12301,14 +12311,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45582</v>
+        <v>46120</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12321,7 +12331,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12364,7 +12374,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 33546-2022</t>
+          <t>A 40896-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12378,10 +12388,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44789</v>
+        <v>44825</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12394,7 +12404,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>11.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12437,7 +12447,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 9821-2022</t>
+          <t>A 12329-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12451,10 +12461,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44620</v>
+        <v>45378</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12467,7 +12477,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12510,7 +12520,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 38941-2023</t>
+          <t>A 37371-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12524,10 +12534,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45163</v>
+        <v>45156</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12540,7 +12550,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12583,7 +12593,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 32527-2024</t>
+          <t>A 33830-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12597,10 +12607,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45513</v>
+        <v>46251</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12612,13 +12622,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12661,7 +12666,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 49781-2024</t>
+          <t>A 18840-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12675,10 +12680,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45597</v>
+        <v>46129</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12691,7 +12696,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12734,7 +12739,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 32541-2024</t>
+          <t>A 3074-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12748,10 +12753,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45513</v>
+        <v>44946</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12763,13 +12768,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12812,7 +12812,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 27441-2026</t>
+          <t>A 7730-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46189</v>
+        <v>44973</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12885,7 +12885,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 61046-2024</t>
+          <t>A 10494-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12899,10 +12899,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45645</v>
+        <v>44623</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.3</v>
+        <v>13.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12958,7 +12958,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 27586-2026</t>
+          <t>A 19373-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12968,14 +12968,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46190</v>
+        <v>46133</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13031,7 +13031,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 14211-2026</t>
+          <t>A 46364-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13045,10 +13045,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46099</v>
+        <v>45582</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13104,7 +13104,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 3795-2024</t>
+          <t>A 33782-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13118,10 +13118,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45321</v>
+        <v>46251</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13177,7 +13177,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 15592-2026</t>
+          <t>A 33546-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13191,10 +13191,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46106</v>
+        <v>44789</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>8.4</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13250,7 +13250,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 16030-2026</t>
+          <t>A 9821-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13264,10 +13264,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46108</v>
+        <v>44620</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>15.8</v>
+        <v>2.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13323,7 +13323,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 42456-2024</t>
+          <t>A 38941-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13337,10 +13337,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45565</v>
+        <v>45163</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13396,7 +13396,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 17485-2026</t>
+          <t>A 30505-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13406,14 +13406,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46120</v>
+        <v>46210</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13469,7 +13469,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 30796-2024</t>
+          <t>A 49781-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13483,10 +13483,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45497</v>
+        <v>45597</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13542,7 +13542,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 18840-2026</t>
+          <t>A 61046-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13556,10 +13556,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46129</v>
+        <v>45645</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13615,7 +13615,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 19373-2026</t>
+          <t>A 3795-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13629,10 +13629,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46133</v>
+        <v>45321</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13688,7 +13688,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 20009-2026</t>
+          <t>A 42456-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13702,10 +13702,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46136</v>
+        <v>45565</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 16152-2024</t>
+          <t>A 30796-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13775,10 +13775,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45406</v>
+        <v>45497</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13834,7 +13834,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 47755-2022</t>
+          <t>A 36033-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44854</v>
+        <v>46267</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13907,7 +13907,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 10768-2024</t>
+          <t>A 16152-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13921,10 +13921,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45369</v>
+        <v>45406</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13980,7 +13980,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 62299-2022</t>
+          <t>A 47755-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13994,10 +13994,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44923</v>
+        <v>44854</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14053,7 +14053,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 11460-2024</t>
+          <t>A 10768-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14067,10 +14067,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45372</v>
+        <v>45369</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14126,7 +14126,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 33830-2026</t>
+          <t>A 62299-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14140,10 +14140,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46251</v>
+        <v>44923</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>8.9</v>
+        <v>0.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14199,7 +14199,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 55303-2022</t>
+          <t>A 11460-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14213,10 +14213,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44887</v>
+        <v>45372</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14272,7 +14272,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 33782-2026</t>
+          <t>A 55303-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14286,10 +14286,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46251</v>
+        <v>44887</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14362,7 +14362,7 @@
         <v>45539</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>44931</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>45063</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 30505-2026</t>
+          <t>A 20667-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14578,10 +14578,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46210</v>
+        <v>46141</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45652</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45771</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45318</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 44708-2023</t>
+          <t>A 38535-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14870,10 +14870,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45190</v>
+        <v>46283</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14929,7 +14929,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 25514-2022</t>
+          <t>A 44708-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14943,10 +14943,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44732</v>
+        <v>45190</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15002,7 +15002,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 12967-2024</t>
+          <t>A 25514-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15016,10 +15016,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45385</v>
+        <v>44732</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15075,7 +15075,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 24432-2022</t>
+          <t>A 12967-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15085,14 +15085,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44726</v>
+        <v>45385</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15148,7 +15148,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 37658-2022</t>
+          <t>A 24432-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15158,14 +15158,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44810</v>
+        <v>44726</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 15658-2025</t>
+          <t>A 32804-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15235,10 +15235,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45748</v>
+        <v>46241</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15250,8 +15250,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15294,7 +15299,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 66960-2021</t>
+          <t>A 32797-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15308,10 +15313,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44522</v>
+        <v>46241</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15323,8 +15328,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15367,7 +15377,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 37305-2022</t>
+          <t>A 37658-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15381,10 +15391,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44808</v>
+        <v>44810</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15397,7 +15407,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>9.9</v>
+        <v>1.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15440,7 +15450,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 36033-2026</t>
+          <t>A 15658-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15454,10 +15464,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46267</v>
+        <v>45748</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15470,7 +15480,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15513,7 +15523,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 53193-2023</t>
+          <t>A 66960-2021</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15527,10 +15537,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45229</v>
+        <v>44522</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15543,7 +15553,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15586,7 +15596,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 20955-2025</t>
+          <t>A 37305-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15600,10 +15610,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45777</v>
+        <v>44808</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15616,7 +15626,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.2</v>
+        <v>9.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15659,7 +15669,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 22016-2025</t>
+          <t>A 53193-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15673,10 +15683,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45784</v>
+        <v>45229</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15689,7 +15699,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15732,7 +15742,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 20667-2026</t>
+          <t>A 20955-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15746,10 +15756,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46141</v>
+        <v>45777</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15762,7 +15772,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15805,7 +15815,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 37801-2024</t>
+          <t>A 22016-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15815,14 +15825,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45543</v>
+        <v>45784</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15835,7 +15845,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15878,7 +15888,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 32797-2026</t>
+          <t>A 37801-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15888,14 +15898,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46241</v>
+        <v>45543</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15907,13 +15917,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15973,7 +15978,7 @@
         <v>45728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16046,7 +16051,7 @@
         <v>45404</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16102,7 +16107,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 38535-2026</t>
+          <t>A 24559-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16116,10 +16121,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46283</v>
+        <v>45798</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16132,7 +16137,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16175,7 +16180,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 24559-2025</t>
+          <t>A 49062-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16189,10 +16194,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45798</v>
+        <v>45594</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16205,7 +16210,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16248,7 +16253,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 32804-2026</t>
+          <t>A 45519-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16262,10 +16267,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46241</v>
+        <v>45194</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16277,13 +16282,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16326,7 +16326,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 49062-2024</t>
+          <t>A 27201-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16340,10 +16340,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45594</v>
+        <v>45812</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16399,7 +16399,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 45519-2023</t>
+          <t>A 30486-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16413,10 +16413,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45194</v>
+        <v>45829</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16472,7 +16472,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 27201-2025</t>
+          <t>A 31464-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16486,10 +16486,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45812</v>
+        <v>45833</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16545,7 +16545,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 30486-2025</t>
+          <t>A 34671-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16559,10 +16559,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45829</v>
+        <v>45847</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16574,8 +16574,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16618,7 +16623,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 31464-2025</t>
+          <t>A 10640-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16632,10 +16637,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45833</v>
+        <v>45721</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16648,7 +16653,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16691,7 +16696,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 34671-2025</t>
+          <t>A 13510-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16705,10 +16710,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45847</v>
+        <v>44648</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16720,13 +16725,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>2.6</v>
+        <v>17.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16769,7 +16769,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 10640-2025</t>
+          <t>A 36192-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -16783,10 +16783,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45721</v>
+        <v>45867</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16839,27 +16839,27 @@
       </c>
       <c r="V219" s="2" t="inlineStr"/>
     </row>
-    <row r="220" ht="15" customHeight="1">
+    <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 13510-2022</t>
+          <t>S 643-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44648</v>
+        <v>46090</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>17.6</v>
+        <v>0.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -16911,152 +16911,6 @@
         <v>0</v>
       </c>
       <c r="V220" s="2" t="inlineStr"/>
-    </row>
-    <row r="221" ht="15" customHeight="1">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>A 36192-2025</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D221" s="1" t="n">
-        <v>45867</v>
-      </c>
-      <c r="E221" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="I221" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J221" t="n">
-        <v>0</v>
-      </c>
-      <c r="K221" t="n">
-        <v>0</v>
-      </c>
-      <c r="L221" t="n">
-        <v>0</v>
-      </c>
-      <c r="M221" t="n">
-        <v>0</v>
-      </c>
-      <c r="N221" t="n">
-        <v>0</v>
-      </c>
-      <c r="O221" t="n">
-        <v>0</v>
-      </c>
-      <c r="P221" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0</v>
-      </c>
-      <c r="S221" t="n">
-        <v>0</v>
-      </c>
-      <c r="T221" t="n">
-        <v>0</v>
-      </c>
-      <c r="U221" t="n">
-        <v>0</v>
-      </c>
-      <c r="V221" s="2" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>S 643-2026</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D222" s="1" t="n">
-        <v>46090</v>
-      </c>
-      <c r="E222" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="I222" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J222" t="n">
-        <v>0</v>
-      </c>
-      <c r="K222" t="n">
-        <v>0</v>
-      </c>
-      <c r="L222" t="n">
-        <v>0</v>
-      </c>
-      <c r="M222" t="n">
-        <v>0</v>
-      </c>
-      <c r="N222" t="n">
-        <v>0</v>
-      </c>
-      <c r="O222" t="n">
-        <v>0</v>
-      </c>
-      <c r="P222" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0</v>
-      </c>
-      <c r="S222" t="n">
-        <v>0</v>
-      </c>
-      <c r="T222" t="n">
-        <v>0</v>
-      </c>
-      <c r="U222" t="n">
-        <v>0</v>
-      </c>
-      <c r="V222" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE220"/>
+  <dimension ref="A1:AE219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45386</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44876</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44572</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44608</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44622</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44811</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44686</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52687-2021</t>
+          <t>A 22016-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44466</v>
+        <v>45784</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 67535-2021</t>
+          <t>A 52687-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44524</v>
+        <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2649,13 +2649,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2698,7 +2693,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 66971-2021</t>
+          <t>A 1295-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2712,10 +2707,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44522</v>
+        <v>44572</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2728,7 +2723,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2771,7 +2766,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 318-2022</t>
+          <t>A 67535-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2785,10 +2780,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44565</v>
+        <v>44524</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2800,8 +2795,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>8.6</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1295-2022</t>
+          <t>A 66971-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44572</v>
+        <v>44522</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2917,7 +2917,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24127-2024</t>
+          <t>A 318-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45456</v>
+        <v>44565</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>8.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23984-2024</t>
+          <t>A 53193-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45456</v>
+        <v>45229</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62294-2022</t>
+          <t>A 39611-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44923</v>
+        <v>44818</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3092,8 +3092,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3136,7 +3141,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12264-2024</t>
+          <t>A 29300-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3150,10 +3155,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45378</v>
+        <v>45483</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3166,7 +3171,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3209,7 +3214,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12266-2024</t>
+          <t>A 7628-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3223,10 +3228,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45378</v>
+        <v>44607</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3244,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3282,7 +3287,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 6354-2025</t>
+          <t>A 33546-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3296,10 +3301,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45699</v>
+        <v>44789</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3312,7 +3317,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>19.3</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3355,7 +3360,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3886-2025</t>
+          <t>A 53426-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3369,10 +3374,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45684</v>
+        <v>44879</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3384,13 +3389,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>13.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3433,7 +3433,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 39611-2022</t>
+          <t>A 62266-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44818</v>
+        <v>44923</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3462,13 +3462,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3511,7 +3506,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 65254-2021</t>
+          <t>A 39116-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3525,10 +3520,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44515</v>
+        <v>44817</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3541,7 +3536,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3584,7 +3579,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18612-2025</t>
+          <t>A 11123-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3598,10 +3593,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45763</v>
+        <v>45371</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3614,7 +3609,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3657,7 +3652,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34909-2023</t>
+          <t>A 10768-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3671,10 +3666,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45141</v>
+        <v>45369</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3687,7 +3682,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3730,7 +3725,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 65116-2023</t>
+          <t>A 10777-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3740,14 +3735,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45287</v>
+        <v>45369</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3760,7 +3755,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3803,7 +3798,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15704-2023</t>
+          <t>A 57918-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3817,10 +3812,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45021</v>
+        <v>44900</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3833,7 +3828,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3876,7 +3871,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15181-2023</t>
+          <t>A 41893-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3890,10 +3885,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45016</v>
+        <v>44830</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3905,8 +3900,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 24129-2024</t>
+          <t>A 37658-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45456</v>
+        <v>44810</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 29300-2024</t>
+          <t>A 37801-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4032,14 +4032,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45483</v>
+        <v>45543</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4095,7 +4095,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16487-2023</t>
+          <t>A 53227-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45029</v>
+        <v>44468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11123-2024</t>
+          <t>A 18612-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45371</v>
+        <v>45763</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4241,7 +4241,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37562-2024</t>
+          <t>A 7730-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45541</v>
+        <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27652-2022</t>
+          <t>A 15648-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44743</v>
+        <v>45748</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>9.1</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 34435-2024</t>
+          <t>A 24559-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45525</v>
+        <v>45798</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 7628-2022</t>
+          <t>A 11837-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44607</v>
+        <v>45728</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4533,7 +4533,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 55033-2023</t>
+          <t>A 21979-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45237</v>
+        <v>45784</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 53401-2022</t>
+          <t>A 15645-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44879</v>
+        <v>45404</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59879-2024</t>
+          <t>A 68454-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45640</v>
+        <v>44529</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 11991-2022</t>
+          <t>A 60103-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44635</v>
+        <v>44909</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58330-2022</t>
+          <t>A 3044-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44901</v>
+        <v>44582</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 4906-2024</t>
+          <t>A 7781-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45329</v>
+        <v>44973</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13119-2023</t>
+          <t>A 56116-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45002</v>
+        <v>44889</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46533-2024</t>
+          <t>A 73158-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45582</v>
+        <v>44550</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47902-2024</t>
+          <t>A 64784-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45589</v>
+        <v>45282</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 68454-2021</t>
+          <t>A 36982-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44529</v>
+        <v>45539</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 57259-2022</t>
+          <t>A 38941-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44895</v>
+        <v>45163</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10777-2024</t>
+          <t>A 16473-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45369</v>
+        <v>45029</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 2263-2024</t>
+          <t>A 16475-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45310</v>
+        <v>45029</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5438,13 +5438,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5487,7 +5482,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20009-2026</t>
+          <t>A 34435-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5501,10 +5496,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46136</v>
+        <v>45525</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5517,7 +5512,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5560,7 +5555,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15648-2025</t>
+          <t>A 66960-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5574,10 +5569,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45748</v>
+        <v>44522</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5590,7 +5585,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5633,7 +5628,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53227-2021</t>
+          <t>A 42456-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5647,10 +5642,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44468</v>
+        <v>45565</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5663,7 +5658,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5706,7 +5701,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 21979-2025</t>
+          <t>A 19781-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5720,10 +5715,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45784</v>
+        <v>45771</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5736,7 +5731,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>6.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5779,7 +5774,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8273-2024</t>
+          <t>A 12967-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5793,10 +5788,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45352</v>
+        <v>45385</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5809,7 +5804,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5852,7 +5847,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52688-2024</t>
+          <t>A 11991-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5866,10 +5861,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45610</v>
+        <v>44635</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5882,7 +5877,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5925,7 +5920,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 3272-2025</t>
+          <t>A 45519-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5939,10 +5934,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45679</v>
+        <v>45194</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5955,7 +5950,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5998,7 +5993,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 46529-2024</t>
+          <t>A 37371-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6012,10 +6007,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45582</v>
+        <v>45156</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6028,7 +6023,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>11.7</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6071,7 +6066,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 20152-2026</t>
+          <t>A 49062-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6085,10 +6080,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46138</v>
+        <v>45594</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6101,7 +6096,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6144,7 +6139,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 131-2024</t>
+          <t>A 3074-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6158,10 +6153,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45294</v>
+        <v>44946</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6174,7 +6169,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6217,7 +6212,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 75-2025</t>
+          <t>A 13119-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6231,10 +6226,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45659</v>
+        <v>45002</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6247,7 +6242,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.4</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6290,7 +6285,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 68400-2021</t>
+          <t>A 35969-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6304,10 +6299,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44529</v>
+        <v>45533</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6320,7 +6315,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6363,7 +6358,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 30773-2024</t>
+          <t>A 27201-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6377,10 +6372,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45496</v>
+        <v>45812</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6393,7 +6388,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6436,7 +6431,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 54087-2021</t>
+          <t>A 47708-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6450,10 +6445,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44470</v>
+        <v>45931</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6465,13 +6460,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6514,7 +6504,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35465-2022</t>
+          <t>A 48790-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6528,10 +6518,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44798</v>
+        <v>45937</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6544,7 +6534,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6587,7 +6577,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 39116-2022</t>
+          <t>A 48791-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6601,10 +6591,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44817</v>
+        <v>45937</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6617,7 +6607,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6660,7 +6650,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 28224-2023</t>
+          <t>A 48787-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6674,10 +6664,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45099</v>
+        <v>45937</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6690,7 +6680,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6733,7 +6723,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 4307-2025</t>
+          <t>A 7921-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6747,10 +6737,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45685</v>
+        <v>45350</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6763,7 +6753,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6806,7 +6796,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20500-2026</t>
+          <t>A 48788-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6820,10 +6810,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46140</v>
+        <v>45937</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6836,7 +6826,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6879,7 +6869,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48788-2025</t>
+          <t>A 17126-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6893,10 +6883,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45937</v>
+        <v>44677</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6909,7 +6899,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6952,7 +6942,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62266-2022</t>
+          <t>A 50337-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6966,10 +6956,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44923</v>
+        <v>45944</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6982,7 +6972,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7025,7 +7015,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20501-2026</t>
+          <t>A 50209-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7039,10 +7029,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46140</v>
+        <v>45943</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7055,7 +7045,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7098,7 +7088,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 48790-2025</t>
+          <t>A 46533-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7112,10 +7102,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45937</v>
+        <v>45582</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7128,7 +7118,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7171,7 +7161,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47708-2025</t>
+          <t>A 53131-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7185,10 +7175,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45931</v>
+        <v>44876</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7201,7 +7191,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7244,7 +7234,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 48787-2025</t>
+          <t>A 13515-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7258,10 +7248,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45937</v>
+        <v>44648</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7274,7 +7264,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7317,7 +7307,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 48791-2025</t>
+          <t>A 7783-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7331,10 +7321,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45937</v>
+        <v>44973</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7347,7 +7337,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7390,7 +7380,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 22207-2026</t>
+          <t>A 11460-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7404,10 +7394,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46153</v>
+        <v>45372</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7420,7 +7410,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7463,7 +7453,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 21929-2026</t>
+          <t>A 75-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7477,10 +7467,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46150</v>
+        <v>45659</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7493,7 +7483,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7536,7 +7526,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 50209-2025</t>
+          <t>A 3795-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7550,10 +7540,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45943</v>
+        <v>45321</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7566,7 +7556,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7609,7 +7599,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 10767-2024</t>
+          <t>A 62299-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7623,10 +7613,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45369</v>
+        <v>44923</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7639,7 +7629,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7682,7 +7672,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 50337-2025</t>
+          <t>A 49781-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7696,10 +7686,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45944</v>
+        <v>45597</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7712,7 +7702,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7755,7 +7745,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 60103-2022</t>
+          <t>A 34909-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7769,10 +7759,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44909</v>
+        <v>45141</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7785,7 +7775,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7828,7 +7818,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 22620-2026</t>
+          <t>A 55033-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7842,10 +7832,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46155</v>
+        <v>45237</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7858,7 +7848,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7901,7 +7891,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 13515-2022</t>
+          <t>A 6354-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7915,10 +7905,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44648</v>
+        <v>45699</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7931,7 +7921,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.3</v>
+        <v>19.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7974,7 +7964,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 54526-2025</t>
+          <t>A 21363-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7988,10 +7978,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45965</v>
+        <v>45063</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8004,7 +7994,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8047,7 +8037,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 4077-2025</t>
+          <t>A 54526-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8061,10 +8051,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45684</v>
+        <v>45965</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8077,7 +8067,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8120,7 +8110,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 2402-2024</t>
+          <t>A 40896-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8134,10 +8124,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45310</v>
+        <v>44825</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8150,7 +8140,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.3</v>
+        <v>11.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8193,7 +8183,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 73158-2021</t>
+          <t>A 15658-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8207,10 +8197,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44550</v>
+        <v>45748</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8223,7 +8213,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8266,7 +8256,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 13883-2022</t>
+          <t>A 61884-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8280,10 +8270,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44650</v>
+        <v>45652</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8296,7 +8286,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6.1</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8339,7 +8329,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 56523-2025</t>
+          <t>A 15000-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8353,10 +8343,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45975</v>
+        <v>45015</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8369,7 +8359,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8412,7 +8402,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 57262-2025</t>
+          <t>A 65254-2021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8426,10 +8416,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45979</v>
+        <v>44515</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8442,7 +8432,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8485,7 +8475,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 10858-2026</t>
+          <t>A 46364-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8499,10 +8489,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46078</v>
+        <v>45582</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8515,7 +8505,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>8.5</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8558,7 +8548,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 57890-2025</t>
+          <t>A 45521-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8572,10 +8562,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45981</v>
+        <v>44845</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8588,7 +8578,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8631,7 +8621,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 57886-2025</t>
+          <t>A 6251-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8645,10 +8635,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45981</v>
+        <v>44965</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8661,7 +8651,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>8</v>
+        <v>15.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8704,7 +8694,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 57891-2025</t>
+          <t>A 56523-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8718,10 +8708,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45981</v>
+        <v>45975</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8734,7 +8724,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8777,7 +8767,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 59625-2023</t>
+          <t>A 5927-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8791,10 +8781,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45254</v>
+        <v>44598</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8807,7 +8797,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8850,7 +8840,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 59252-2025</t>
+          <t>A 24127-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8864,10 +8854,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45988</v>
+        <v>45456</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8880,7 +8870,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8923,7 +8913,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 15659-2025</t>
+          <t>A 23984-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8937,10 +8927,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45748</v>
+        <v>45456</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8953,7 +8943,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8996,7 +8986,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 60505-2025</t>
+          <t>A 24129-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9010,10 +9000,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45995</v>
+        <v>45456</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9026,7 +9016,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9069,7 +9059,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 16154-2024</t>
+          <t>A 57262-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9083,10 +9073,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45406</v>
+        <v>45979</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9099,7 +9089,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9142,7 +9132,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 16155-2024</t>
+          <t>A 57890-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9156,10 +9146,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45406</v>
+        <v>45981</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9172,7 +9162,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9215,7 +9205,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 61535-2025</t>
+          <t>A 23451-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9229,10 +9219,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46001</v>
+        <v>45076</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9244,8 +9234,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9288,7 +9283,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61539-2025</t>
+          <t>A 3886-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9302,10 +9297,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46001</v>
+        <v>45684</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9317,8 +9312,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9361,7 +9361,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 35969-2024</t>
+          <t>A 57886-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45533</v>
+        <v>45981</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9434,7 +9434,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 41554-2024</t>
+          <t>A 57891-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9448,10 +9448,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45560</v>
+        <v>45981</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9507,7 +9507,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 45983-2024</t>
+          <t>A 59252-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9521,10 +9521,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45580</v>
+        <v>45988</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9580,7 +9580,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 32826-2022</t>
+          <t>A 41554-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44784</v>
+        <v>45560</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9653,7 +9653,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 63884-2025</t>
+          <t>A 61046-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9667,10 +9667,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46020</v>
+        <v>45645</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9726,7 +9726,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 60-2026</t>
+          <t>A 35465-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9740,10 +9740,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46024</v>
+        <v>44798</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9799,7 +9799,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 53426-2022</t>
+          <t>A 60-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44879</v>
+        <v>46024</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>13.2</v>
+        <v>3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9872,7 +9872,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 13220-2022</t>
+          <t>A 65116-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9882,14 +9882,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44644</v>
+        <v>45287</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9945,7 +9945,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 19447-2025</t>
+          <t>A 60505-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9959,10 +9959,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45770</v>
+        <v>45995</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10018,7 +10018,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 64669-2023</t>
+          <t>A 30486-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45281</v>
+        <v>45829</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10091,7 +10091,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 16473-2023</t>
+          <t>A 31464-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10105,10 +10105,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45029</v>
+        <v>45833</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>5.5</v>
+        <v>1.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10164,7 +10164,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 16475-2023</t>
+          <t>A 59625-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10178,10 +10178,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45029</v>
+        <v>45254</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10237,7 +10237,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 53131-2022</t>
+          <t>A 61535-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44876</v>
+        <v>46001</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10310,7 +10310,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 1525-2026</t>
+          <t>A 61539-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10324,10 +10324,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46034</v>
+        <v>46001</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10383,7 +10383,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 3256-2026</t>
+          <t>A 1525-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10397,10 +10397,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46041</v>
+        <v>46034</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>8.1</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10456,7 +10456,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 27441-2026</t>
+          <t>A 19447-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46189</v>
+        <v>45770</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10529,7 +10529,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 64784-2023</t>
+          <t>A 131-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10543,10 +10543,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45282</v>
+        <v>45294</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10602,7 +10602,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 27586-2026</t>
+          <t>A 54087-2021</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10612,14 +10612,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46190</v>
+        <v>44470</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10631,8 +10631,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10675,7 +10680,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 3044-2022</t>
+          <t>A 3256-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10689,10 +10694,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44582</v>
+        <v>46041</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10705,7 +10710,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>8.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10748,7 +10753,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 15000-2023</t>
+          <t>A 63884-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10762,10 +10767,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45015</v>
+        <v>46020</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10778,7 +10783,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10821,7 +10826,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 6251-2023</t>
+          <t>A 27652-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10835,10 +10840,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44965</v>
+        <v>44743</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10851,7 +10856,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>15.4</v>
+        <v>9.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10894,7 +10899,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 7655-2026</t>
+          <t>A 45983-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10908,10 +10913,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46062</v>
+        <v>45580</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10924,7 +10929,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10967,7 +10972,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 19781-2025</t>
+          <t>A 5242-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10981,10 +10986,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45771</v>
+        <v>44594</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10997,7 +11002,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>6.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11040,7 +11045,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 23451-2023</t>
+          <t>A 46529-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11054,10 +11059,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45076</v>
+        <v>45582</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11069,13 +11074,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>11.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11118,7 +11118,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 60498-2024</t>
+          <t>A 16154-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11132,10 +11132,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45643</v>
+        <v>45406</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11191,7 +11191,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 5927-2022</t>
+          <t>A 16155-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11205,10 +11205,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44598</v>
+        <v>45406</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11264,7 +11264,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 32527-2024</t>
+          <t>A 57259-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45513</v>
+        <v>44895</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11293,13 +11293,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>8.699999999999999</v>
+        <v>2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11342,7 +11337,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 32541-2024</t>
+          <t>A 32804-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11356,10 +11351,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45513</v>
+        <v>46241</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11377,7 +11372,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11420,7 +11415,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 41893-2022</t>
+          <t>A 7655-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11434,10 +11429,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44830</v>
+        <v>46062</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11449,13 +11444,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11498,7 +11488,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 7783-2023</t>
+          <t>A 59879-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11512,10 +11502,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44973</v>
+        <v>45640</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11528,7 +11518,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11571,7 +11561,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 14211-2026</t>
+          <t>A 38535-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11585,10 +11575,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46099</v>
+        <v>46283</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11601,7 +11591,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11644,7 +11634,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 5242-2022</t>
+          <t>A 32826-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11658,10 +11648,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44594</v>
+        <v>44784</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11674,7 +11664,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11717,7 +11707,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 57918-2022</t>
+          <t>A 32797-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11731,10 +11721,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44900</v>
+        <v>46241</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11746,8 +11736,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11790,7 +11785,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 7781-2023</t>
+          <t>A 58330-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11804,10 +11799,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44973</v>
+        <v>44901</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11820,7 +11815,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11863,7 +11858,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 7921-2024</t>
+          <t>A 15704-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11877,10 +11872,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45350</v>
+        <v>45021</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11893,7 +11888,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11936,7 +11931,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 15592-2026</t>
+          <t>A 30796-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11950,10 +11945,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46106</v>
+        <v>45497</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11966,7 +11961,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12009,7 +12004,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 45521-2022</t>
+          <t>A 16152-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12023,10 +12018,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44845</v>
+        <v>45406</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12039,7 +12034,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12082,7 +12077,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 16030-2026</t>
+          <t>A 4906-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12096,10 +12091,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46108</v>
+        <v>45329</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12112,7 +12107,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>15.8</v>
+        <v>1.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12155,7 +12150,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 17126-2022</t>
+          <t>A 13883-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12169,10 +12164,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44677</v>
+        <v>44650</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12185,7 +12180,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12228,7 +12223,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 56116-2022</t>
+          <t>A 53401-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12242,10 +12237,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44889</v>
+        <v>44879</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12258,7 +12253,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12301,7 +12296,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 17485-2026</t>
+          <t>A 15181-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12311,14 +12306,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46120</v>
+        <v>45016</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12331,7 +12326,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12374,7 +12369,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 40896-2022</t>
+          <t>A 32527-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12388,10 +12383,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44825</v>
+        <v>45513</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12403,8 +12398,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>11.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12447,7 +12447,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 12329-2024</t>
+          <t>A 855-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12461,10 +12461,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45378</v>
+        <v>44931</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 37371-2023</t>
+          <t>A 32541-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12534,10 +12534,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45156</v>
+        <v>45513</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12549,8 +12549,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12593,7 +12598,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 33830-2026</t>
+          <t>A 47755-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12607,10 +12612,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46251</v>
+        <v>44854</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12623,7 +12628,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>8.9</v>
+        <v>2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12666,7 +12671,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 18840-2026</t>
+          <t>A 9821-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12680,10 +12685,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46129</v>
+        <v>44620</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12696,7 +12701,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12739,7 +12744,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 3074-2023</t>
+          <t>A 13220-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12753,10 +12758,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44946</v>
+        <v>44644</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12769,7 +12774,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12812,7 +12817,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 7730-2023</t>
+          <t>A 34671-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12826,10 +12831,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44973</v>
+        <v>45847</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12841,8 +12846,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12885,7 +12895,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 10494-2022</t>
+          <t>A 68400-2021</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12899,10 +12909,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44623</v>
+        <v>44529</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12915,7 +12925,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>13.3</v>
+        <v>2.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12958,7 +12968,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 19373-2026</t>
+          <t>A 14211-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12972,10 +12982,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46133</v>
+        <v>46099</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12988,7 +12998,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13031,7 +13041,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 46364-2024</t>
+          <t>A 25514-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13045,10 +13055,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45582</v>
+        <v>44732</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13061,7 +13071,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13104,7 +13114,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 33782-2026</t>
+          <t>A 10494-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13118,10 +13128,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46251</v>
+        <v>44623</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13134,7 +13144,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.7</v>
+        <v>13.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13177,7 +13187,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 33546-2022</t>
+          <t>A 15592-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13191,10 +13201,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44789</v>
+        <v>46106</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13207,7 +13217,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.5</v>
+        <v>8.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13250,7 +13260,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 9821-2022</t>
+          <t>A 13510-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13264,10 +13274,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44620</v>
+        <v>44648</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13280,7 +13290,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.5</v>
+        <v>17.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13323,7 +13333,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 38941-2023</t>
+          <t>A 10640-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13337,10 +13347,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45163</v>
+        <v>45721</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13353,7 +13363,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13396,7 +13406,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 30505-2026</t>
+          <t>A 52688-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13410,10 +13420,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46210</v>
+        <v>45610</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13426,7 +13436,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13469,7 +13479,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 49781-2024</t>
+          <t>A 16030-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13483,10 +13493,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45597</v>
+        <v>46108</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13499,7 +13509,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>5.7</v>
+        <v>15.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13542,7 +13552,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 61046-2024</t>
+          <t>A 47902-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13556,10 +13566,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45645</v>
+        <v>45589</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13572,7 +13582,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13615,7 +13625,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 3795-2024</t>
+          <t>A 36192-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13629,10 +13639,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45321</v>
+        <v>45867</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13645,7 +13655,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13688,7 +13698,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 42456-2024</t>
+          <t>A 17485-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13698,14 +13708,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45565</v>
+        <v>46120</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13718,7 +13728,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13761,7 +13771,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 30796-2024</t>
+          <t>A 2263-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13775,10 +13785,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45497</v>
+        <v>45310</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13790,8 +13800,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13834,7 +13849,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 36033-2026</t>
+          <t>A 37305-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13848,10 +13863,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46267</v>
+        <v>44808</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13864,7 +13879,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.4</v>
+        <v>9.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13907,7 +13922,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 16152-2024</t>
+          <t>A 18840-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13921,10 +13936,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45406</v>
+        <v>46129</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13937,7 +13952,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13980,7 +13995,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 47755-2022</t>
+          <t>A 60498-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13994,10 +14009,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44854</v>
+        <v>45643</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14010,7 +14025,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14053,7 +14068,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 10768-2024</t>
+          <t>A 19373-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14067,10 +14082,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45369</v>
+        <v>46133</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14083,7 +14098,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14126,7 +14141,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 62299-2022</t>
+          <t>A 37562-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14140,10 +14155,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44923</v>
+        <v>45541</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14156,7 +14171,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14199,7 +14214,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 11460-2024</t>
+          <t>A 15659-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14213,10 +14228,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45372</v>
+        <v>45748</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14229,7 +14244,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>5.3</v>
+        <v>0.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14272,7 +14287,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 55303-2022</t>
+          <t>A 20009-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14286,10 +14301,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44887</v>
+        <v>46136</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14302,7 +14317,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14345,7 +14360,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 36982-2024</t>
+          <t>A 19773-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14359,10 +14374,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45539</v>
+        <v>45771</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14375,7 +14390,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14418,7 +14433,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 855-2023</t>
+          <t>A 4307-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14432,10 +14447,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44931</v>
+        <v>45685</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14448,7 +14463,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14491,7 +14506,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 21363-2023</t>
+          <t>A 8273-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14505,10 +14520,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45063</v>
+        <v>45352</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14521,7 +14536,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14564,7 +14579,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 20667-2026</t>
+          <t>A 2402-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14578,10 +14593,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46141</v>
+        <v>45310</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14594,7 +14609,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.8</v>
+        <v>0.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14637,7 +14652,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 61884-2024</t>
+          <t>A 3272-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14651,10 +14666,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45652</v>
+        <v>45679</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14667,7 +14682,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14710,7 +14725,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 19773-2025</t>
+          <t>A 30773-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14724,10 +14739,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45771</v>
+        <v>45496</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14740,7 +14755,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14800,7 +14815,7 @@
         <v>45318</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14856,7 +14871,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 38535-2026</t>
+          <t>A 10767-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14870,10 +14885,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46283</v>
+        <v>45369</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14886,7 +14901,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14929,7 +14944,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 44708-2023</t>
+          <t>A 24432-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14939,14 +14954,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45190</v>
+        <v>44726</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14959,7 +14974,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15002,7 +15017,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 25514-2022</t>
+          <t>A 20500-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15016,10 +15031,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44732</v>
+        <v>46140</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15032,7 +15047,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15075,7 +15090,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 12967-2024</t>
+          <t>A 16487-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15089,10 +15104,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45385</v>
+        <v>45029</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15105,7 +15120,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15148,7 +15163,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 24432-2022</t>
+          <t>A 64669-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15158,14 +15173,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44726</v>
+        <v>45281</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15178,7 +15193,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15221,7 +15236,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 32804-2026</t>
+          <t>A 20501-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15235,10 +15250,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46241</v>
+        <v>46140</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15250,13 +15265,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15299,7 +15309,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 32797-2026</t>
+          <t>A 20152-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15313,10 +15323,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46241</v>
+        <v>46138</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15328,13 +15338,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15377,7 +15382,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 37658-2022</t>
+          <t>A 55303-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15391,10 +15396,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44810</v>
+        <v>44887</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15407,7 +15412,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15450,7 +15455,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 15658-2025</t>
+          <t>A 12329-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15464,10 +15469,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45748</v>
+        <v>45378</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15480,7 +15485,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15523,7 +15528,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 66960-2021</t>
+          <t>A 28224-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15537,10 +15542,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44522</v>
+        <v>45099</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15553,7 +15558,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15596,7 +15601,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 37305-2022</t>
+          <t>A 4077-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15610,10 +15615,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44808</v>
+        <v>45684</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15626,7 +15631,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>9.9</v>
+        <v>1.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15669,7 +15674,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 53193-2023</t>
+          <t>A 62294-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15683,10 +15688,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45229</v>
+        <v>44923</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15699,7 +15704,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15742,7 +15747,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 20955-2025</t>
+          <t>A 12264-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15756,10 +15761,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45777</v>
+        <v>45378</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15772,7 +15777,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15815,7 +15820,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 22016-2025</t>
+          <t>A 12266-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15829,10 +15834,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45784</v>
+        <v>45378</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15845,7 +15850,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15888,7 +15893,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37801-2024</t>
+          <t>A 44708-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15898,14 +15903,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45543</v>
+        <v>45190</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15918,7 +15923,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15961,7 +15966,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 11837-2025</t>
+          <t>A 21929-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15975,10 +15980,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45728</v>
+        <v>46150</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15991,7 +15996,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16034,7 +16039,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 15645-2024</t>
+          <t>A 20955-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16048,10 +16053,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45404</v>
+        <v>45777</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16064,7 +16069,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16107,7 +16112,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 24559-2025</t>
+          <t>A 22620-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16121,10 +16126,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45798</v>
+        <v>46155</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16137,7 +16142,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16180,7 +16185,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 49062-2024</t>
+          <t>A 10858-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16194,10 +16199,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45594</v>
+        <v>46078</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16210,7 +16215,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16253,7 +16258,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 45519-2023</t>
+          <t>A 27441-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16267,10 +16272,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45194</v>
+        <v>46189</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16283,7 +16288,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16326,7 +16331,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 27201-2025</t>
+          <t>A 27586-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16336,14 +16341,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45812</v>
+        <v>46190</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16356,7 +16361,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16399,7 +16404,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 30486-2025</t>
+          <t>A 33782-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16413,10 +16418,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45829</v>
+        <v>46251</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16429,7 +16434,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16472,7 +16477,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 31464-2025</t>
+          <t>A 33830-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16486,10 +16491,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45833</v>
+        <v>46251</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16502,7 +16507,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.4</v>
+        <v>8.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16545,7 +16550,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 34671-2025</t>
+          <t>A 30505-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16559,10 +16564,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45847</v>
+        <v>46210</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16574,13 +16579,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16623,7 +16623,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 10640-2025</t>
+          <t>A 36033-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16637,10 +16637,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45721</v>
+        <v>46267</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 13510-2022</t>
+          <t>A 20667-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16710,10 +16710,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44648</v>
+        <v>46141</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>17.6</v>
+        <v>3.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16766,27 +16766,27 @@
       </c>
       <c r="V218" s="2" t="inlineStr"/>
     </row>
-    <row r="219" ht="15" customHeight="1">
+    <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 36192-2025</t>
+          <t>S 643-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45867</v>
+        <v>46090</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -16838,79 +16838,6 @@
         <v>0</v>
       </c>
       <c r="V219" s="2" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>S 643-2026</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D220" s="1" t="n">
-        <v>46090</v>
-      </c>
-      <c r="E220" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="I220" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J220" t="n">
-        <v>0</v>
-      </c>
-      <c r="K220" t="n">
-        <v>0</v>
-      </c>
-      <c r="L220" t="n">
-        <v>0</v>
-      </c>
-      <c r="M220" t="n">
-        <v>0</v>
-      </c>
-      <c r="N220" t="n">
-        <v>0</v>
-      </c>
-      <c r="O220" t="n">
-        <v>0</v>
-      </c>
-      <c r="P220" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
-      <c r="R220" t="n">
-        <v>0</v>
-      </c>
-      <c r="S220" t="n">
-        <v>0</v>
-      </c>
-      <c r="T220" t="n">
-        <v>0</v>
-      </c>
-      <c r="U220" t="n">
-        <v>0</v>
-      </c>
-      <c r="V220" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45386</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44876</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1296-2022</t>
+          <t>A 20737-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44572</v>
+        <v>44701</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1744,7 +1744,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 20737-2022</t>
+          <t>A 1296-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1758,10 +1758,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44701</v>
+        <v>44572</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1834,7 +1834,7 @@
         <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44608</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44622</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44811</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44686</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 22016-2025</t>
+          <t>A 52687-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45784</v>
+        <v>44466</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 52687-2021</t>
+          <t>A 67535-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44466</v>
+        <v>44524</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2649,8 +2649,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2693,7 +2698,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1295-2022</t>
+          <t>A 66971-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2707,10 +2712,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44572</v>
+        <v>44522</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2723,7 +2728,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2766,7 +2771,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 67535-2021</t>
+          <t>A 318-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2780,10 +2785,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44524</v>
+        <v>44565</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2795,13 +2800,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>8.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 66971-2021</t>
+          <t>A 1295-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44522</v>
+        <v>44572</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2917,7 +2917,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 318-2022</t>
+          <t>A 62294-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44565</v>
+        <v>44923</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53193-2023</t>
+          <t>A 12264-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45229</v>
+        <v>45378</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 39611-2022</t>
+          <t>A 12266-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44818</v>
+        <v>45378</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3092,13 +3092,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3141,7 +3136,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 29300-2024</t>
+          <t>A 6354-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3155,10 +3150,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45483</v>
+        <v>45699</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3171,7 +3166,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>19.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3214,7 +3209,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7628-2022</t>
+          <t>A 24127-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3228,10 +3223,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44607</v>
+        <v>45456</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3244,7 +3239,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3287,7 +3282,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33546-2022</t>
+          <t>A 3886-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3301,10 +3296,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44789</v>
+        <v>45684</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3316,8 +3311,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 53426-2022</t>
+          <t>A 39611-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44879</v>
+        <v>44818</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3389,8 +3389,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>13.2</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3433,7 +3438,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62266-2022</t>
+          <t>A 18612-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3447,10 +3452,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44923</v>
+        <v>45763</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3463,7 +3468,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3506,7 +3511,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 39116-2022</t>
+          <t>A 23984-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3520,10 +3525,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44817</v>
+        <v>45456</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3536,7 +3541,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3579,7 +3584,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11123-2024</t>
+          <t>A 65254-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3593,10 +3598,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45371</v>
+        <v>44515</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3609,7 +3614,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3652,7 +3657,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10768-2024</t>
+          <t>A 34909-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3666,10 +3671,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45369</v>
+        <v>45141</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3682,7 +3687,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3725,7 +3730,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10777-2024</t>
+          <t>A 65116-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3735,14 +3740,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45369</v>
+        <v>45287</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3755,7 +3760,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3798,7 +3803,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57918-2022</t>
+          <t>A 29300-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3812,10 +3817,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44900</v>
+        <v>45483</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3828,7 +3833,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3871,7 +3876,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 41893-2022</t>
+          <t>A 15704-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3885,10 +3890,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44830</v>
+        <v>45021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3900,13 +3905,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37658-2022</t>
+          <t>A 16487-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44810</v>
+        <v>45029</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37801-2024</t>
+          <t>A 15181-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4032,14 +4032,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45543</v>
+        <v>45016</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4095,7 +4095,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 53227-2021</t>
+          <t>A 11123-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44468</v>
+        <v>45371</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18612-2025</t>
+          <t>A 34435-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45763</v>
+        <v>45525</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4241,7 +4241,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7730-2023</t>
+          <t>A 55033-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44973</v>
+        <v>45237</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15648-2025</t>
+          <t>A 53401-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45748</v>
+        <v>44879</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24559-2025</t>
+          <t>A 37562-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45798</v>
+        <v>45541</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11837-2025</t>
+          <t>A 46533-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45728</v>
+        <v>45582</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 21979-2025</t>
+          <t>A 27652-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45784</v>
+        <v>44743</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>9.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15645-2024</t>
+          <t>A 7628-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45404</v>
+        <v>44607</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 68454-2021</t>
+          <t>A 59879-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44529</v>
+        <v>45640</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60103-2022</t>
+          <t>A 24129-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44909</v>
+        <v>45456</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3044-2022</t>
+          <t>A 11991-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44582</v>
+        <v>44635</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7781-2023</t>
+          <t>A 58330-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44973</v>
+        <v>44901</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56116-2022</t>
+          <t>A 4906-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44889</v>
+        <v>45329</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 73158-2021</t>
+          <t>A 13119-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44550</v>
+        <v>45002</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 64784-2023</t>
+          <t>A 47902-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45282</v>
+        <v>45589</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 36982-2024</t>
+          <t>A 68454-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45539</v>
+        <v>44529</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38941-2023</t>
+          <t>A 57259-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45163</v>
+        <v>44895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 16473-2023</t>
+          <t>A 2263-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45029</v>
+        <v>45310</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5365,8 +5365,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5409,7 +5414,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16475-2023</t>
+          <t>A 36192-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5423,10 +5428,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45029</v>
+        <v>45867</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5439,7 +5444,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5482,7 +5487,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34435-2024</t>
+          <t>A 10777-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5496,10 +5501,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45525</v>
+        <v>45369</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5512,7 +5517,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5555,7 +5560,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 66960-2021</t>
+          <t>A 19373-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5569,10 +5574,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44522</v>
+        <v>46133</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5585,7 +5590,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5628,7 +5633,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 42456-2024</t>
+          <t>A 20009-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5642,10 +5647,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45565</v>
+        <v>46136</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5701,7 +5706,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19781-2025</t>
+          <t>A 15648-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5715,10 +5720,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45771</v>
+        <v>45748</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5731,7 +5736,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5774,7 +5779,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12967-2024</t>
+          <t>A 21979-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5788,10 +5793,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45385</v>
+        <v>45784</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5804,7 +5809,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5847,7 +5852,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11991-2022</t>
+          <t>A 53227-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5861,10 +5866,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44635</v>
+        <v>44468</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5877,7 +5882,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5920,7 +5925,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 45519-2023</t>
+          <t>A 8273-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5934,10 +5939,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45194</v>
+        <v>45352</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5950,7 +5955,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5993,7 +5998,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37371-2023</t>
+          <t>A 52688-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6007,10 +6012,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45156</v>
+        <v>45610</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6023,7 +6028,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6066,7 +6071,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 49062-2024</t>
+          <t>A 46529-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6080,10 +6085,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45594</v>
+        <v>45582</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6096,7 +6101,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>11.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6139,7 +6144,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3074-2023</t>
+          <t>A 131-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6153,10 +6158,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44946</v>
+        <v>45294</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6169,7 +6174,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6212,7 +6217,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13119-2023</t>
+          <t>A 75-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6226,10 +6231,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45002</v>
+        <v>45659</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6242,7 +6247,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6285,7 +6290,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35969-2024</t>
+          <t>A 68400-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6299,10 +6304,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45533</v>
+        <v>44529</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6315,7 +6320,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6358,7 +6363,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 27201-2025</t>
+          <t>A 54087-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6372,10 +6377,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45812</v>
+        <v>44470</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6387,8 +6392,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6431,7 +6441,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 47708-2025</t>
+          <t>A 35465-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6445,10 +6455,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45931</v>
+        <v>44798</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6461,7 +6471,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6504,7 +6514,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48790-2025</t>
+          <t>A 3272-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6518,10 +6528,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45937</v>
+        <v>45679</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6534,7 +6544,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6577,7 +6587,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 48791-2025</t>
+          <t>A 39116-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6591,10 +6601,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45937</v>
+        <v>44817</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6607,7 +6617,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6650,7 +6660,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 48787-2025</t>
+          <t>A 62266-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6664,10 +6674,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45937</v>
+        <v>44923</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6680,7 +6690,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6723,7 +6733,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 7921-2024</t>
+          <t>A 48788-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6737,10 +6747,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45350</v>
+        <v>45937</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6753,7 +6763,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6796,7 +6806,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 48788-2025</t>
+          <t>A 48790-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6813,7 +6823,7 @@
         <v>45937</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6826,7 +6836,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6869,7 +6879,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 17126-2022</t>
+          <t>A 47708-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6883,10 +6893,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44677</v>
+        <v>45931</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6899,7 +6909,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6942,7 +6952,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50337-2025</t>
+          <t>A 48787-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6956,10 +6966,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45944</v>
+        <v>45937</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6972,7 +6982,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7015,7 +7025,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50209-2025</t>
+          <t>A 48791-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7029,10 +7039,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45943</v>
+        <v>45937</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7045,7 +7055,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7088,7 +7098,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 46533-2024</t>
+          <t>A 10767-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7102,10 +7112,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45582</v>
+        <v>45369</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7118,7 +7128,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7161,7 +7171,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 53131-2022</t>
+          <t>A 50209-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7175,10 +7185,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44876</v>
+        <v>45943</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7191,7 +7201,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7234,7 +7244,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 13515-2022</t>
+          <t>A 60103-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7248,10 +7258,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44648</v>
+        <v>44909</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7264,7 +7274,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7307,7 +7317,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 7783-2023</t>
+          <t>A 50337-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7321,10 +7331,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44973</v>
+        <v>45944</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7337,7 +7347,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7380,7 +7390,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 11460-2024</t>
+          <t>A 20152-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7394,10 +7404,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45372</v>
+        <v>46138</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7410,7 +7420,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7453,7 +7463,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 75-2025</t>
+          <t>A 13515-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7467,10 +7477,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45659</v>
+        <v>44648</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7483,7 +7493,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7526,7 +7536,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3795-2024</t>
+          <t>A 30773-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7540,10 +7550,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45321</v>
+        <v>45496</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7556,7 +7566,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7599,7 +7609,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 62299-2022</t>
+          <t>A 4077-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7613,10 +7623,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44923</v>
+        <v>45684</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7629,7 +7639,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7672,7 +7682,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 49781-2024</t>
+          <t>A 2402-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7686,10 +7696,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45597</v>
+        <v>45310</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7702,7 +7712,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.7</v>
+        <v>0.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7745,7 +7755,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 34909-2023</t>
+          <t>A 73158-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7759,10 +7769,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45141</v>
+        <v>44550</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7775,7 +7785,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7818,7 +7828,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 55033-2023</t>
+          <t>A 13883-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7832,10 +7842,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45237</v>
+        <v>44650</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7848,7 +7858,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7891,7 +7901,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 6354-2025</t>
+          <t>A 28224-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7905,10 +7915,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45699</v>
+        <v>45099</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7921,7 +7931,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>19.3</v>
+        <v>4.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7964,7 +7974,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21363-2023</t>
+          <t>A 4307-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7978,10 +7988,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45063</v>
+        <v>45685</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7994,7 +8004,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8054,7 +8064,7 @@
         <v>45965</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8110,7 +8120,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 40896-2022</t>
+          <t>A 20500-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8124,10 +8134,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44825</v>
+        <v>46140</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8140,7 +8150,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>11.3</v>
+        <v>2.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8183,7 +8193,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 15658-2025</t>
+          <t>A 56523-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8197,10 +8207,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45748</v>
+        <v>45975</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8213,7 +8223,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8256,7 +8266,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 61884-2024</t>
+          <t>A 57262-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8270,10 +8280,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45652</v>
+        <v>45979</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8286,7 +8296,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8329,7 +8339,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 15000-2023</t>
+          <t>A 59625-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8343,10 +8353,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45015</v>
+        <v>45254</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8359,7 +8369,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8402,7 +8412,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 65254-2021</t>
+          <t>A 57890-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8416,10 +8426,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44515</v>
+        <v>45981</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8432,7 +8442,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8475,7 +8485,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 46364-2024</t>
+          <t>A 57886-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8489,10 +8499,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45582</v>
+        <v>45981</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8505,7 +8515,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8548,7 +8558,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 45521-2022</t>
+          <t>A 57891-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8562,10 +8572,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44845</v>
+        <v>45981</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8578,7 +8588,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8621,7 +8631,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 6251-2023</t>
+          <t>A 15659-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8635,10 +8645,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44965</v>
+        <v>45748</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8651,7 +8661,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>15.4</v>
+        <v>0.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8694,7 +8704,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56523-2025</t>
+          <t>A 20501-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8708,10 +8718,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45975</v>
+        <v>46140</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8724,7 +8734,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8767,7 +8777,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 5927-2022</t>
+          <t>A 16154-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8781,10 +8791,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44598</v>
+        <v>45406</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8797,7 +8807,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8840,7 +8850,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 24127-2024</t>
+          <t>A 16155-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8854,10 +8864,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45456</v>
+        <v>45406</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8870,7 +8880,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8913,7 +8923,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 23984-2024</t>
+          <t>A 59252-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8927,10 +8937,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45456</v>
+        <v>45988</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8943,7 +8953,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8986,7 +8996,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 24129-2024</t>
+          <t>A 21929-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9000,10 +9010,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45456</v>
+        <v>46150</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9016,7 +9026,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9059,7 +9069,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 57262-2025</t>
+          <t>A 35969-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9073,10 +9083,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45979</v>
+        <v>45533</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9089,7 +9099,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9132,7 +9142,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 57890-2025</t>
+          <t>A 60505-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9146,10 +9156,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45981</v>
+        <v>45995</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9162,7 +9172,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9205,7 +9215,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 23451-2023</t>
+          <t>A 61535-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9219,10 +9229,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45076</v>
+        <v>46001</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9234,13 +9244,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9283,7 +9288,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 3886-2025</t>
+          <t>A 61539-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9297,10 +9302,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45684</v>
+        <v>46001</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9312,13 +9317,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9361,7 +9361,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 57886-2025</t>
+          <t>A 22620-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45981</v>
+        <v>46155</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9434,7 +9434,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 57891-2025</t>
+          <t>A 41554-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9448,10 +9448,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45981</v>
+        <v>45560</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9507,7 +9507,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 59252-2025</t>
+          <t>A 45983-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9521,10 +9521,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45988</v>
+        <v>45580</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9580,7 +9580,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 41554-2024</t>
+          <t>A 32826-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45560</v>
+        <v>44784</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9653,7 +9653,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 61046-2024</t>
+          <t>A 53426-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9667,10 +9667,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45645</v>
+        <v>44879</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.3</v>
+        <v>13.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9726,7 +9726,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 35465-2022</t>
+          <t>A 13220-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9740,10 +9740,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44798</v>
+        <v>44644</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9799,7 +9799,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 60-2026</t>
+          <t>A 19447-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46024</v>
+        <v>45770</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9872,7 +9872,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 65116-2023</t>
+          <t>A 64669-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9882,14 +9882,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45287</v>
+        <v>45281</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9945,7 +9945,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 60505-2025</t>
+          <t>A 63884-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9959,10 +9959,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45995</v>
+        <v>46020</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10018,7 +10018,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 30486-2025</t>
+          <t>A 16473-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45829</v>
+        <v>45029</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10091,7 +10091,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31464-2025</t>
+          <t>A 16475-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10105,10 +10105,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45833</v>
+        <v>45029</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10164,7 +10164,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 59625-2023</t>
+          <t>A 53131-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10178,10 +10178,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45254</v>
+        <v>44876</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10237,7 +10237,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61535-2025</t>
+          <t>A 60-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46001</v>
+        <v>46024</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10310,7 +10310,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 61539-2025</t>
+          <t>A 1525-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10324,10 +10324,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46001</v>
+        <v>46034</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10383,7 +10383,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 1525-2026</t>
+          <t>A 64784-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10397,10 +10397,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46034</v>
+        <v>45282</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10456,7 +10456,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 19447-2025</t>
+          <t>A 3256-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45770</v>
+        <v>46041</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.9</v>
+        <v>8.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10529,7 +10529,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 131-2024</t>
+          <t>A 3044-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10543,10 +10543,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45294</v>
+        <v>44582</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.5</v>
+        <v>1.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10602,7 +10602,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 54087-2021</t>
+          <t>A 15000-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44470</v>
+        <v>45015</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10631,13 +10631,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10680,7 +10675,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 3256-2026</t>
+          <t>A 6251-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10694,10 +10689,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46041</v>
+        <v>44965</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10710,7 +10705,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>8.1</v>
+        <v>15.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10753,7 +10748,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 63884-2025</t>
+          <t>A 10858-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10767,10 +10762,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46020</v>
+        <v>46078</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10783,7 +10778,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.9</v>
+        <v>8.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10826,7 +10821,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 27652-2022</t>
+          <t>A 19781-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10840,10 +10835,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44743</v>
+        <v>45771</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10856,7 +10851,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10899,7 +10894,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 45983-2024</t>
+          <t>A 23451-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10913,10 +10908,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45580</v>
+        <v>45076</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10928,8 +10923,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10972,7 +10972,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 5242-2022</t>
+          <t>A 7655-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10986,10 +10986,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44594</v>
+        <v>46062</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11045,7 +11045,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 46529-2024</t>
+          <t>A 60498-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11059,10 +11059,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45582</v>
+        <v>45643</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11118,7 +11118,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 16154-2024</t>
+          <t>A 5927-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11132,10 +11132,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45406</v>
+        <v>44598</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11191,7 +11191,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 16155-2024</t>
+          <t>A 41893-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11205,10 +11205,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45406</v>
+        <v>44830</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11218,6 +11218,11 @@
       <c r="G143" t="inlineStr">
         <is>
           <t>TROLLHÄTTAN</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I143" t="n">
@@ -11264,7 +11269,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 57259-2022</t>
+          <t>A 7783-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11278,10 +11283,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44895</v>
+        <v>44973</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11294,7 +11299,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11337,7 +11342,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 32804-2026</t>
+          <t>A 5242-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11351,10 +11356,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46241</v>
+        <v>44594</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11366,13 +11371,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11415,7 +11415,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 7655-2026</t>
+          <t>A 57918-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11429,10 +11429,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46062</v>
+        <v>44900</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11488,7 +11488,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 59879-2024</t>
+          <t>A 32527-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11502,10 +11502,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45640</v>
+        <v>45513</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11517,8 +11517,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11561,7 +11566,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 38535-2026</t>
+          <t>A 32541-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11575,10 +11580,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46283</v>
+        <v>45513</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11590,8 +11595,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11634,7 +11644,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 32826-2022</t>
+          <t>A 7781-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11648,10 +11658,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44784</v>
+        <v>44973</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11664,7 +11674,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11707,7 +11717,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 32797-2026</t>
+          <t>A 7921-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11721,10 +11731,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46241</v>
+        <v>45350</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11736,13 +11746,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11785,7 +11790,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 58330-2022</t>
+          <t>A 45521-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11799,10 +11804,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44901</v>
+        <v>44845</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11815,7 +11820,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11858,7 +11863,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 15704-2023</t>
+          <t>A 14211-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11872,10 +11877,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45021</v>
+        <v>46099</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11888,7 +11893,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11931,7 +11936,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 30796-2024</t>
+          <t>A 17126-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11945,10 +11950,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45497</v>
+        <v>44677</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11961,7 +11966,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12004,7 +12009,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 16152-2024</t>
+          <t>A 15592-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12018,10 +12023,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45406</v>
+        <v>46106</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12034,7 +12039,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.8</v>
+        <v>8.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12077,7 +12082,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 4906-2024</t>
+          <t>A 56116-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12091,10 +12096,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45329</v>
+        <v>44889</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12107,7 +12112,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12150,7 +12155,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 13883-2022</t>
+          <t>A 16030-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12164,10 +12169,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44650</v>
+        <v>46108</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12180,7 +12185,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6.1</v>
+        <v>15.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12223,7 +12228,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 53401-2022</t>
+          <t>A 27441-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12237,10 +12242,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44879</v>
+        <v>46189</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12253,7 +12258,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12296,7 +12301,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 15181-2023</t>
+          <t>A 40896-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12310,10 +12315,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45016</v>
+        <v>44825</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12326,7 +12331,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>4.9</v>
+        <v>11.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12369,7 +12374,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 32527-2024</t>
+          <t>A 12329-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12383,10 +12388,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45513</v>
+        <v>45378</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12398,13 +12403,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>8.699999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12447,7 +12447,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 855-2023</t>
+          <t>A 37371-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12461,10 +12461,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44931</v>
+        <v>45156</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 32541-2024</t>
+          <t>A 27586-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12530,14 +12530,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45513</v>
+        <v>46190</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12549,13 +12549,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12598,7 +12593,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 47755-2022</t>
+          <t>A 17485-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12608,14 +12603,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44854</v>
+        <v>46120</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12628,7 +12623,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12671,7 +12666,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 9821-2022</t>
+          <t>A 3074-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12685,10 +12680,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44620</v>
+        <v>44946</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12701,7 +12696,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12744,7 +12739,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 13220-2022</t>
+          <t>A 7730-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12758,10 +12753,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44644</v>
+        <v>44973</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12817,7 +12812,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 34671-2025</t>
+          <t>A 10494-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12831,10 +12826,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45847</v>
+        <v>44623</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12846,13 +12841,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>2.6</v>
+        <v>13.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12895,7 +12885,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 68400-2021</t>
+          <t>A 46364-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12909,10 +12899,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44529</v>
+        <v>45582</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12925,7 +12915,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12968,7 +12958,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 14211-2026</t>
+          <t>A 18840-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12982,10 +12972,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46099</v>
+        <v>46129</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12998,7 +12988,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13041,7 +13031,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 25514-2022</t>
+          <t>A 33546-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13055,10 +13045,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44732</v>
+        <v>44789</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13071,7 +13061,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13114,7 +13104,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 10494-2022</t>
+          <t>A 9821-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13128,10 +13118,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44623</v>
+        <v>44620</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13144,7 +13134,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>13.3</v>
+        <v>2.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13187,7 +13177,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 15592-2026</t>
+          <t>A 38941-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13201,10 +13191,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46106</v>
+        <v>45163</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13217,7 +13207,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>8.4</v>
+        <v>1.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13260,7 +13250,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 13510-2022</t>
+          <t>A 49781-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13274,10 +13264,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44648</v>
+        <v>45597</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13290,7 +13280,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>17.6</v>
+        <v>5.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13333,7 +13323,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 10640-2025</t>
+          <t>A 61046-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13347,10 +13337,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45721</v>
+        <v>45645</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13363,7 +13353,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13406,7 +13396,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 52688-2024</t>
+          <t>A 3795-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13420,10 +13410,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45610</v>
+        <v>45321</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13479,7 +13469,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 16030-2026</t>
+          <t>A 33830-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13493,10 +13483,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46108</v>
+        <v>46251</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13509,7 +13499,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>15.8</v>
+        <v>8.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13552,7 +13542,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 47902-2024</t>
+          <t>A 42456-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13566,10 +13556,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45589</v>
+        <v>45565</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13582,7 +13572,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13625,7 +13615,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 36192-2025</t>
+          <t>A 33782-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13639,10 +13629,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45867</v>
+        <v>46251</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13655,7 +13645,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13698,7 +13688,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 17485-2026</t>
+          <t>A 30505-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13708,14 +13698,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46120</v>
+        <v>46210</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13728,7 +13718,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13771,7 +13761,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 2263-2024</t>
+          <t>A 30796-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13785,10 +13775,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45310</v>
+        <v>45497</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13800,13 +13790,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13849,7 +13834,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 37305-2022</t>
+          <t>A 16152-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13863,10 +13848,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44808</v>
+        <v>45406</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13879,7 +13864,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>9.9</v>
+        <v>0.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13922,7 +13907,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 18840-2026</t>
+          <t>A 47755-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13936,10 +13921,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46129</v>
+        <v>44854</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13952,7 +13937,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13995,7 +13980,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 60498-2024</t>
+          <t>A 10768-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14009,10 +13994,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45643</v>
+        <v>45369</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14025,7 +14010,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14068,7 +14053,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 19373-2026</t>
+          <t>A 62299-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14082,10 +14067,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46133</v>
+        <v>44923</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14098,7 +14083,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14141,7 +14126,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 37562-2024</t>
+          <t>A 11460-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14155,10 +14140,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45541</v>
+        <v>45372</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14171,7 +14156,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14214,7 +14199,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 15659-2025</t>
+          <t>A 55303-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14228,10 +14213,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45748</v>
+        <v>44887</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14244,7 +14229,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14287,7 +14272,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 20009-2026</t>
+          <t>A 36982-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14301,10 +14286,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46136</v>
+        <v>45539</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14317,7 +14302,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14360,7 +14345,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 19773-2025</t>
+          <t>A 855-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14374,10 +14359,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45771</v>
+        <v>44931</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14390,7 +14375,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14433,7 +14418,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 4307-2025</t>
+          <t>A 21363-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14447,10 +14432,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45685</v>
+        <v>45063</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14463,7 +14448,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14506,7 +14491,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 8273-2024</t>
+          <t>A 36033-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14520,10 +14505,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45352</v>
+        <v>46267</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14536,7 +14521,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14579,7 +14564,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 2402-2024</t>
+          <t>A 61884-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14593,10 +14578,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45310</v>
+        <v>45652</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14609,7 +14594,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14652,7 +14637,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 3272-2025</t>
+          <t>A 19773-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14666,10 +14651,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45679</v>
+        <v>45771</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14682,7 +14667,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14725,7 +14710,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 30773-2024</t>
+          <t>A 3399-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14739,10 +14724,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45496</v>
+        <v>45318</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14755,7 +14740,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14798,7 +14783,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 3399-2024</t>
+          <t>A 44708-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14812,10 +14797,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45318</v>
+        <v>45190</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14828,7 +14813,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14871,7 +14856,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 10767-2024</t>
+          <t>A 25514-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14885,10 +14870,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45369</v>
+        <v>44732</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14944,7 +14929,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 24432-2022</t>
+          <t>A 12967-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14954,14 +14939,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44726</v>
+        <v>45385</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14974,7 +14959,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15017,7 +15002,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 20500-2026</t>
+          <t>A 24432-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15027,14 +15012,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46140</v>
+        <v>44726</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15047,7 +15032,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15090,7 +15075,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 16487-2023</t>
+          <t>A 20667-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15104,10 +15089,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45029</v>
+        <v>46141</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15120,7 +15105,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15163,7 +15148,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 64669-2023</t>
+          <t>A 37658-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15177,10 +15162,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45281</v>
+        <v>44810</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15193,7 +15178,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15236,7 +15221,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 20501-2026</t>
+          <t>A 15658-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15250,10 +15235,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46140</v>
+        <v>45748</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15266,7 +15251,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15309,7 +15294,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 20152-2026</t>
+          <t>A 66960-2021</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15323,10 +15308,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46138</v>
+        <v>44522</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15339,7 +15324,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15382,7 +15367,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 55303-2022</t>
+          <t>A 37305-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15396,10 +15381,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44887</v>
+        <v>44808</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15412,7 +15397,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.5</v>
+        <v>9.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15455,7 +15440,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 12329-2024</t>
+          <t>A 53193-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15469,10 +15454,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45378</v>
+        <v>45229</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15485,7 +15470,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15528,7 +15513,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 28224-2023</t>
+          <t>A 20955-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15542,10 +15527,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45099</v>
+        <v>45777</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15558,7 +15543,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15601,7 +15586,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 4077-2025</t>
+          <t>A 38535-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15615,10 +15600,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45684</v>
+        <v>46283</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15631,7 +15616,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15674,7 +15659,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 62294-2022</t>
+          <t>A 22016-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15688,10 +15673,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44923</v>
+        <v>45784</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15704,7 +15689,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15747,7 +15732,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 12264-2024</t>
+          <t>A 32804-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15761,10 +15746,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45378</v>
+        <v>46241</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15776,8 +15761,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15820,7 +15810,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 12266-2024</t>
+          <t>A 32797-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15834,10 +15824,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45378</v>
+        <v>46241</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15849,8 +15839,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15893,7 +15888,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 44708-2023</t>
+          <t>A 37801-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15903,14 +15898,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45190</v>
+        <v>45543</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15923,7 +15918,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15966,7 +15961,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 21929-2026</t>
+          <t>A 11837-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15980,10 +15975,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46150</v>
+        <v>45728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15996,7 +15991,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16039,7 +16034,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 20955-2025</t>
+          <t>A 15645-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16053,10 +16048,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45777</v>
+        <v>45404</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16069,7 +16064,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16112,7 +16107,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 22620-2026</t>
+          <t>A 24559-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16126,10 +16121,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46155</v>
+        <v>45798</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16142,7 +16137,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16185,7 +16180,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 10858-2026</t>
+          <t>A 49062-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16199,10 +16194,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46078</v>
+        <v>45594</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16215,7 +16210,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16258,7 +16253,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 27441-2026</t>
+          <t>A 45519-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16272,10 +16267,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46189</v>
+        <v>45194</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16288,7 +16283,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16331,7 +16326,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 27586-2026</t>
+          <t>A 27201-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16341,14 +16336,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46190</v>
+        <v>45812</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16361,7 +16356,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16404,7 +16399,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 33782-2026</t>
+          <t>A 30486-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16418,10 +16413,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46251</v>
+        <v>45829</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16434,7 +16429,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16477,7 +16472,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 33830-2026</t>
+          <t>A 31464-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16491,10 +16486,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46251</v>
+        <v>45833</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16507,7 +16502,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>8.9</v>
+        <v>1.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16550,7 +16545,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 30505-2026</t>
+          <t>A 34671-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16564,10 +16559,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46210</v>
+        <v>45847</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16579,8 +16574,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16623,7 +16623,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 36033-2026</t>
+          <t>A 10640-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16637,10 +16637,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46267</v>
+        <v>45721</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 20667-2026</t>
+          <t>A 13510-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16710,10 +16710,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46141</v>
+        <v>44648</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>3.8</v>
+        <v>17.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16786,7 +16786,7 @@
         <v>46090</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>

--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE219"/>
+  <dimension ref="A1:AE218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45386</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44876</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 20737-2022</t>
+          <t>A 1296-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44701</v>
+        <v>44572</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1744,7 +1744,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1296-2022</t>
+          <t>A 20737-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1758,10 +1758,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44572</v>
+        <v>44701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1834,7 +1834,7 @@
         <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44608</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44622</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44811</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44686</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>44466</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44524</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44522</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44565</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44572</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62294-2022</t>
+          <t>A 33546-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44923</v>
+        <v>44789</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12264-2024</t>
+          <t>A 11123-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45378</v>
+        <v>45371</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12266-2024</t>
+          <t>A 10768-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45378</v>
+        <v>45369</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 6354-2025</t>
+          <t>A 10777-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45699</v>
+        <v>45369</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>19.3</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24127-2024</t>
+          <t>A 37658-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45456</v>
+        <v>44810</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3886-2025</t>
+          <t>A 37801-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3292,14 +3292,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45684</v>
+        <v>45543</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3311,13 +3311,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3360,7 +3355,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 39611-2022</t>
+          <t>A 63884-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3374,10 +3369,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44818</v>
+        <v>46020</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3389,13 +3384,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3438,7 +3428,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18612-2025</t>
+          <t>A 60103-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3452,10 +3442,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45763</v>
+        <v>44909</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3468,7 +3458,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3511,7 +3501,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23984-2024</t>
+          <t>A 60-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3525,10 +3515,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45456</v>
+        <v>46024</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3541,7 +3531,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3584,7 +3574,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 65254-2021</t>
+          <t>A 3044-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3598,10 +3588,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44515</v>
+        <v>44582</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3614,7 +3604,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3657,7 +3647,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34909-2023</t>
+          <t>A 56116-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3671,10 +3661,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45141</v>
+        <v>44889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3687,7 +3677,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3730,7 +3720,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 65116-2023</t>
+          <t>A 64784-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3740,14 +3730,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45287</v>
+        <v>45282</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3760,7 +3750,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3803,7 +3793,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 29300-2024</t>
+          <t>A 36982-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3817,10 +3807,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45483</v>
+        <v>45539</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3833,7 +3823,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3876,7 +3866,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15704-2023</t>
+          <t>A 24559-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3890,10 +3880,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45021</v>
+        <v>45798</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3906,7 +3896,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3949,7 +3939,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16487-2023</t>
+          <t>A 11837-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3963,10 +3953,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45029</v>
+        <v>45728</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3979,7 +3969,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4022,7 +4012,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15181-2023</t>
+          <t>A 15645-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4036,10 +4026,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45016</v>
+        <v>45404</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4052,7 +4042,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4095,7 +4085,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11123-2024</t>
+          <t>A 1525-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4109,10 +4099,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45371</v>
+        <v>46034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4125,7 +4115,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4168,7 +4158,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34435-2024</t>
+          <t>A 15648-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4182,10 +4172,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45525</v>
+        <v>45748</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4198,7 +4188,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4241,7 +4231,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55033-2023</t>
+          <t>A 21979-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4255,10 +4245,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45237</v>
+        <v>45784</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4271,7 +4261,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4314,7 +4304,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 53401-2022</t>
+          <t>A 66960-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4328,10 +4318,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44879</v>
+        <v>44522</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4344,7 +4334,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4387,7 +4377,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37562-2024</t>
+          <t>A 3256-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4401,10 +4391,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45541</v>
+        <v>46041</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4417,7 +4407,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.2</v>
+        <v>8.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4460,7 +4450,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 46533-2024</t>
+          <t>A 11991-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4474,10 +4464,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45582</v>
+        <v>44635</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4490,7 +4480,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4533,7 +4523,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27652-2022</t>
+          <t>A 3074-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4547,10 +4537,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44743</v>
+        <v>44946</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4563,7 +4553,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4606,7 +4596,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7628-2022</t>
+          <t>A 13119-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4620,10 +4610,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44607</v>
+        <v>45002</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4636,7 +4626,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4679,7 +4669,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59879-2024</t>
+          <t>A 17126-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4693,10 +4683,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45640</v>
+        <v>44677</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4709,7 +4699,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4752,7 +4742,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24129-2024</t>
+          <t>A 45519-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4766,10 +4756,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45456</v>
+        <v>45194</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4782,7 +4772,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4825,7 +4815,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11991-2022</t>
+          <t>A 49062-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4839,10 +4829,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44635</v>
+        <v>45594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4855,7 +4845,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4898,7 +4888,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 58330-2022</t>
+          <t>A 46533-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4912,10 +4902,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44901</v>
+        <v>45582</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4928,7 +4918,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4971,7 +4961,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4906-2024</t>
+          <t>A 53131-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4985,10 +4975,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45329</v>
+        <v>44876</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5001,7 +4991,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5044,7 +5034,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13119-2023</t>
+          <t>A 32527-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5058,10 +5048,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45002</v>
+        <v>45513</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5073,8 +5063,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5117,7 +5112,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47902-2024</t>
+          <t>A 32541-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5131,10 +5126,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45589</v>
+        <v>45513</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5146,8 +5141,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 68454-2021</t>
+          <t>A 7783-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44529</v>
+        <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 57259-2022</t>
+          <t>A 11460-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44895</v>
+        <v>45372</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 2263-2024</t>
+          <t>A 47708-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45310</v>
+        <v>45931</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5365,13 +5365,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5414,7 +5409,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 36192-2025</t>
+          <t>A 48790-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5428,10 +5423,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45867</v>
+        <v>45937</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5444,7 +5439,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5487,7 +5482,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10777-2024</t>
+          <t>A 48791-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5501,10 +5496,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45369</v>
+        <v>45937</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5517,7 +5512,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5560,7 +5555,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 19373-2026</t>
+          <t>A 48787-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5574,10 +5569,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46133</v>
+        <v>45937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5590,7 +5585,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5633,7 +5628,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20009-2026</t>
+          <t>A 48788-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5647,10 +5642,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46136</v>
+        <v>45937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5663,7 +5658,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5706,7 +5701,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15648-2025</t>
+          <t>A 62299-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5720,10 +5715,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45748</v>
+        <v>44923</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5736,7 +5731,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5779,7 +5774,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 21979-2025</t>
+          <t>A 49781-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5793,10 +5788,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45784</v>
+        <v>45597</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5809,7 +5804,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5852,7 +5847,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 53227-2021</t>
+          <t>A 34909-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5866,10 +5861,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44468</v>
+        <v>45141</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5882,7 +5877,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5925,7 +5920,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8273-2024</t>
+          <t>A 50337-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5939,10 +5934,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45352</v>
+        <v>45944</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5955,7 +5950,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5998,7 +5993,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 52688-2024</t>
+          <t>A 50209-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6012,10 +6007,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45610</v>
+        <v>45943</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6028,7 +6023,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6071,7 +6066,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 46529-2024</t>
+          <t>A 14211-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6085,10 +6080,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45582</v>
+        <v>46099</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6101,7 +6096,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>11.7</v>
+        <v>2.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6144,7 +6139,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 131-2024</t>
+          <t>A 55033-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6158,10 +6153,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45294</v>
+        <v>45237</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6174,7 +6169,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>7.5</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6217,7 +6212,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 75-2025</t>
+          <t>A 6354-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6231,10 +6226,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45659</v>
+        <v>45699</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6247,7 +6242,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.4</v>
+        <v>19.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6290,7 +6285,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 68400-2021</t>
+          <t>A 21363-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6304,10 +6299,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44529</v>
+        <v>45063</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6320,7 +6315,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6363,7 +6358,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 54087-2021</t>
+          <t>A 15592-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6377,10 +6372,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44470</v>
+        <v>46106</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6392,13 +6387,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>8.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6441,7 +6431,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35465-2022</t>
+          <t>A 40896-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6455,10 +6445,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44798</v>
+        <v>44825</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6471,7 +6461,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>11.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6514,7 +6504,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 3272-2025</t>
+          <t>A 16030-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6528,10 +6518,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45679</v>
+        <v>46108</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6544,7 +6534,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.1</v>
+        <v>15.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6587,7 +6577,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 39116-2022</t>
+          <t>A 15658-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6601,10 +6591,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44817</v>
+        <v>45748</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6617,7 +6607,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6660,7 +6650,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 62266-2022</t>
+          <t>A 15000-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6674,10 +6664,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44923</v>
+        <v>45015</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6690,7 +6680,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6733,7 +6723,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 48788-2025</t>
+          <t>A 65254-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6747,10 +6737,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45937</v>
+        <v>44515</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6763,7 +6753,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6806,7 +6796,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 48790-2025</t>
+          <t>A 46364-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6820,10 +6810,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45937</v>
+        <v>45582</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6836,7 +6826,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6879,7 +6869,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 47708-2025</t>
+          <t>A 6251-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6893,10 +6883,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45931</v>
+        <v>44965</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6909,7 +6899,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.9</v>
+        <v>15.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6952,7 +6942,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 48787-2025</t>
+          <t>A 17485-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6962,14 +6952,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45937</v>
+        <v>46120</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7025,7 +7015,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 48791-2025</t>
+          <t>A 24127-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7039,10 +7029,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45937</v>
+        <v>45456</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7055,7 +7045,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7098,7 +7088,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 10767-2024</t>
+          <t>A 54526-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7112,10 +7102,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45369</v>
+        <v>45965</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7128,7 +7118,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7171,7 +7161,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 50209-2025</t>
+          <t>A 27201-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7185,10 +7175,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45943</v>
+        <v>45812</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7201,7 +7191,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7244,7 +7234,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60103-2022</t>
+          <t>A 23451-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7258,10 +7248,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44909</v>
+        <v>45076</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7273,8 +7263,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7317,7 +7312,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 50337-2025</t>
+          <t>A 3886-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7331,10 +7326,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45944</v>
+        <v>45684</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7346,8 +7341,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7390,7 +7390,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20152-2026</t>
+          <t>A 56523-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7404,10 +7404,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46138</v>
+        <v>45975</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7463,7 +7463,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13515-2022</t>
+          <t>A 18840-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7477,10 +7477,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44648</v>
+        <v>46129</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7536,7 +7536,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30773-2024</t>
+          <t>A 57262-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7550,10 +7550,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45496</v>
+        <v>45979</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7609,7 +7609,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4077-2025</t>
+          <t>A 19373-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7623,10 +7623,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45684</v>
+        <v>46133</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7682,7 +7682,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 2402-2024</t>
+          <t>A 57890-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45310</v>
+        <v>45981</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7755,7 +7755,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 73158-2021</t>
+          <t>A 41554-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44550</v>
+        <v>45560</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7828,7 +7828,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13883-2022</t>
+          <t>A 57886-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7842,10 +7842,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44650</v>
+        <v>45981</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>6.1</v>
+        <v>8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7901,7 +7901,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 28224-2023</t>
+          <t>A 57891-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45099</v>
+        <v>45981</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7974,7 +7974,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 4307-2025</t>
+          <t>A 61046-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7988,10 +7988,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45685</v>
+        <v>45645</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8047,7 +8047,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 54526-2025</t>
+          <t>A 20009-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45965</v>
+        <v>46136</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 20500-2026</t>
+          <t>A 59252-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46140</v>
+        <v>45988</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8193,7 +8193,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56523-2025</t>
+          <t>A 4307-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8207,10 +8207,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45975</v>
+        <v>45685</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8266,7 +8266,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 57262-2025</t>
+          <t>A 60505-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45979</v>
+        <v>45995</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8339,7 +8339,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 59625-2023</t>
+          <t>A 61535-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8353,10 +8353,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45254</v>
+        <v>46001</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8412,7 +8412,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 57890-2025</t>
+          <t>A 61539-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8426,10 +8426,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45981</v>
+        <v>46001</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8485,7 +8485,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 57886-2025</t>
+          <t>A 3272-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8499,10 +8499,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45981</v>
+        <v>45679</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 57891-2025</t>
+          <t>A 30773-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8572,10 +8572,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45981</v>
+        <v>45496</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 15659-2025</t>
+          <t>A 53193-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8645,10 +8645,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45748</v>
+        <v>45229</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8704,7 +8704,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 20501-2026</t>
+          <t>A 39611-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8718,10 +8718,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46140</v>
+        <v>44818</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8733,8 +8733,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8777,7 +8782,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 16154-2024</t>
+          <t>A 29300-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8791,10 +8796,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45406</v>
+        <v>45483</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8850,7 +8855,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 16155-2024</t>
+          <t>A 20500-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8864,10 +8869,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45406</v>
+        <v>46140</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8880,7 +8885,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8923,7 +8928,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 59252-2025</t>
+          <t>A 7628-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8937,10 +8942,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45988</v>
+        <v>44607</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8953,7 +8958,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8996,7 +9001,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21929-2026</t>
+          <t>A 20501-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9010,10 +9015,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46150</v>
+        <v>46140</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9026,7 +9031,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9069,7 +9074,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 35969-2024</t>
+          <t>A 20152-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9083,10 +9088,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45533</v>
+        <v>46138</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9099,7 +9104,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9142,7 +9147,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 60505-2025</t>
+          <t>A 53426-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9156,10 +9161,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45995</v>
+        <v>44879</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9172,7 +9177,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.5</v>
+        <v>13.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9215,7 +9220,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 61535-2025</t>
+          <t>A 62266-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9229,10 +9234,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46001</v>
+        <v>44923</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9245,7 +9250,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9288,7 +9293,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61539-2025</t>
+          <t>A 39116-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9302,10 +9307,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46001</v>
+        <v>44817</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9318,7 +9323,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9361,7 +9366,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 22620-2026</t>
+          <t>A 28224-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9375,10 +9380,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46155</v>
+        <v>45099</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9391,7 +9396,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9434,7 +9439,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 41554-2024</t>
+          <t>A 57918-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9448,10 +9453,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45560</v>
+        <v>44900</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9464,7 +9469,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9507,7 +9512,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 45983-2024</t>
+          <t>A 41893-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9521,10 +9526,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45580</v>
+        <v>44830</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9536,8 +9541,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9580,7 +9590,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 32826-2022</t>
+          <t>A 53227-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9594,10 +9604,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44784</v>
+        <v>44468</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9610,7 +9620,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9653,7 +9663,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 53426-2022</t>
+          <t>A 18612-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9667,10 +9677,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44879</v>
+        <v>45763</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9683,7 +9693,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>13.2</v>
+        <v>2.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9726,7 +9736,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 13220-2022</t>
+          <t>A 7730-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9740,10 +9750,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44644</v>
+        <v>44973</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9799,7 +9809,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 19447-2025</t>
+          <t>A 30486-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9813,10 +9823,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45770</v>
+        <v>45829</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9829,7 +9839,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9872,7 +9882,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 64669-2023</t>
+          <t>A 21929-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9886,10 +9896,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45281</v>
+        <v>46150</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9902,7 +9912,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9945,7 +9955,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 63884-2025</t>
+          <t>A 31464-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9959,10 +9969,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46020</v>
+        <v>45833</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9975,7 +9985,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10018,7 +10028,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 16473-2023</t>
+          <t>A 22620-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10032,10 +10042,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45029</v>
+        <v>46155</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10048,7 +10058,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10091,7 +10101,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 16475-2023</t>
+          <t>A 68454-2021</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10105,10 +10115,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45029</v>
+        <v>44529</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10121,7 +10131,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10164,7 +10174,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 53131-2022</t>
+          <t>A 34671-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10178,10 +10188,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44876</v>
+        <v>45847</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10193,8 +10203,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10237,7 +10252,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 60-2026</t>
+          <t>A 7781-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10251,10 +10266,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46024</v>
+        <v>44973</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10267,7 +10282,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10310,7 +10325,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 1525-2026</t>
+          <t>A 73158-2021</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10324,10 +10339,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46034</v>
+        <v>44550</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10340,7 +10355,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10383,7 +10398,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 64784-2023</t>
+          <t>A 10858-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10397,10 +10412,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45282</v>
+        <v>46078</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10413,7 +10428,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.2</v>
+        <v>8.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10456,7 +10471,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 3256-2026</t>
+          <t>A 13510-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10470,10 +10485,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46041</v>
+        <v>44648</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10486,7 +10501,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>8.1</v>
+        <v>17.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10529,7 +10544,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 3044-2022</t>
+          <t>A 10640-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10543,10 +10558,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44582</v>
+        <v>45721</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10559,7 +10574,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10602,7 +10617,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 15000-2023</t>
+          <t>A 38941-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10616,10 +10631,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45015</v>
+        <v>45163</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10632,7 +10647,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10675,7 +10690,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 6251-2023</t>
+          <t>A 36192-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10689,10 +10704,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44965</v>
+        <v>45867</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10705,7 +10720,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>15.4</v>
+        <v>0.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10748,7 +10763,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 10858-2026</t>
+          <t>A 16473-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10762,10 +10777,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46078</v>
+        <v>45029</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10778,7 +10793,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10821,7 +10836,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 19781-2025</t>
+          <t>A 16475-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10835,10 +10850,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45771</v>
+        <v>45029</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10851,7 +10866,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>6.1</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10894,7 +10909,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 23451-2023</t>
+          <t>A 34435-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10908,10 +10923,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45076</v>
+        <v>45525</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10923,13 +10938,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10972,7 +10982,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7655-2026</t>
+          <t>A 42456-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10986,10 +10996,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46062</v>
+        <v>45565</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11002,7 +11012,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11045,7 +11055,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 60498-2024</t>
+          <t>A 19781-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11059,10 +11069,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45643</v>
+        <v>45771</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11075,7 +11085,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.1</v>
+        <v>6.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11118,7 +11128,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 5927-2022</t>
+          <t>A 12967-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11132,10 +11142,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44598</v>
+        <v>45385</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11148,7 +11158,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11191,7 +11201,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 41893-2022</t>
+          <t>A 37371-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11205,10 +11215,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44830</v>
+        <v>45156</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11220,13 +11230,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11269,7 +11274,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 7783-2023</t>
+          <t>A 27441-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11283,10 +11288,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44973</v>
+        <v>46189</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11342,7 +11347,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 5242-2022</t>
+          <t>A 35969-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11356,10 +11361,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44594</v>
+        <v>45533</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11372,7 +11377,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>8.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11415,7 +11420,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 57918-2022</t>
+          <t>A 27586-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11425,14 +11430,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44900</v>
+        <v>46190</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11445,7 +11450,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11488,7 +11493,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 32527-2024</t>
+          <t>A 7921-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11502,10 +11507,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45513</v>
+        <v>45350</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11517,13 +11522,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>8.699999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11566,7 +11566,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 32541-2024</t>
+          <t>A 13515-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11580,10 +11580,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45513</v>
+        <v>44648</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11595,13 +11595,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11644,7 +11639,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 7781-2023</t>
+          <t>A 75-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11658,10 +11653,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44973</v>
+        <v>45659</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11674,7 +11669,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11717,7 +11712,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 7921-2024</t>
+          <t>A 3795-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11731,10 +11726,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45350</v>
+        <v>45321</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11747,7 +11742,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11790,7 +11785,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 45521-2022</t>
+          <t>A 33782-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11804,10 +11799,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44845</v>
+        <v>46251</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11820,7 +11815,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11863,7 +11858,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 14211-2026</t>
+          <t>A 33830-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11877,10 +11872,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46099</v>
+        <v>46251</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11893,7 +11888,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.5</v>
+        <v>8.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11936,7 +11931,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 17126-2022</t>
+          <t>A 30505-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11950,10 +11945,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44677</v>
+        <v>46210</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11966,7 +11961,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12009,7 +12004,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 15592-2026</t>
+          <t>A 61884-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12023,10 +12018,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46106</v>
+        <v>45652</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12039,7 +12034,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>8.4</v>
+        <v>2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12082,7 +12077,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 56116-2022</t>
+          <t>A 45521-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12096,10 +12091,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44889</v>
+        <v>44845</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12112,7 +12107,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12155,7 +12150,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 16030-2026</t>
+          <t>A 5927-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12169,10 +12164,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46108</v>
+        <v>44598</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12185,7 +12180,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>15.8</v>
+        <v>6.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12228,7 +12223,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 27441-2026</t>
+          <t>A 23984-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12242,10 +12237,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46189</v>
+        <v>45456</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12258,7 +12253,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12301,7 +12296,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 40896-2022</t>
+          <t>A 24129-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12315,10 +12310,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44825</v>
+        <v>45456</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12331,7 +12326,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>11.3</v>
+        <v>1.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12374,7 +12369,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 12329-2024</t>
+          <t>A 35465-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12388,10 +12383,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45378</v>
+        <v>44798</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12404,7 +12399,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12447,7 +12442,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 37371-2023</t>
+          <t>A 65116-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12457,14 +12452,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45156</v>
+        <v>45287</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12477,7 +12472,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12520,7 +12515,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 27586-2026</t>
+          <t>A 59625-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12530,14 +12525,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46190</v>
+        <v>45254</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12550,7 +12545,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12593,7 +12588,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 17485-2026</t>
+          <t>A 36033-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12603,14 +12598,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46120</v>
+        <v>46267</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12623,7 +12618,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12666,7 +12661,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 3074-2023</t>
+          <t>A 19447-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12680,10 +12675,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44946</v>
+        <v>45770</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12696,7 +12691,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12739,7 +12734,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 7730-2023</t>
+          <t>A 131-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12753,10 +12748,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44973</v>
+        <v>45294</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12769,7 +12764,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>7.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12812,7 +12807,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 10494-2022</t>
+          <t>A 54087-2021</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12826,10 +12821,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44623</v>
+        <v>44470</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12841,8 +12836,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>13.3</v>
+        <v>2.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12885,7 +12885,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 46364-2024</t>
+          <t>A 27652-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12899,10 +12899,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45582</v>
+        <v>44743</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.4</v>
+        <v>9.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12958,7 +12958,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 18840-2026</t>
+          <t>A 45983-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12972,10 +12972,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46129</v>
+        <v>45580</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13031,7 +13031,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 33546-2022</t>
+          <t>A 5242-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13045,10 +13045,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44789</v>
+        <v>44594</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13104,7 +13104,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 9821-2022</t>
+          <t>A 20667-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13118,10 +13118,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44620</v>
+        <v>46141</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13177,7 +13177,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 38941-2023</t>
+          <t>A 46529-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13191,10 +13191,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45163</v>
+        <v>45582</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.7</v>
+        <v>11.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13250,7 +13250,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 49781-2024</t>
+          <t>A 16154-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13264,10 +13264,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45597</v>
+        <v>45406</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>5.7</v>
+        <v>0.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13323,7 +13323,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 61046-2024</t>
+          <t>A 16155-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13337,10 +13337,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45645</v>
+        <v>45406</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13396,7 +13396,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 3795-2024</t>
+          <t>A 57259-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13410,10 +13410,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45321</v>
+        <v>44895</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13469,7 +13469,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 33830-2026</t>
+          <t>A 59879-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13483,10 +13483,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46251</v>
+        <v>45640</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>8.9</v>
+        <v>0.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13542,7 +13542,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 42456-2024</t>
+          <t>A 32826-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13556,10 +13556,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45565</v>
+        <v>44784</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13615,7 +13615,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 33782-2026</t>
+          <t>A 58330-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13629,10 +13629,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46251</v>
+        <v>44901</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13688,7 +13688,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 30505-2026</t>
+          <t>A 15704-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13702,10 +13702,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46210</v>
+        <v>45021</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13778,7 +13778,7 @@
         <v>45497</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45406</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 47755-2022</t>
+          <t>A 4906-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13921,10 +13921,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44854</v>
+        <v>45329</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13980,7 +13980,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 10768-2024</t>
+          <t>A 32804-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13994,10 +13994,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45369</v>
+        <v>46241</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14009,8 +14009,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14053,7 +14058,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 62299-2022</t>
+          <t>A 38535-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14067,10 +14072,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44923</v>
+        <v>46283</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14083,7 +14088,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14126,7 +14131,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 11460-2024</t>
+          <t>A 13883-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14140,10 +14145,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45372</v>
+        <v>44650</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14156,7 +14161,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14199,7 +14204,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 55303-2022</t>
+          <t>A 32797-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14213,10 +14218,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44887</v>
+        <v>46241</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14228,8 +14233,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14272,7 +14282,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 36982-2024</t>
+          <t>A 53401-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14286,10 +14296,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45539</v>
+        <v>44879</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14302,7 +14312,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14345,7 +14355,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 855-2023</t>
+          <t>A 15181-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14359,10 +14369,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44931</v>
+        <v>45016</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14375,7 +14385,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14418,7 +14428,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 21363-2023</t>
+          <t>A 855-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14432,10 +14442,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45063</v>
+        <v>44931</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14448,7 +14458,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14491,7 +14501,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 36033-2026</t>
+          <t>A 47755-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14505,10 +14515,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46267</v>
+        <v>44854</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14521,7 +14531,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14564,7 +14574,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 61884-2024</t>
+          <t>A 9821-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14578,10 +14588,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45652</v>
+        <v>44620</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14594,7 +14604,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14637,7 +14647,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 19773-2025</t>
+          <t>A 13220-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14651,10 +14661,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45771</v>
+        <v>44644</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14710,7 +14720,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 3399-2024</t>
+          <t>A 68400-2021</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14724,10 +14734,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45318</v>
+        <v>44529</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14740,7 +14750,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14783,7 +14793,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 44708-2023</t>
+          <t>A 25514-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14797,10 +14807,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45190</v>
+        <v>44732</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14813,7 +14823,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14856,7 +14866,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 25514-2022</t>
+          <t>A 10494-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14870,10 +14880,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44732</v>
+        <v>44623</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14886,7 +14896,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.5</v>
+        <v>13.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14929,7 +14939,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 12967-2024</t>
+          <t>A 52688-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14943,10 +14953,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45385</v>
+        <v>45610</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14959,7 +14969,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15002,7 +15012,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 24432-2022</t>
+          <t>A 47902-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15012,14 +15022,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44726</v>
+        <v>45589</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15032,7 +15042,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15075,7 +15085,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 20667-2026</t>
+          <t>A 2263-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15089,10 +15099,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46141</v>
+        <v>45310</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15104,8 +15114,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15148,7 +15163,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 37658-2022</t>
+          <t>A 37305-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15162,10 +15177,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44810</v>
+        <v>44808</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15178,7 +15193,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>9.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15221,7 +15236,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 15658-2025</t>
+          <t>A 60498-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15235,10 +15250,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45748</v>
+        <v>45643</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15251,7 +15266,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15294,7 +15309,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 66960-2021</t>
+          <t>A 37562-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15308,10 +15323,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44522</v>
+        <v>45541</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15324,7 +15339,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15367,7 +15382,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 37305-2022</t>
+          <t>A 15659-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15381,10 +15396,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44808</v>
+        <v>45748</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15397,7 +15412,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>9.9</v>
+        <v>0.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15440,7 +15455,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 53193-2023</t>
+          <t>A 19773-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15454,10 +15469,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45229</v>
+        <v>45771</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15470,7 +15485,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15513,7 +15528,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 20955-2025</t>
+          <t>A 8273-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15527,10 +15542,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45777</v>
+        <v>45352</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15543,7 +15558,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15586,7 +15601,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 38535-2026</t>
+          <t>A 2402-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15600,10 +15615,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46283</v>
+        <v>45310</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15616,7 +15631,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15659,7 +15674,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 22016-2025</t>
+          <t>A 3399-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15673,10 +15688,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45784</v>
+        <v>45318</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15689,7 +15704,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15732,7 +15747,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 32804-2026</t>
+          <t>A 10767-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15746,10 +15761,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46241</v>
+        <v>45369</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15761,13 +15776,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15810,7 +15820,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 32797-2026</t>
+          <t>A 24432-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15820,14 +15830,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46241</v>
+        <v>44726</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15839,13 +15849,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15888,7 +15893,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37801-2024</t>
+          <t>A 16487-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15898,14 +15903,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45543</v>
+        <v>45029</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15918,7 +15923,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15961,7 +15966,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 11837-2025</t>
+          <t>A 64669-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15975,10 +15980,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45728</v>
+        <v>45281</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15991,7 +15996,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16034,7 +16039,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 15645-2024</t>
+          <t>A 55303-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16048,10 +16053,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45404</v>
+        <v>44887</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16064,7 +16069,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16107,7 +16112,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 24559-2025</t>
+          <t>A 12329-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16121,10 +16126,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45798</v>
+        <v>45378</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16137,7 +16142,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>6.5</v>
+        <v>0.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16180,7 +16185,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 49062-2024</t>
+          <t>A 4077-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16194,10 +16199,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45594</v>
+        <v>45684</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16210,7 +16215,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16253,7 +16258,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 45519-2023</t>
+          <t>A 62294-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16267,10 +16272,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45194</v>
+        <v>44923</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16283,7 +16288,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16326,7 +16331,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 27201-2025</t>
+          <t>A 12264-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16340,10 +16345,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45812</v>
+        <v>45378</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16356,7 +16361,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16399,7 +16404,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 30486-2025</t>
+          <t>A 12266-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16413,10 +16418,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45829</v>
+        <v>45378</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16429,7 +16434,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16472,7 +16477,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 31464-2025</t>
+          <t>A 44708-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16486,10 +16491,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45833</v>
+        <v>45190</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16502,7 +16507,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16545,7 +16550,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 34671-2025</t>
+          <t>A 20955-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16559,10 +16564,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45847</v>
+        <v>45777</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16574,13 +16579,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16623,7 +16623,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 10640-2025</t>
+          <t>A 22016-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16637,10 +16637,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45721</v>
+        <v>45784</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16693,27 +16693,27 @@
       </c>
       <c r="V217" s="2" t="inlineStr"/>
     </row>
-    <row r="218" ht="15" customHeight="1">
+    <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 13510-2022</t>
+          <t>S 643-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44648</v>
+        <v>46090</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>17.6</v>
+        <v>0.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -16765,79 +16765,6 @@
         <v>0</v>
       </c>
       <c r="V218" s="2" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>S 643-2026</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D219" s="1" t="n">
-        <v>46090</v>
-      </c>
-      <c r="E219" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="I219" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J219" t="n">
-        <v>0</v>
-      </c>
-      <c r="K219" t="n">
-        <v>0</v>
-      </c>
-      <c r="L219" t="n">
-        <v>0</v>
-      </c>
-      <c r="M219" t="n">
-        <v>0</v>
-      </c>
-      <c r="N219" t="n">
-        <v>0</v>
-      </c>
-      <c r="O219" t="n">
-        <v>0</v>
-      </c>
-      <c r="P219" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
-      <c r="R219" t="n">
-        <v>0</v>
-      </c>
-      <c r="S219" t="n">
-        <v>0</v>
-      </c>
-      <c r="T219" t="n">
-        <v>0</v>
-      </c>
-      <c r="U219" t="n">
-        <v>0</v>
-      </c>
-      <c r="V219" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45386</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44876</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44572</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44608</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44622</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44811</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44686</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>44466</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44524</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44522</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44565</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44572</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44789</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>45371</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45369</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>45369</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44810</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45543</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>46020</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>44909</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>46024</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44582</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>45282</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>45539</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>45798</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>45728</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>45404</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>46034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>45748</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>45784</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44522</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>46041</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>44635</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>44946</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>45002</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44677</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>45194</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>45594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>45582</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>44876</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>45513</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>45513</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45372</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>45931</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>45937</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45937</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>45937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>45937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44923</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>45597</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>45141</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45944</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>45943</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>46099</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>45237</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>45699</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>45063</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>46106</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44825</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>46108</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>45748</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>45015</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44515</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45582</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>44965</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>46120</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45456</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>45965</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>45812</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45076</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>45684</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>45975</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>46129</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>45979</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>46133</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>45981</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>45560</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>45981</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>45981</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>45645</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>46136</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>45988</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>45685</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>45995</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>46001</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>46001</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>45679</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45496</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>45229</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>44818</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>45483</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>46140</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>44607</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>46140</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>46138</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>44879</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>44923</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>44817</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45099</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>44900</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>44830</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>44468</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>45763</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44973</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45829</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>46150</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>45833</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>46155</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>44529</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>45847</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44973</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44550</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>46078</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44648</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>45721</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45163</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45867</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>45029</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45029</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45525</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45565</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45771</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>45385</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45156</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46189</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45533</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>46190</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>45350</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>44648</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>45659</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>45321</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>46251</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>46251</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>46210</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>45652</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44845</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>44598</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45456</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45456</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>44798</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45287</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45254</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>46267</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45770</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45294</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>44470</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>44743</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>45580</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>44594</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>46141</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45582</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45406</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45406</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>44895</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45640</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>44784</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>44901</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>45021</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45497</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45406</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45329</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>46241</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>46283</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44650</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>46241</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>44879</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14372,7 +14372,7 @@
         <v>45016</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14445,7 +14445,7 @@
         <v>44931</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>44854</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>44620</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>44644</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>44529</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>44732</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>44623</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>45610</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>45589</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>45310</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>44808</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45643</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45541</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45748</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>45771</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>45352</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45310</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45318</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45369</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>44726</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45029</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45281</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>44887</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>45378</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>45684</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>44923</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45378</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>45378</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45190</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45777</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45784</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>46090</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>

--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45386</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44876</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44572</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44608</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44622</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44811</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44686</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>44466</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44524</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44522</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44565</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>44572</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44789</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>45371</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45369</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>45369</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44810</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45543</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>46020</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>44909</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>46024</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44582</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>45282</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>45539</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>45798</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>45728</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>45404</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>46034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>45748</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>45784</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44522</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>46041</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>44635</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>44946</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>45002</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44677</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>45194</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>45594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>45582</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>44876</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>45513</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>45513</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45372</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>45931</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>45937</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45937</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>45937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>45937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44923</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>45597</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>45141</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45944</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>45943</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>46099</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>45237</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>45699</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>45063</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>46106</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44825</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>46108</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>45748</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>45015</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44515</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45582</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>44965</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>46120</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45456</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>45965</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>45812</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45076</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>45684</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>45975</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>46129</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>45979</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>46133</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>45981</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>45560</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>45981</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>45981</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>45645</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>46136</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>45988</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>45685</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>45995</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>46001</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>46001</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>45679</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45496</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>45229</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>44818</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>45483</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>46140</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>44607</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>46140</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>46138</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>44879</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>44923</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>44817</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45099</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>44900</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>44830</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>44468</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>45763</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44973</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45829</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>46150</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>45833</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>46155</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>44529</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>45847</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44973</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44550</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>46078</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44648</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>45721</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45163</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45867</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>45029</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45029</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45525</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45565</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45771</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>45385</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45156</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46189</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45533</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>46190</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>45350</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>44648</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>45659</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>45321</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>46251</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>46251</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>46210</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>45652</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44845</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>44598</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45456</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45456</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>44798</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45287</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45254</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>46267</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45770</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45294</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>44470</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>44743</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>45580</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>44594</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>46141</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45582</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45406</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45406</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>44895</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45640</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>44784</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>44901</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>45021</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45497</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45406</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45329</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>46241</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>46283</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44650</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>46241</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>44879</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14372,7 +14372,7 @@
         <v>45016</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14445,7 +14445,7 @@
         <v>44931</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>44854</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>44620</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>44644</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>44529</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>44732</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>44623</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>45610</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>45589</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>45310</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>44808</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45643</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45541</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45748</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>45771</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>45352</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45310</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45318</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45369</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>44726</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45029</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45281</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>44887</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>45378</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>45684</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>44923</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45378</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>45378</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45190</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45777</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45784</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>46090</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>

--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE218"/>
+  <dimension ref="A1:AE217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45386</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44876</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44572</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44608</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44622</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44811</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44686</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52687-2021</t>
+          <t>A 67535-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44466</v>
+        <v>44524</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2576,8 +2576,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2620,7 +2625,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 67535-2021</t>
+          <t>A 66971-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2634,10 +2639,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44524</v>
+        <v>44522</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2649,13 +2654,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2698,7 +2698,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 66971-2021</t>
+          <t>A 318-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44522</v>
+        <v>44565</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>8.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 318-2022</t>
+          <t>A 1295-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44565</v>
+        <v>44572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8.6</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1295-2022</t>
+          <t>A 24127-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44572</v>
+        <v>45456</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2917,7 +2917,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33546-2022</t>
+          <t>A 23984-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44789</v>
+        <v>45456</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11123-2024</t>
+          <t>A 12264-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45371</v>
+        <v>45378</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>8.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10768-2024</t>
+          <t>A 12266-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45369</v>
+        <v>45378</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10777-2024</t>
+          <t>A 62294-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45369</v>
+        <v>44923</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 37658-2022</t>
+          <t>A 6354-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44810</v>
+        <v>45699</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>19.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37801-2024</t>
+          <t>A 3886-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3292,14 +3292,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45543</v>
+        <v>45684</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3311,8 +3311,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3355,7 +3360,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 63884-2025</t>
+          <t>A 39611-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3369,10 +3374,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46020</v>
+        <v>44818</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3384,8 +3389,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3428,7 +3438,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60103-2022</t>
+          <t>A 65254-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3442,10 +3452,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44909</v>
+        <v>44515</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3458,7 +3468,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3501,7 +3511,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60-2026</t>
+          <t>A 18612-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3515,10 +3525,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46024</v>
+        <v>45763</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3531,7 +3541,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3574,7 +3584,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3044-2022</t>
+          <t>A 34909-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3588,10 +3598,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44582</v>
+        <v>45141</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3604,7 +3614,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3647,7 +3657,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 56116-2022</t>
+          <t>A 65116-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3657,14 +3667,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44889</v>
+        <v>45287</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3677,7 +3687,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3720,7 +3730,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64784-2023</t>
+          <t>A 15704-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3734,10 +3744,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45282</v>
+        <v>45021</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3750,7 +3760,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3793,7 +3803,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 36982-2024</t>
+          <t>A 15181-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3807,10 +3817,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45539</v>
+        <v>45016</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3823,7 +3833,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3866,7 +3876,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24559-2025</t>
+          <t>A 24129-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3880,10 +3890,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45798</v>
+        <v>45456</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3896,7 +3906,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3939,7 +3949,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11837-2025</t>
+          <t>A 15648-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3953,10 +3963,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45728</v>
+        <v>45748</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3969,7 +3979,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4012,7 +4022,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15645-2024</t>
+          <t>A 37801-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4022,14 +4032,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45404</v>
+        <v>45543</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4042,7 +4052,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4085,7 +4095,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1525-2026</t>
+          <t>A 11837-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4099,10 +4109,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46034</v>
+        <v>45728</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4115,7 +4125,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4158,7 +4168,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15648-2025</t>
+          <t>A 15645-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4172,10 +4182,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45748</v>
+        <v>45404</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4248,7 +4258,7 @@
         <v>45784</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4304,7 +4314,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 66960-2021</t>
+          <t>A 24559-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4318,10 +4328,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44522</v>
+        <v>45798</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4334,7 +4344,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4377,7 +4387,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 3256-2026</t>
+          <t>A 29300-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4391,10 +4401,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46041</v>
+        <v>45483</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4407,7 +4417,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8.1</v>
+        <v>0.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4450,7 +4460,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11991-2022</t>
+          <t>A 16487-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4464,10 +4474,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44635</v>
+        <v>45029</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4480,7 +4490,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4523,7 +4533,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3074-2023</t>
+          <t>A 49062-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4537,10 +4547,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44946</v>
+        <v>45594</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4553,7 +4563,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.1</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4596,7 +4606,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13119-2023</t>
+          <t>A 45519-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4610,10 +4620,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45002</v>
+        <v>45194</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4626,7 +4636,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4669,7 +4679,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17126-2022</t>
+          <t>A 11123-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4683,10 +4693,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44677</v>
+        <v>45371</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4699,7 +4709,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4742,7 +4752,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45519-2023</t>
+          <t>A 27201-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4756,10 +4766,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45194</v>
+        <v>45812</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4772,7 +4782,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4815,7 +4825,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 49062-2024</t>
+          <t>A 34435-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4829,10 +4839,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45594</v>
+        <v>45525</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4845,7 +4855,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4888,7 +4898,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 46533-2024</t>
+          <t>A 55033-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4902,10 +4912,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45582</v>
+        <v>45237</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4918,7 +4928,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4961,7 +4971,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 53131-2022</t>
+          <t>A 53401-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4975,10 +4985,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44876</v>
+        <v>44879</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4991,7 +5001,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5034,7 +5044,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32527-2024</t>
+          <t>A 46533-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5048,10 +5058,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45513</v>
+        <v>45582</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5063,13 +5073,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>8.699999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5112,7 +5117,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 32541-2024</t>
+          <t>A 37562-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5126,10 +5131,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45513</v>
+        <v>45541</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5141,13 +5146,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7783-2023</t>
+          <t>A 27652-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44973</v>
+        <v>44743</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>9.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11460-2024</t>
+          <t>A 7628-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45372</v>
+        <v>44607</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5336,7 +5336,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47708-2025</t>
+          <t>A 30486-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45931</v>
+        <v>45829</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48790-2025</t>
+          <t>A 59879-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45937</v>
+        <v>45640</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 48791-2025</t>
+          <t>A 31464-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45937</v>
+        <v>45833</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5555,7 +5555,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48787-2025</t>
+          <t>A 48788-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5572,7 +5572,7 @@
         <v>45937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5628,7 +5628,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 48788-2025</t>
+          <t>A 11991-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45937</v>
+        <v>44635</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62299-2022</t>
+          <t>A 48790-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5715,10 +5715,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44923</v>
+        <v>45937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5774,7 +5774,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49781-2024</t>
+          <t>A 47708-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45597</v>
+        <v>45931</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5847,7 +5847,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 34909-2023</t>
+          <t>A 48787-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45141</v>
+        <v>45937</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5920,7 +5920,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50337-2025</t>
+          <t>A 48791-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45944</v>
+        <v>45937</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5993,7 +5993,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 50209-2025</t>
+          <t>A 4906-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45943</v>
+        <v>45329</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6066,7 +6066,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14211-2026</t>
+          <t>A 50209-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46099</v>
+        <v>45943</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55033-2023</t>
+          <t>A 47902-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45237</v>
+        <v>45589</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6354-2025</t>
+          <t>A 50337-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6226,10 +6226,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45699</v>
+        <v>45944</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>19.3</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 21363-2023</t>
+          <t>A 58330-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45063</v>
+        <v>44901</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6358,7 +6358,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 15592-2026</t>
+          <t>A 34671-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46106</v>
+        <v>45847</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6387,8 +6387,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>8.4</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6431,7 +6436,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40896-2022</t>
+          <t>A 13119-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6445,10 +6450,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44825</v>
+        <v>45002</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6461,7 +6466,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>11.3</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6504,7 +6509,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16030-2026</t>
+          <t>A 63884-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6518,10 +6523,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46108</v>
+        <v>46020</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6534,7 +6539,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>15.8</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6577,7 +6582,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 15658-2025</t>
+          <t>A 60-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6591,10 +6596,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45748</v>
+        <v>46024</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6607,7 +6612,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6650,7 +6655,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15000-2023</t>
+          <t>A 68454-2021</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6664,10 +6669,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45015</v>
+        <v>44529</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6680,7 +6685,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6723,7 +6728,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 65254-2021</t>
+          <t>A 10640-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6737,10 +6742,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44515</v>
+        <v>45721</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6753,7 +6758,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.4</v>
+        <v>3.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6796,7 +6801,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46364-2024</t>
+          <t>A 13510-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6810,10 +6815,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45582</v>
+        <v>44648</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6826,7 +6831,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>17.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6869,7 +6874,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 6251-2023</t>
+          <t>A 57259-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6883,10 +6888,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44965</v>
+        <v>44895</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6899,7 +6904,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>15.4</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6942,7 +6947,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17485-2026</t>
+          <t>A 36192-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6952,14 +6957,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46120</v>
+        <v>45867</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6972,7 +6977,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7015,7 +7020,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 24127-2024</t>
+          <t>A 10777-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7029,10 +7034,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45456</v>
+        <v>45369</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7045,7 +7050,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7105,7 +7110,7 @@
         <v>45965</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7161,7 +7166,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 27201-2025</t>
+          <t>A 1525-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7175,10 +7180,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45812</v>
+        <v>46034</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7191,7 +7196,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7234,7 +7239,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 23451-2023</t>
+          <t>A 56523-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7248,10 +7253,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45076</v>
+        <v>45975</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7263,13 +7268,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3886-2025</t>
+          <t>A 3256-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45684</v>
+        <v>46041</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7341,13 +7341,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>8.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7390,7 +7385,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 56523-2025</t>
+          <t>A 57262-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7404,10 +7399,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7420,7 +7415,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7463,7 +7458,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 18840-2026</t>
+          <t>A 2263-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7477,10 +7472,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46129</v>
+        <v>45310</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7492,8 +7487,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7536,7 +7536,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 57262-2025</t>
+          <t>A 57890-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7550,10 +7550,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7609,7 +7609,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 19373-2026</t>
+          <t>A 57886-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7623,10 +7623,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46133</v>
+        <v>45981</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7682,7 +7682,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 57890-2025</t>
+          <t>A 57891-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7699,7 +7699,7 @@
         <v>45981</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7755,7 +7755,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 41554-2024</t>
+          <t>A 59252-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45560</v>
+        <v>45988</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7828,7 +7828,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 57886-2025</t>
+          <t>A 53227-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7842,10 +7842,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45981</v>
+        <v>44468</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7901,7 +7901,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 57891-2025</t>
+          <t>A 60505-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45981</v>
+        <v>45995</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7974,7 +7974,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 61046-2024</t>
+          <t>A 8273-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7988,10 +7988,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45645</v>
+        <v>45352</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8047,7 +8047,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20009-2026</t>
+          <t>A 52688-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46136</v>
+        <v>45610</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 59252-2025</t>
+          <t>A 61535-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45988</v>
+        <v>46001</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8193,7 +8193,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 4307-2025</t>
+          <t>A 61539-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8207,10 +8207,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45685</v>
+        <v>46001</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8266,7 +8266,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 60505-2025</t>
+          <t>A 46529-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45995</v>
+        <v>45582</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.5</v>
+        <v>11.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8339,7 +8339,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 61535-2025</t>
+          <t>A 131-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8353,10 +8353,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46001</v>
+        <v>45294</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>7.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8412,7 +8412,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61539-2025</t>
+          <t>A 75-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8426,10 +8426,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46001</v>
+        <v>45659</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8485,7 +8485,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 3272-2025</t>
+          <t>A 68400-2021</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8499,10 +8499,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45679</v>
+        <v>44529</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 30773-2024</t>
+          <t>A 54087-2021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8572,10 +8572,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45496</v>
+        <v>44470</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8587,8 +8587,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8631,7 +8636,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 53193-2023</t>
+          <t>A 35465-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8645,10 +8650,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45229</v>
+        <v>44798</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8661,7 +8666,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8704,7 +8709,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 39611-2022</t>
+          <t>A 39116-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8718,10 +8723,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44818</v>
+        <v>44817</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8733,13 +8738,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8782,7 +8782,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 29300-2024</t>
+          <t>A 62266-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8796,10 +8796,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45483</v>
+        <v>44923</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8855,7 +8855,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 20500-2026</t>
+          <t>A 32527-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46140</v>
+        <v>45513</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8884,8 +8884,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8928,7 +8933,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 7628-2022</t>
+          <t>A 32541-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8942,10 +8947,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44607</v>
+        <v>45513</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8957,8 +8962,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9001,7 +9011,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 20501-2026</t>
+          <t>A 10767-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9015,10 +9025,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46140</v>
+        <v>45369</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9031,7 +9041,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9074,7 +9084,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 20152-2026</t>
+          <t>A 60103-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9088,10 +9098,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46138</v>
+        <v>44909</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9104,7 +9114,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9147,7 +9157,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 53426-2022</t>
+          <t>A 14211-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9161,10 +9171,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44879</v>
+        <v>46099</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9177,7 +9187,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>13.2</v>
+        <v>2.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9220,7 +9230,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 62266-2022</t>
+          <t>A 15592-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9234,10 +9244,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44923</v>
+        <v>46106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9250,7 +9260,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>8.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9293,7 +9303,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 39116-2022</t>
+          <t>A 13515-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9307,10 +9317,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44817</v>
+        <v>44648</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9366,7 +9376,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 28224-2023</t>
+          <t>A 16030-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9380,10 +9390,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45099</v>
+        <v>46108</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9396,7 +9406,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.8</v>
+        <v>15.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9439,7 +9449,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 57918-2022</t>
+          <t>A 4077-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9453,10 +9463,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44900</v>
+        <v>45684</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9469,7 +9479,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9512,7 +9522,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 41893-2022</t>
+          <t>A 2402-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9526,10 +9536,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44830</v>
+        <v>45310</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9541,13 +9551,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9590,7 +9595,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 53227-2021</t>
+          <t>A 73158-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9604,10 +9609,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44468</v>
+        <v>44550</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9620,7 +9625,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9663,7 +9668,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 18612-2025</t>
+          <t>A 13883-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9677,10 +9682,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45763</v>
+        <v>44650</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9693,7 +9698,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9736,7 +9741,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 7730-2023</t>
+          <t>A 17485-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9746,14 +9751,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44973</v>
+        <v>46120</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9766,7 +9771,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9809,7 +9814,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 30486-2025</t>
+          <t>A 59625-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9823,10 +9828,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45829</v>
+        <v>45254</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9839,7 +9844,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9882,7 +9887,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 21929-2026</t>
+          <t>A 18840-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9896,10 +9901,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46150</v>
+        <v>46129</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9912,7 +9917,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9955,7 +9960,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 31464-2025</t>
+          <t>A 15659-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9969,10 +9974,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45833</v>
+        <v>45748</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9985,7 +9990,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10028,7 +10033,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 22620-2026</t>
+          <t>A 19373-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10042,10 +10047,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46155</v>
+        <v>46133</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10058,7 +10063,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10101,7 +10106,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 68454-2021</t>
+          <t>A 16154-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10115,10 +10120,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44529</v>
+        <v>45406</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10131,7 +10136,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10174,7 +10179,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 34671-2025</t>
+          <t>A 16155-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10188,10 +10193,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45847</v>
+        <v>45406</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10203,13 +10208,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10252,7 +10252,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 7781-2023</t>
+          <t>A 20009-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10266,10 +10266,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44973</v>
+        <v>46136</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 73158-2021</t>
+          <t>A 35969-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10339,10 +10339,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44550</v>
+        <v>45533</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 10858-2026</t>
+          <t>A 3272-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10412,10 +10412,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46078</v>
+        <v>45679</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10471,7 +10471,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 13510-2022</t>
+          <t>A 41554-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44648</v>
+        <v>45560</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>17.6</v>
+        <v>1.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10544,7 +10544,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 10640-2025</t>
+          <t>A 45983-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10558,10 +10558,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45721</v>
+        <v>45580</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10617,7 +10617,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 38941-2023</t>
+          <t>A 32826-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10631,10 +10631,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45163</v>
+        <v>44784</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10690,7 +10690,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 36192-2025</t>
+          <t>A 20152-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10704,10 +10704,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45867</v>
+        <v>46138</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10763,7 +10763,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 16473-2023</t>
+          <t>A 53426-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10777,10 +10777,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45029</v>
+        <v>44879</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.5</v>
+        <v>13.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10836,7 +10836,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 16475-2023</t>
+          <t>A 13220-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10850,10 +10850,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45029</v>
+        <v>44644</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10909,7 +10909,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 34435-2024</t>
+          <t>A 19447-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10923,10 +10923,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45525</v>
+        <v>45770</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10982,7 +10982,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 42456-2024</t>
+          <t>A 64669-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10996,10 +10996,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45565</v>
+        <v>45281</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11055,7 +11055,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 19781-2025</t>
+          <t>A 30773-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11069,10 +11069,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45771</v>
+        <v>45496</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 12967-2024</t>
+          <t>A 16473-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11142,10 +11142,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45385</v>
+        <v>45029</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11201,7 +11201,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 37371-2023</t>
+          <t>A 16475-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11215,10 +11215,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45156</v>
+        <v>45029</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11274,7 +11274,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 27441-2026</t>
+          <t>A 53131-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11288,10 +11288,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46189</v>
+        <v>44876</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11347,7 +11347,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 35969-2024</t>
+          <t>A 28224-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11361,10 +11361,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45533</v>
+        <v>45099</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11420,7 +11420,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 27586-2026</t>
+          <t>A 4307-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11430,14 +11430,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46190</v>
+        <v>45685</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11493,7 +11493,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 7921-2024</t>
+          <t>A 20500-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11507,10 +11507,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45350</v>
+        <v>46140</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11566,7 +11566,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 13515-2022</t>
+          <t>A 64784-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11580,10 +11580,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44648</v>
+        <v>45282</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11639,7 +11639,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 75-2025</t>
+          <t>A 20501-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11653,10 +11653,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45659</v>
+        <v>46140</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11712,7 +11712,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 3795-2024</t>
+          <t>A 3044-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11726,10 +11726,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45321</v>
+        <v>44582</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33782-2026</t>
+          <t>A 15000-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11799,10 +11799,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46251</v>
+        <v>45015</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 33830-2026</t>
+          <t>A 6251-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11872,10 +11872,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46251</v>
+        <v>44965</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>8.9</v>
+        <v>15.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11931,7 +11931,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 30505-2026</t>
+          <t>A 21929-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11945,10 +11945,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46210</v>
+        <v>46150</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12004,7 +12004,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 61884-2024</t>
+          <t>A 19781-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12018,10 +12018,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45652</v>
+        <v>45771</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12077,7 +12077,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 45521-2022</t>
+          <t>A 23451-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44845</v>
+        <v>45076</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12106,8 +12106,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12150,7 +12155,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 5927-2022</t>
+          <t>A 22620-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12164,10 +12169,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44598</v>
+        <v>46155</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12180,7 +12185,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12223,7 +12228,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 23984-2024</t>
+          <t>A 60498-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12237,10 +12242,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45456</v>
+        <v>45643</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12253,7 +12258,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12296,7 +12301,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 24129-2024</t>
+          <t>A 5927-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12310,10 +12315,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45456</v>
+        <v>44598</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12326,7 +12331,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12369,7 +12374,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 35465-2022</t>
+          <t>A 41893-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12383,10 +12388,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44798</v>
+        <v>44830</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12398,8 +12403,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12442,7 +12452,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 65116-2023</t>
+          <t>A 7783-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12452,14 +12462,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45287</v>
+        <v>44973</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12472,7 +12482,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12515,7 +12525,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 59625-2023</t>
+          <t>A 5242-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12529,10 +12539,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45254</v>
+        <v>44594</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12545,7 +12555,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12588,7 +12598,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 36033-2026</t>
+          <t>A 57918-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12602,10 +12612,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46267</v>
+        <v>44900</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12618,7 +12628,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12661,7 +12671,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 19447-2025</t>
+          <t>A 7781-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12675,10 +12685,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45770</v>
+        <v>44973</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12691,7 +12701,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12734,7 +12744,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 131-2024</t>
+          <t>A 7921-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12748,10 +12758,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45294</v>
+        <v>45350</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12764,7 +12774,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>7.5</v>
+        <v>0.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12807,7 +12817,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 54087-2021</t>
+          <t>A 10858-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12821,10 +12831,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44470</v>
+        <v>46078</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12836,13 +12846,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>2.1</v>
+        <v>8.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12885,7 +12890,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 27652-2022</t>
+          <t>A 45521-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12899,10 +12904,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44743</v>
+        <v>44845</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12915,7 +12920,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>9.1</v>
+        <v>4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12958,7 +12963,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 45983-2024</t>
+          <t>A 17126-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12972,10 +12977,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45580</v>
+        <v>44677</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12988,7 +12993,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13031,7 +13036,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 5242-2022</t>
+          <t>A 56116-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13045,10 +13050,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44594</v>
+        <v>44889</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13061,7 +13066,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13104,7 +13109,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 20667-2026</t>
+          <t>A 40896-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13118,10 +13123,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46141</v>
+        <v>44825</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13134,7 +13139,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.8</v>
+        <v>11.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13177,7 +13182,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 46529-2024</t>
+          <t>A 12329-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13191,10 +13196,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45582</v>
+        <v>45378</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13207,7 +13212,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>11.7</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13250,7 +13255,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 16154-2024</t>
+          <t>A 37371-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13264,10 +13269,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45406</v>
+        <v>45156</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13280,7 +13285,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13323,7 +13328,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 16155-2024</t>
+          <t>A 3074-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13337,10 +13342,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45406</v>
+        <v>44946</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13353,7 +13358,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13396,7 +13401,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 57259-2022</t>
+          <t>A 7730-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13410,10 +13415,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44895</v>
+        <v>44973</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13426,7 +13431,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13469,7 +13474,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 59879-2024</t>
+          <t>A 10494-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13483,10 +13488,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45640</v>
+        <v>44623</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13499,7 +13504,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.8</v>
+        <v>13.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13542,7 +13547,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 32826-2022</t>
+          <t>A 46364-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13556,10 +13561,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44784</v>
+        <v>45582</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13572,7 +13577,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13615,7 +13620,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 58330-2022</t>
+          <t>A 33546-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13629,10 +13634,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44901</v>
+        <v>44789</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13645,7 +13650,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13688,7 +13693,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 15704-2023</t>
+          <t>A 9821-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13702,10 +13707,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45021</v>
+        <v>44620</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13718,7 +13723,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13761,7 +13766,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 30796-2024</t>
+          <t>A 38941-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13775,10 +13780,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45497</v>
+        <v>45163</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13791,7 +13796,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13834,7 +13839,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 16152-2024</t>
+          <t>A 27441-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13848,10 +13853,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45406</v>
+        <v>46189</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13864,7 +13869,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13907,7 +13912,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 4906-2024</t>
+          <t>A 27586-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13917,14 +13922,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45329</v>
+        <v>46190</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13937,7 +13942,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13980,7 +13985,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 32804-2026</t>
+          <t>A 49781-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13994,10 +13999,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46241</v>
+        <v>45597</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14009,13 +14014,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14058,7 +14058,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 38535-2026</t>
+          <t>A 61046-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14072,10 +14072,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46283</v>
+        <v>45645</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14131,7 +14131,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 13883-2022</t>
+          <t>A 3795-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44650</v>
+        <v>45321</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>6.1</v>
+        <v>1.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14204,7 +14204,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 32797-2026</t>
+          <t>A 42456-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14218,10 +14218,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46241</v>
+        <v>45565</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14233,13 +14233,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14282,7 +14277,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 53401-2022</t>
+          <t>A 30796-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14296,10 +14291,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44879</v>
+        <v>45497</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14312,7 +14307,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14355,7 +14350,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 15181-2023</t>
+          <t>A 30505-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14369,10 +14364,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45016</v>
+        <v>46210</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14385,7 +14380,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14428,7 +14423,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 855-2023</t>
+          <t>A 16152-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14442,10 +14437,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44931</v>
+        <v>45406</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14458,7 +14453,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14518,7 +14513,7 @@
         <v>44854</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14574,7 +14569,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 9821-2022</t>
+          <t>A 10768-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14588,10 +14583,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44620</v>
+        <v>45369</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14604,7 +14599,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14647,7 +14642,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 13220-2022</t>
+          <t>A 62299-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14661,10 +14656,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44644</v>
+        <v>44923</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14677,7 +14672,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14720,7 +14715,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 68400-2021</t>
+          <t>A 11460-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14734,10 +14729,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44529</v>
+        <v>45372</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14750,7 +14745,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14793,7 +14788,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 25514-2022</t>
+          <t>A 55303-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14807,10 +14802,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44732</v>
+        <v>44887</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14866,7 +14861,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 10494-2022</t>
+          <t>A 36982-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14880,10 +14875,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44623</v>
+        <v>45539</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14896,7 +14891,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>13.3</v>
+        <v>3.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14939,7 +14934,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 52688-2024</t>
+          <t>A 855-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14953,10 +14948,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45610</v>
+        <v>44931</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14969,7 +14964,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15012,7 +15007,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 47902-2024</t>
+          <t>A 21363-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15026,10 +15021,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45589</v>
+        <v>45063</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15042,7 +15037,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15085,7 +15080,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 2263-2024</t>
+          <t>A 61884-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15099,10 +15094,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45310</v>
+        <v>45652</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15114,13 +15109,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15163,7 +15153,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 37305-2022</t>
+          <t>A 36033-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15177,10 +15167,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44808</v>
+        <v>46267</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15193,7 +15183,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>9.9</v>
+        <v>1.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15236,7 +15226,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 60498-2024</t>
+          <t>A 19773-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15250,10 +15240,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45643</v>
+        <v>45771</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15266,7 +15256,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15309,7 +15299,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 37562-2024</t>
+          <t>A 3399-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15323,10 +15313,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45541</v>
+        <v>45318</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15339,7 +15329,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15382,7 +15372,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 15659-2025</t>
+          <t>A 44708-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15396,10 +15386,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45748</v>
+        <v>45190</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15412,7 +15402,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15455,7 +15445,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 19773-2025</t>
+          <t>A 25514-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15469,10 +15459,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45771</v>
+        <v>44732</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15485,7 +15475,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15528,7 +15518,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 8273-2024</t>
+          <t>A 12967-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15542,10 +15532,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45352</v>
+        <v>45385</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15558,7 +15548,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15601,7 +15591,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 2402-2024</t>
+          <t>A 24432-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15611,14 +15601,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45310</v>
+        <v>44726</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15631,7 +15621,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15674,7 +15664,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 3399-2024</t>
+          <t>A 37658-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15688,10 +15678,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45318</v>
+        <v>44810</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15704,7 +15694,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15747,7 +15737,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 10767-2024</t>
+          <t>A 15658-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15761,10 +15751,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45369</v>
+        <v>45748</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15777,7 +15767,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15820,7 +15810,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 24432-2022</t>
+          <t>A 66960-2021</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15830,14 +15820,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44726</v>
+        <v>44522</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15850,7 +15840,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15893,7 +15883,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 16487-2023</t>
+          <t>A 37305-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15907,10 +15897,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45029</v>
+        <v>44808</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15923,7 +15913,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.9</v>
+        <v>9.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15966,7 +15956,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 64669-2023</t>
+          <t>A 20667-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15980,10 +15970,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45281</v>
+        <v>46141</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15996,7 +15986,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16039,7 +16029,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 55303-2022</t>
+          <t>A 53193-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16053,10 +16043,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44887</v>
+        <v>45229</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16069,7 +16059,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16112,7 +16102,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 12329-2024</t>
+          <t>A 20955-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16126,10 +16116,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45378</v>
+        <v>45777</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16142,7 +16132,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16185,7 +16175,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 4077-2025</t>
+          <t>A 22016-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16199,10 +16189,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45684</v>
+        <v>45784</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16215,7 +16205,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16258,7 +16248,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 62294-2022</t>
+          <t>A 38535-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16272,10 +16262,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44923</v>
+        <v>46283</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16288,7 +16278,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16331,7 +16321,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 12264-2024</t>
+          <t>A 32804-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16345,10 +16335,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45378</v>
+        <v>46241</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16360,8 +16350,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16404,7 +16399,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 12266-2024</t>
+          <t>A 32797-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16418,10 +16413,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45378</v>
+        <v>46241</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16433,8 +16428,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16477,7 +16477,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 44708-2023</t>
+          <t>A 33830-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16491,10 +16491,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45190</v>
+        <v>46251</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.6</v>
+        <v>8.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16550,7 +16550,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 20955-2025</t>
+          <t>A 33782-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16564,10 +16564,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45777</v>
+        <v>46251</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16620,27 +16620,27 @@
       </c>
       <c r="V216" s="2" t="inlineStr"/>
     </row>
-    <row r="217" ht="15" customHeight="1">
+    <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 22016-2025</t>
+          <t>S 643-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45784</v>
+        <v>46090</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16692,79 +16692,6 @@
         <v>0</v>
       </c>
       <c r="V217" s="2" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>S 643-2026</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D218" s="1" t="n">
-        <v>46090</v>
-      </c>
-      <c r="E218" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="I218" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J218" t="n">
-        <v>0</v>
-      </c>
-      <c r="K218" t="n">
-        <v>0</v>
-      </c>
-      <c r="L218" t="n">
-        <v>0</v>
-      </c>
-      <c r="M218" t="n">
-        <v>0</v>
-      </c>
-      <c r="N218" t="n">
-        <v>0</v>
-      </c>
-      <c r="O218" t="n">
-        <v>0</v>
-      </c>
-      <c r="P218" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
-      <c r="R218" t="n">
-        <v>0</v>
-      </c>
-      <c r="S218" t="n">
-        <v>0</v>
-      </c>
-      <c r="T218" t="n">
-        <v>0</v>
-      </c>
-      <c r="U218" t="n">
-        <v>0</v>
-      </c>
-      <c r="V218" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE217"/>
+  <dimension ref="A1:AE216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45386</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44876</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44572</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>44608</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>44622</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44811</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44686</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>44524</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44522</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44565</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 24127-2024</t>
+          <t>A 33546-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45456</v>
+        <v>44789</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2917,7 +2917,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 23984-2024</t>
+          <t>A 11123-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45456</v>
+        <v>45371</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12264-2024</t>
+          <t>A 10768-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45378</v>
+        <v>45369</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12266-2024</t>
+          <t>A 10777-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45378</v>
+        <v>45369</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62294-2022</t>
+          <t>A 37658-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44923</v>
+        <v>44810</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6354-2025</t>
+          <t>A 37801-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3219,14 +3219,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45699</v>
+        <v>45543</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>19.3</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3886-2025</t>
+          <t>A 63884-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45684</v>
+        <v>46020</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3311,13 +3311,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3360,7 +3355,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 39611-2022</t>
+          <t>A 60103-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3374,10 +3369,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44818</v>
+        <v>44909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3389,13 +3384,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3438,7 +3428,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 65254-2021</t>
+          <t>A 60-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3452,10 +3442,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44515</v>
+        <v>46024</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3468,7 +3458,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3511,7 +3501,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18612-2025</t>
+          <t>A 3044-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3525,10 +3515,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45763</v>
+        <v>44582</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3541,7 +3531,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3584,7 +3574,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34909-2023</t>
+          <t>A 56116-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3598,10 +3588,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45141</v>
+        <v>44889</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3614,7 +3604,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3657,7 +3647,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 65116-2023</t>
+          <t>A 64784-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3667,14 +3657,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45287</v>
+        <v>45282</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3687,7 +3677,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3730,7 +3720,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15704-2023</t>
+          <t>A 24559-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3744,10 +3734,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45021</v>
+        <v>45798</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3760,7 +3750,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3803,7 +3793,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15181-2023</t>
+          <t>A 36982-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3817,10 +3807,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45016</v>
+        <v>45539</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3833,7 +3823,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3876,7 +3866,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24129-2024</t>
+          <t>A 11837-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3890,10 +3880,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45456</v>
+        <v>45728</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3906,7 +3896,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3966,7 +3956,7 @@
         <v>45748</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4022,7 +4012,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37801-2024</t>
+          <t>A 15645-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4032,14 +4022,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45543</v>
+        <v>45404</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4052,7 +4042,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4095,7 +4085,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11837-2025</t>
+          <t>A 21979-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4109,10 +4099,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45728</v>
+        <v>45784</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4125,7 +4115,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4168,7 +4158,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15645-2024</t>
+          <t>A 66960-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4182,10 +4172,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45404</v>
+        <v>44522</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4198,7 +4188,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4241,7 +4231,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21979-2025</t>
+          <t>A 45519-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4255,10 +4245,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45784</v>
+        <v>45194</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4271,7 +4261,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4314,7 +4304,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 24559-2025</t>
+          <t>A 49062-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4328,10 +4318,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45798</v>
+        <v>45594</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4344,7 +4334,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4387,7 +4377,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 29300-2024</t>
+          <t>A 27201-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4401,10 +4391,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45483</v>
+        <v>45812</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4417,7 +4407,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4460,7 +4450,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16487-2023</t>
+          <t>A 1525-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4474,10 +4464,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45029</v>
+        <v>46034</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4490,7 +4480,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4533,7 +4523,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 49062-2024</t>
+          <t>A 11991-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4547,10 +4537,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45594</v>
+        <v>44635</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4563,7 +4553,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4606,7 +4596,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45519-2023</t>
+          <t>A 3074-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4620,10 +4610,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45194</v>
+        <v>44946</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4636,7 +4626,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.5</v>
+        <v>6.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4679,7 +4669,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11123-2024</t>
+          <t>A 13119-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4693,10 +4683,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45371</v>
+        <v>45002</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4709,7 +4699,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4752,7 +4742,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27201-2025</t>
+          <t>A 3256-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4766,10 +4756,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45812</v>
+        <v>46041</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4782,7 +4772,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>8.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4825,7 +4815,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 34435-2024</t>
+          <t>A 17126-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4839,10 +4829,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45525</v>
+        <v>44677</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4855,7 +4845,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4898,7 +4888,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 55033-2023</t>
+          <t>A 30486-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4912,10 +4902,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45237</v>
+        <v>45829</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4928,7 +4918,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4971,7 +4961,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 53401-2022</t>
+          <t>A 31464-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4985,10 +4975,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44879</v>
+        <v>45833</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5001,7 +4991,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5061,7 +5051,7 @@
         <v>45582</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5117,7 +5107,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37562-2024</t>
+          <t>A 53131-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5131,10 +5121,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45541</v>
+        <v>44876</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5147,7 +5137,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5190,7 +5180,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 27652-2022</t>
+          <t>A 7783-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5204,10 +5194,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44743</v>
+        <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5220,7 +5210,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>9.1</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5263,7 +5253,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7628-2022</t>
+          <t>A 11460-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5277,10 +5267,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44607</v>
+        <v>45372</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5293,7 +5283,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5336,7 +5326,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30486-2025</t>
+          <t>A 47708-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5350,10 +5340,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45829</v>
+        <v>45931</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5366,7 +5356,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5409,7 +5399,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 59879-2024</t>
+          <t>A 48790-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5423,10 +5413,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45640</v>
+        <v>45937</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5439,7 +5429,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5482,7 +5472,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31464-2025</t>
+          <t>A 48791-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5496,10 +5486,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45833</v>
+        <v>45937</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5512,7 +5502,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5555,7 +5545,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48788-2025</t>
+          <t>A 34671-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5569,10 +5559,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45937</v>
+        <v>45847</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5584,8 +5574,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5628,7 +5623,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11991-2022</t>
+          <t>A 48787-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5642,10 +5637,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44635</v>
+        <v>45937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5658,7 +5653,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5701,7 +5696,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48790-2025</t>
+          <t>A 48788-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5718,7 +5713,7 @@
         <v>45937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5731,7 +5726,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5774,7 +5769,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47708-2025</t>
+          <t>A 62299-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5788,10 +5783,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45931</v>
+        <v>44923</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5804,7 +5799,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5847,7 +5842,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 48787-2025</t>
+          <t>A 49781-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5861,10 +5856,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45937</v>
+        <v>45597</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5877,7 +5872,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5920,7 +5915,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 48791-2025</t>
+          <t>A 13510-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5934,10 +5929,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45937</v>
+        <v>44648</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5950,7 +5945,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>17.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5993,7 +5988,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4906-2024</t>
+          <t>A 50337-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6007,10 +6002,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45329</v>
+        <v>45944</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6023,7 +6018,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6066,7 +6061,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50209-2025</t>
+          <t>A 10640-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6080,10 +6075,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45943</v>
+        <v>45721</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6096,7 +6091,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6139,7 +6134,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 47902-2024</t>
+          <t>A 50209-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6153,10 +6148,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45589</v>
+        <v>45943</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6169,7 +6164,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6212,7 +6207,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50337-2025</t>
+          <t>A 34909-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6226,10 +6221,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45944</v>
+        <v>45141</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6242,7 +6237,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6285,7 +6280,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58330-2022</t>
+          <t>A 55033-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6299,10 +6294,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44901</v>
+        <v>45237</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6315,7 +6310,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6358,7 +6353,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34671-2025</t>
+          <t>A 6354-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6372,10 +6367,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45847</v>
+        <v>45699</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6387,13 +6382,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>19.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6436,7 +6426,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13119-2023</t>
+          <t>A 36192-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6450,10 +6440,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45002</v>
+        <v>45867</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6466,7 +6456,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6509,7 +6499,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 63884-2025</t>
+          <t>A 21363-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6523,10 +6513,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46020</v>
+        <v>45063</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6539,7 +6529,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6582,7 +6572,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60-2026</t>
+          <t>A 40896-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6596,10 +6586,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46024</v>
+        <v>44825</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6612,7 +6602,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>11.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6655,7 +6645,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 68454-2021</t>
+          <t>A 15658-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6669,10 +6659,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44529</v>
+        <v>45748</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6685,7 +6675,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6728,7 +6718,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10640-2025</t>
+          <t>A 15000-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6742,10 +6732,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45721</v>
+        <v>45015</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6758,7 +6748,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6801,7 +6791,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13510-2022</t>
+          <t>A 65254-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6815,10 +6805,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44648</v>
+        <v>44515</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6831,7 +6821,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>17.6</v>
+        <v>6.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6874,7 +6864,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 57259-2022</t>
+          <t>A 46364-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6888,10 +6878,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44895</v>
+        <v>45582</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6904,7 +6894,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6947,7 +6937,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36192-2025</t>
+          <t>A 6251-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6961,10 +6951,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45867</v>
+        <v>44965</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6977,7 +6967,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.4</v>
+        <v>15.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7020,7 +7010,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10777-2024</t>
+          <t>A 54526-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7034,10 +7024,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45369</v>
+        <v>45965</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7050,7 +7040,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7093,7 +7083,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 54526-2025</t>
+          <t>A 24127-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7107,10 +7097,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45965</v>
+        <v>45456</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7123,7 +7113,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7166,7 +7156,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 1525-2026</t>
+          <t>A 23451-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7180,10 +7170,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46034</v>
+        <v>45076</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7195,8 +7185,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7239,7 +7234,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 56523-2025</t>
+          <t>A 3886-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7253,10 +7248,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45975</v>
+        <v>45684</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7268,8 +7263,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3256-2026</t>
+          <t>A 56523-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46041</v>
+        <v>45975</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>8.1</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7402,7 +7402,7 @@
         <v>45979</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 2263-2024</t>
+          <t>A 57890-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45310</v>
+        <v>45981</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7487,13 +7487,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7536,7 +7531,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 57890-2025</t>
+          <t>A 41554-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7550,10 +7545,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45981</v>
+        <v>45560</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7566,7 +7561,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7626,7 +7621,7 @@
         <v>45981</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7699,7 +7694,7 @@
         <v>45981</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7755,7 +7750,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 59252-2025</t>
+          <t>A 61046-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7769,10 +7764,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45988</v>
+        <v>45645</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7785,7 +7780,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7828,7 +7823,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 53227-2021</t>
+          <t>A 59252-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7842,10 +7837,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44468</v>
+        <v>45988</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7858,7 +7853,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7918,7 +7913,7 @@
         <v>45995</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7974,7 +7969,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 8273-2024</t>
+          <t>A 61535-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7988,10 +7983,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45352</v>
+        <v>46001</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8004,7 +7999,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8047,7 +8042,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 52688-2024</t>
+          <t>A 61539-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8061,10 +8056,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45610</v>
+        <v>46001</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8077,7 +8072,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8120,7 +8115,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 61535-2025</t>
+          <t>A 32527-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8134,10 +8129,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46001</v>
+        <v>45513</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8149,8 +8144,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8193,7 +8193,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61539-2025</t>
+          <t>A 32541-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8207,10 +8207,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46001</v>
+        <v>45513</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8222,8 +8222,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8266,7 +8271,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 46529-2024</t>
+          <t>A 53193-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8280,10 +8285,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45582</v>
+        <v>45229</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8296,7 +8301,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>11.7</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8339,7 +8344,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 131-2024</t>
+          <t>A 14211-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8353,10 +8358,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45294</v>
+        <v>46099</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8369,7 +8374,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8412,7 +8417,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 75-2025</t>
+          <t>A 39611-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8426,10 +8431,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45659</v>
+        <v>44818</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8441,8 +8446,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8485,7 +8495,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 68400-2021</t>
+          <t>A 29300-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8499,10 +8509,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44529</v>
+        <v>45483</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8515,7 +8525,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8558,7 +8568,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 54087-2021</t>
+          <t>A 7628-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8572,10 +8582,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44470</v>
+        <v>44607</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8585,11 +8595,6 @@
       <c r="G107" t="inlineStr">
         <is>
           <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -8636,7 +8641,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 35465-2022</t>
+          <t>A 15592-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8650,10 +8655,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44798</v>
+        <v>46106</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8666,7 +8671,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8709,7 +8714,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 39116-2022</t>
+          <t>A 53426-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8723,10 +8728,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44817</v>
+        <v>44879</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8739,7 +8744,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.3</v>
+        <v>13.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8799,7 +8804,7 @@
         <v>44923</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8855,7 +8860,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 32527-2024</t>
+          <t>A 39116-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8869,10 +8874,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45513</v>
+        <v>44817</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8884,13 +8889,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>8.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 32541-2024</t>
+          <t>A 16030-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45513</v>
+        <v>46108</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8962,13 +8962,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>15.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9011,7 +9006,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 10767-2024</t>
+          <t>A 57918-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9025,10 +9020,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45369</v>
+        <v>44900</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9041,7 +9036,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9084,7 +9079,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 60103-2022</t>
+          <t>A 41893-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9098,10 +9093,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44909</v>
+        <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9113,8 +9108,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9157,7 +9157,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 14211-2026</t>
+          <t>A 17485-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9167,14 +9167,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46099</v>
+        <v>46120</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9230,7 +9230,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 15592-2026</t>
+          <t>A 18612-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9244,10 +9244,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46106</v>
+        <v>45763</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>8.4</v>
+        <v>2.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9303,7 +9303,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 13515-2022</t>
+          <t>A 7730-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9317,10 +9317,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44648</v>
+        <v>44973</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9376,7 +9376,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 16030-2026</t>
+          <t>A 18840-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46108</v>
+        <v>46129</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>15.8</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9449,7 +9449,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 4077-2025</t>
+          <t>A 19373-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9463,10 +9463,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45684</v>
+        <v>46133</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9522,7 +9522,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 2402-2024</t>
+          <t>A 20009-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9536,10 +9536,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45310</v>
+        <v>46136</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9595,7 +9595,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 73158-2021</t>
+          <t>A 68454-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9609,10 +9609,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44550</v>
+        <v>44529</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9668,7 +9668,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 13883-2022</t>
+          <t>A 4307-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9682,10 +9682,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44650</v>
+        <v>45685</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>6.1</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9741,7 +9741,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 17485-2026</t>
+          <t>A 7781-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9751,14 +9751,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46120</v>
+        <v>44973</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9814,7 +9814,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 59625-2023</t>
+          <t>A 73158-2021</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45254</v>
+        <v>44550</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9887,7 +9887,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 18840-2026</t>
+          <t>A 38941-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9901,10 +9901,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46129</v>
+        <v>45163</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9960,7 +9960,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 15659-2025</t>
+          <t>A 16473-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9974,10 +9974,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45748</v>
+        <v>45029</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.3</v>
+        <v>5.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10033,7 +10033,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 19373-2026</t>
+          <t>A 16475-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46133</v>
+        <v>45029</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 16154-2024</t>
+          <t>A 3272-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10120,10 +10120,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45406</v>
+        <v>45679</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 16155-2024</t>
+          <t>A 34435-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10193,10 +10193,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45406</v>
+        <v>45525</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10252,7 +10252,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20009-2026</t>
+          <t>A 30773-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10266,10 +10266,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46136</v>
+        <v>45496</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10325,7 +10325,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 35969-2024</t>
+          <t>A 42456-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10339,10 +10339,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45533</v>
+        <v>45565</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10398,7 +10398,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 3272-2025</t>
+          <t>A 20500-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10412,10 +10412,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45679</v>
+        <v>46140</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10471,7 +10471,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 41554-2024</t>
+          <t>A 19781-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45560</v>
+        <v>45771</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.7</v>
+        <v>6.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10544,7 +10544,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 45983-2024</t>
+          <t>A 12967-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10558,10 +10558,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45580</v>
+        <v>45385</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10617,7 +10617,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 32826-2022</t>
+          <t>A 20501-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10631,10 +10631,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44784</v>
+        <v>46140</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10707,7 +10707,7 @@
         <v>46138</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 53426-2022</t>
+          <t>A 37371-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10777,10 +10777,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44879</v>
+        <v>45156</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>13.2</v>
+        <v>2.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10836,7 +10836,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 13220-2022</t>
+          <t>A 35969-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10850,10 +10850,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44644</v>
+        <v>45533</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 19447-2025</t>
+          <t>A 28224-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10923,10 +10923,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45770</v>
+        <v>45099</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10982,7 +10982,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 64669-2023</t>
+          <t>A 7921-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10996,10 +10996,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45281</v>
+        <v>45350</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11055,7 +11055,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 30773-2024</t>
+          <t>A 21929-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11069,10 +11069,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45496</v>
+        <v>46150</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 16473-2023</t>
+          <t>A 13515-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11142,10 +11142,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45029</v>
+        <v>44648</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11201,7 +11201,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 16475-2023</t>
+          <t>A 75-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11215,10 +11215,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45029</v>
+        <v>45659</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11274,7 +11274,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 53131-2022</t>
+          <t>A 3795-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11288,10 +11288,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44876</v>
+        <v>45321</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11347,7 +11347,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 28224-2023</t>
+          <t>A 22620-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11361,10 +11361,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45099</v>
+        <v>46155</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11420,7 +11420,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 4307-2025</t>
+          <t>A 61884-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11434,10 +11434,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45685</v>
+        <v>45652</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11493,7 +11493,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 20500-2026</t>
+          <t>A 45521-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11507,10 +11507,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46140</v>
+        <v>44845</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11566,7 +11566,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 64784-2023</t>
+          <t>A 5927-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11580,10 +11580,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45282</v>
+        <v>44598</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11639,7 +11639,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 20501-2026</t>
+          <t>A 23984-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11653,10 +11653,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46140</v>
+        <v>45456</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11712,7 +11712,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 3044-2022</t>
+          <t>A 24129-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11726,10 +11726,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44582</v>
+        <v>45456</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 15000-2023</t>
+          <t>A 10858-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11799,10 +11799,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45015</v>
+        <v>46078</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.4</v>
+        <v>8.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 6251-2023</t>
+          <t>A 35465-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11872,10 +11872,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44965</v>
+        <v>44798</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>15.4</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11931,7 +11931,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 21929-2026</t>
+          <t>A 65116-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11941,14 +11941,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46150</v>
+        <v>45287</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12004,7 +12004,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 19781-2025</t>
+          <t>A 59625-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12018,10 +12018,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45771</v>
+        <v>45254</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12077,7 +12077,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 23451-2023</t>
+          <t>A 19447-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45076</v>
+        <v>45770</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12106,13 +12106,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12155,7 +12150,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 22620-2026</t>
+          <t>A 131-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12169,10 +12164,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46155</v>
+        <v>45294</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12185,7 +12180,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12228,7 +12223,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 60498-2024</t>
+          <t>A 54087-2021</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12242,10 +12237,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45643</v>
+        <v>44470</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12257,8 +12252,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12301,7 +12301,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 5927-2022</t>
+          <t>A 27441-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44598</v>
+        <v>46189</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12374,7 +12374,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 41893-2022</t>
+          <t>A 27586-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12384,14 +12384,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44830</v>
+        <v>46190</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12403,13 +12403,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12452,7 +12447,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 7783-2023</t>
+          <t>A 27652-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12466,10 +12461,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44973</v>
+        <v>44743</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12482,7 +12477,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.2</v>
+        <v>9.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12525,7 +12520,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 5242-2022</t>
+          <t>A 45983-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12539,10 +12534,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44594</v>
+        <v>45580</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12555,7 +12550,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12598,7 +12593,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 57918-2022</t>
+          <t>A 5242-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12612,10 +12607,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44900</v>
+        <v>44594</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12628,7 +12623,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12671,7 +12666,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 7781-2023</t>
+          <t>A 46529-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12685,10 +12680,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44973</v>
+        <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12701,7 +12696,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.5</v>
+        <v>11.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12744,7 +12739,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 7921-2024</t>
+          <t>A 16154-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12758,10 +12753,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45350</v>
+        <v>45406</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12774,7 +12769,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12817,7 +12812,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 10858-2026</t>
+          <t>A 16155-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12831,10 +12826,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46078</v>
+        <v>45406</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12847,7 +12842,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12890,7 +12885,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 45521-2022</t>
+          <t>A 57259-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12904,10 +12899,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44845</v>
+        <v>44895</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12920,7 +12915,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12963,7 +12958,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 17126-2022</t>
+          <t>A 59879-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12977,10 +12972,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44677</v>
+        <v>45640</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12993,7 +12988,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13036,7 +13031,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 56116-2022</t>
+          <t>A 32826-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13050,10 +13045,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44889</v>
+        <v>44784</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13066,7 +13061,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13109,7 +13104,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 40896-2022</t>
+          <t>A 58330-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13123,10 +13118,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44825</v>
+        <v>44901</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13139,7 +13134,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>11.3</v>
+        <v>2.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13182,7 +13177,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 12329-2024</t>
+          <t>A 15704-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13196,10 +13191,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45378</v>
+        <v>45021</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13212,7 +13207,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13255,7 +13250,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 37371-2023</t>
+          <t>A 30796-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13269,10 +13264,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45156</v>
+        <v>45497</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13285,7 +13280,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13328,7 +13323,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 3074-2023</t>
+          <t>A 16152-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13342,10 +13337,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44946</v>
+        <v>45406</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13358,7 +13353,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13401,7 +13396,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 7730-2023</t>
+          <t>A 4906-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13415,10 +13410,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44973</v>
+        <v>45329</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13431,7 +13426,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13474,7 +13469,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 10494-2022</t>
+          <t>A 13883-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13488,10 +13483,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44623</v>
+        <v>44650</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13504,7 +13499,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>13.3</v>
+        <v>6.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13547,7 +13542,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 46364-2024</t>
+          <t>A 53401-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13561,10 +13556,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45582</v>
+        <v>44879</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13577,7 +13572,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13620,7 +13615,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 33546-2022</t>
+          <t>A 15181-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13634,10 +13629,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44789</v>
+        <v>45016</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13650,7 +13645,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13693,7 +13688,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 9821-2022</t>
+          <t>A 855-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13707,10 +13702,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44620</v>
+        <v>44931</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13723,7 +13718,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13766,7 +13761,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 38941-2023</t>
+          <t>A 47755-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13780,10 +13775,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45163</v>
+        <v>44854</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13796,7 +13791,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13839,7 +13834,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 27441-2026</t>
+          <t>A 9821-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13853,10 +13848,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46189</v>
+        <v>44620</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13869,7 +13864,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13912,7 +13907,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 27586-2026</t>
+          <t>A 30505-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13922,14 +13917,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46190</v>
+        <v>46210</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13942,7 +13937,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13985,7 +13980,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 49781-2024</t>
+          <t>A 13220-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13999,10 +13994,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45597</v>
+        <v>44644</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14015,7 +14010,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14058,7 +14053,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 61046-2024</t>
+          <t>A 68400-2021</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14072,10 +14067,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45645</v>
+        <v>44529</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14088,7 +14083,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14131,7 +14126,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 3795-2024</t>
+          <t>A 25514-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14145,10 +14140,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45321</v>
+        <v>44732</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14161,7 +14156,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14204,7 +14199,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 42456-2024</t>
+          <t>A 10494-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14218,10 +14213,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45565</v>
+        <v>44623</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14234,7 +14229,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.5</v>
+        <v>13.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14277,7 +14272,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 30796-2024</t>
+          <t>A 52688-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14291,10 +14286,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45497</v>
+        <v>45610</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14307,7 +14302,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14350,7 +14345,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 30505-2026</t>
+          <t>A 47902-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14364,10 +14359,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46210</v>
+        <v>45589</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14380,7 +14375,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14423,7 +14418,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 16152-2024</t>
+          <t>A 2263-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14437,10 +14432,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45406</v>
+        <v>45310</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14452,8 +14447,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14496,7 +14496,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 47755-2022</t>
+          <t>A 37305-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14510,10 +14510,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44854</v>
+        <v>44808</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2</v>
+        <v>9.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14569,7 +14569,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 10768-2024</t>
+          <t>A 60498-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45369</v>
+        <v>45643</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14642,7 +14642,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 62299-2022</t>
+          <t>A 36033-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14656,10 +14656,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44923</v>
+        <v>46267</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14715,7 +14715,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 11460-2024</t>
+          <t>A 37562-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14729,10 +14729,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45372</v>
+        <v>45541</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14788,7 +14788,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 55303-2022</t>
+          <t>A 15659-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14802,10 +14802,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44887</v>
+        <v>45748</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14861,7 +14861,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 36982-2024</t>
+          <t>A 19773-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14875,10 +14875,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45539</v>
+        <v>45771</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14934,7 +14934,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 855-2023</t>
+          <t>A 20667-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14948,10 +14948,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44931</v>
+        <v>46141</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15007,7 +15007,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 21363-2023</t>
+          <t>A 8273-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15021,10 +15021,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45063</v>
+        <v>45352</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15080,7 +15080,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 61884-2024</t>
+          <t>A 2402-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15094,10 +15094,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45652</v>
+        <v>45310</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15153,7 +15153,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 36033-2026</t>
+          <t>A 3399-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15167,10 +15167,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46267</v>
+        <v>45318</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15226,7 +15226,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 19773-2025</t>
+          <t>A 10767-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15240,10 +15240,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45771</v>
+        <v>45369</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15299,7 +15299,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 3399-2024</t>
+          <t>A 24432-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15309,14 +15309,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45318</v>
+        <v>44726</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15372,7 +15372,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 44708-2023</t>
+          <t>A 16487-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15386,10 +15386,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45190</v>
+        <v>45029</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15445,7 +15445,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 25514-2022</t>
+          <t>A 64669-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44732</v>
+        <v>45281</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15518,7 +15518,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 12967-2024</t>
+          <t>A 32804-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15532,10 +15532,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45385</v>
+        <v>46241</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15547,8 +15547,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15591,7 +15596,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 24432-2022</t>
+          <t>A 55303-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15601,14 +15606,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44726</v>
+        <v>44887</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15621,7 +15626,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15664,7 +15669,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 37658-2022</t>
+          <t>A 38535-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15678,10 +15683,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44810</v>
+        <v>46283</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15694,7 +15699,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15737,7 +15742,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 15658-2025</t>
+          <t>A 32797-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15751,10 +15756,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45748</v>
+        <v>46241</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15766,8 +15771,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15810,7 +15820,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 66960-2021</t>
+          <t>A 12329-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15824,10 +15834,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44522</v>
+        <v>45378</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15840,7 +15850,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15883,7 +15893,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37305-2022</t>
+          <t>A 4077-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15897,10 +15907,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44808</v>
+        <v>45684</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15913,7 +15923,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>9.9</v>
+        <v>1.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15956,7 +15966,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 20667-2026</t>
+          <t>A 62294-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15970,10 +15980,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46141</v>
+        <v>44923</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15986,7 +15996,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16029,7 +16039,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 53193-2023</t>
+          <t>A 12264-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16043,10 +16053,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45229</v>
+        <v>45378</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16059,7 +16069,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16102,7 +16112,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 20955-2025</t>
+          <t>A 12266-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16116,10 +16126,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45777</v>
+        <v>45378</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16132,7 +16142,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16175,7 +16185,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 22016-2025</t>
+          <t>A 44708-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16189,10 +16199,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45784</v>
+        <v>45190</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16205,7 +16215,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16248,7 +16258,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 38535-2026</t>
+          <t>A 20955-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16262,10 +16272,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46283</v>
+        <v>45777</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16278,7 +16288,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16321,7 +16331,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 32804-2026</t>
+          <t>A 22016-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16335,10 +16345,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46241</v>
+        <v>45784</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16350,13 +16360,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16399,7 +16404,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 32797-2026</t>
+          <t>A 33830-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16413,10 +16418,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46241</v>
+        <v>46251</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16428,13 +16433,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>4.8</v>
+        <v>8.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16477,7 +16477,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 33830-2026</t>
+          <t>A 33782-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16494,7 +16494,7 @@
         <v>46251</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>8.9</v>
+        <v>1.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16547,27 +16547,27 @@
       </c>
       <c r="V215" s="2" t="inlineStr"/>
     </row>
-    <row r="216" ht="15" customHeight="1">
+    <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 33782-2026</t>
+          <t>S 643-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46251</v>
+        <v>46090</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16619,79 +16619,6 @@
         <v>0</v>
       </c>
       <c r="V216" s="2" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>S 643-2026</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D217" s="1" t="n">
-        <v>46090</v>
-      </c>
-      <c r="E217" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="I217" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J217" t="n">
-        <v>0</v>
-      </c>
-      <c r="K217" t="n">
-        <v>0</v>
-      </c>
-      <c r="L217" t="n">
-        <v>0</v>
-      </c>
-      <c r="M217" t="n">
-        <v>0</v>
-      </c>
-      <c r="N217" t="n">
-        <v>0</v>
-      </c>
-      <c r="O217" t="n">
-        <v>0</v>
-      </c>
-      <c r="P217" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
-      <c r="R217" t="n">
-        <v>0</v>
-      </c>
-      <c r="S217" t="n">
-        <v>0</v>
-      </c>
-      <c r="T217" t="n">
-        <v>0</v>
-      </c>
-      <c r="U217" t="n">
-        <v>0</v>
-      </c>
-      <c r="V217" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 15069-2026</t>
+          <t>A 13131-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46104</v>
+        <v>45386</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -835,20 +835,25 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -863,7 +868,7 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -876,150 +881,145 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Svinrot
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/artfynd/A 13131-2024 artfynd.xlsx", "A 13131-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor/A 13131-2024 karta.png", "A 13131-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor_geotiff/A 13131-2024 georefererad karta.tif", "A 13131-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomål/A 13131-2024 FSC-klagomål.docx", "A 13131-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomålsmail/A 13131-2024 FSC-klagomål mail.docx", "A 13131-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsyn/A 13131-2024 tillsynsbegäran.docx", "A 13131-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsynsmail/A 13131-2024 tillsynsbegäran mail.docx", "A 13131-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 15069-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TROLLHÄTTAN</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Kortskaftad parasitspik
 Rostfläck</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/artfynd/A 15069-2026 artfynd.xlsx", "A 15069-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor/A 15069-2026 karta.png", "A 15069-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor_geotiff/A 15069-2026 georefererad karta.tif", "A 15069-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomål/A 15069-2026 FSC-klagomål.docx", "A 15069-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomålsmail/A 15069-2026 FSC-klagomål mail.docx", "A 15069-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsyn/A 15069-2026 tillsynsbegäran.docx", "A 15069-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsynsmail/A 15069-2026 tillsynsbegäran mail.docx", "A 15069-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 13131-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45386</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Svinrot
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/artfynd/A 13131-2024 artfynd.xlsx", "A 13131-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor/A 13131-2024 karta.png", "A 13131-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor_geotiff/A 13131-2024 georefererad karta.tif", "A 13131-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomål/A 13131-2024 FSC-klagomål.docx", "A 13131-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomålsmail/A 13131-2024 FSC-klagomål mail.docx", "A 13131-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsyn/A 13131-2024 tillsynsbegäran.docx", "A 13131-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsynsmail/A 13131-2024 tillsynsbegäran mail.docx", "A 13131-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44876</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44572</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 17194-2022</t>
+          <t>A 7747-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44677</v>
+        <v>44608</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 7747-2022</t>
+          <t>A 38000-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44608</v>
+        <v>44811</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2182,7 +2182,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 10150-2022</t>
+          <t>A 17194-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44622</v>
+        <v>44677</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2255,7 +2255,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38000-2022</t>
+          <t>A 18533-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44811</v>
+        <v>44686</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 18533-2022</t>
+          <t>A 19577-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44686</v>
+        <v>44693</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 19577-2022</t>
+          <t>A 10150-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44693</v>
+        <v>44622</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 67535-2021</t>
+          <t>A 318-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44524</v>
+        <v>44565</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2576,13 +2576,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>8.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2625,7 +2620,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 66971-2021</t>
+          <t>A 67535-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2639,10 +2634,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44522</v>
+        <v>44524</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2654,8 +2649,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2698,7 +2698,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 318-2022</t>
+          <t>A 66971-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44565</v>
+        <v>44522</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>8.6</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 1295-2022</t>
+          <t>A 24127-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44572</v>
+        <v>45456</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33546-2022</t>
+          <t>A 23984-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44789</v>
+        <v>45456</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2917,7 +2917,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 11123-2024</t>
+          <t>A 1295-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45371</v>
+        <v>44572</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10768-2024</t>
+          <t>A 11460-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45369</v>
+        <v>45372</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10777-2024</t>
+          <t>A 62294-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45369</v>
+        <v>44923</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37658-2022</t>
+          <t>A 3044-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44810</v>
+        <v>44582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 37801-2024</t>
+          <t>A 15000-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3219,14 +3219,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45543</v>
+        <v>45015</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 63884-2025</t>
+          <t>A 55303-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46020</v>
+        <v>44887</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60103-2022</t>
+          <t>A 12264-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44909</v>
+        <v>45378</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60-2026</t>
+          <t>A 12266-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46024</v>
+        <v>45378</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3044-2022</t>
+          <t>A 6251-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44582</v>
+        <v>44965</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>15.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56116-2022</t>
+          <t>A 6354-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44889</v>
+        <v>45699</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>19.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3647,7 +3647,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 64784-2023</t>
+          <t>A 36982-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45282</v>
+        <v>45539</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3720,7 +3720,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 24559-2025</t>
+          <t>A 855-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45798</v>
+        <v>44931</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3793,7 +3793,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 36982-2024</t>
+          <t>A 21363-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45539</v>
+        <v>45063</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3866,7 +3866,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11837-2025</t>
+          <t>A 2263-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45728</v>
+        <v>45310</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3895,8 +3895,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3939,7 +3944,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15648-2025</t>
+          <t>A 61884-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3953,10 +3958,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45748</v>
+        <v>45652</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3969,7 +3974,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4012,7 +4017,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15645-2024</t>
+          <t>A 19781-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4026,10 +4031,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45404</v>
+        <v>45771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4042,7 +4047,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4085,7 +4090,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 21979-2025</t>
+          <t>A 23451-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4099,10 +4104,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45784</v>
+        <v>45076</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4114,8 +4119,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4158,7 +4168,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 66960-2021</t>
+          <t>A 3886-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4172,10 +4182,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44522</v>
+        <v>45684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4187,8 +4197,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4231,7 +4246,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45519-2023</t>
+          <t>A 19773-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4245,10 +4260,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45194</v>
+        <v>45771</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4261,7 +4276,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4304,7 +4319,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49062-2024</t>
+          <t>A 60498-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4318,10 +4333,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45594</v>
+        <v>45643</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4334,7 +4349,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4377,7 +4392,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27201-2025</t>
+          <t>A 5927-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4391,10 +4406,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45812</v>
+        <v>44598</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4407,7 +4422,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4450,7 +4465,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1525-2026</t>
+          <t>A 3399-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4464,10 +4479,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46034</v>
+        <v>45318</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4480,7 +4495,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4523,7 +4538,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11991-2022</t>
+          <t>A 41893-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4537,10 +4552,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44635</v>
+        <v>44830</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4552,8 +4567,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4596,7 +4616,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3074-2023</t>
+          <t>A 7783-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4610,10 +4630,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44946</v>
+        <v>44973</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4626,7 +4646,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.1</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4669,7 +4689,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13119-2023</t>
+          <t>A 18612-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4683,10 +4703,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45002</v>
+        <v>45763</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4699,7 +4719,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4742,7 +4762,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3256-2026</t>
+          <t>A 8273-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4756,10 +4776,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46041</v>
+        <v>45352</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4772,7 +4792,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.1</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4815,7 +4835,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17126-2022</t>
+          <t>A 52688-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4829,10 +4849,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44677</v>
+        <v>45610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4845,7 +4865,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4888,7 +4908,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30486-2025</t>
+          <t>A 65254-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4902,10 +4922,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45829</v>
+        <v>44515</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4918,7 +4938,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>6.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4961,7 +4981,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 31464-2025</t>
+          <t>A 5242-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4975,10 +4995,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45833</v>
+        <v>44594</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4991,7 +5011,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5034,7 +5054,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46533-2024</t>
+          <t>A 57918-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5048,10 +5068,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45582</v>
+        <v>44900</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5064,7 +5084,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5107,7 +5127,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 53131-2022</t>
+          <t>A 39611-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5121,10 +5141,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44876</v>
+        <v>44818</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5136,8 +5156,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5180,7 +5205,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7783-2023</t>
+          <t>A 44708-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5194,10 +5219,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44973</v>
+        <v>45190</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5210,7 +5235,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5253,7 +5278,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11460-2024</t>
+          <t>A 25514-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5267,10 +5292,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45372</v>
+        <v>44732</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5283,7 +5308,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5326,7 +5351,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47708-2025</t>
+          <t>A 7781-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5340,10 +5365,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45931</v>
+        <v>44973</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5356,7 +5381,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5399,7 +5424,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48790-2025</t>
+          <t>A 12967-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5413,10 +5438,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45937</v>
+        <v>45385</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5429,7 +5454,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5472,7 +5497,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 48791-2025</t>
+          <t>A 7921-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5486,10 +5511,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45937</v>
+        <v>45350</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5502,7 +5527,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5545,7 +5570,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 34671-2025</t>
+          <t>A 46529-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5559,10 +5584,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45847</v>
+        <v>45582</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5574,13 +5599,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>11.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5623,7 +5643,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 48787-2025</t>
+          <t>A 24432-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5633,14 +5653,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45937</v>
+        <v>44726</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5653,7 +5673,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5696,7 +5716,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48788-2025</t>
+          <t>A 45521-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5710,10 +5730,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45937</v>
+        <v>44845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5726,7 +5746,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5769,7 +5789,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 62299-2022</t>
+          <t>A 131-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5783,10 +5803,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44923</v>
+        <v>45294</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5799,7 +5819,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5842,7 +5862,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 49781-2024</t>
+          <t>A 75-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5856,10 +5876,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45597</v>
+        <v>45659</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5872,7 +5892,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5915,7 +5935,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13510-2022</t>
+          <t>A 68400-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5929,10 +5949,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44648</v>
+        <v>44529</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5945,7 +5965,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>17.6</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5988,7 +6008,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 50337-2025</t>
+          <t>A 17126-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6002,10 +6022,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45944</v>
+        <v>44677</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6018,7 +6038,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6061,7 +6081,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 10640-2025</t>
+          <t>A 37658-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6075,10 +6095,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45721</v>
+        <v>44810</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6091,7 +6111,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6134,7 +6154,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 50209-2025</t>
+          <t>A 34909-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6148,10 +6168,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45943</v>
+        <v>45141</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6164,7 +6184,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6207,7 +6227,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34909-2023</t>
+          <t>A 54087-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6221,10 +6241,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45141</v>
+        <v>44470</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6236,8 +6256,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6280,7 +6305,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 55033-2023</t>
+          <t>A 56116-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6294,10 +6319,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45237</v>
+        <v>44889</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6310,7 +6335,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6353,7 +6378,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6354-2025</t>
+          <t>A 15658-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6367,10 +6392,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45699</v>
+        <v>45748</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6383,7 +6408,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>19.3</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6426,7 +6451,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 36192-2025</t>
+          <t>A 66960-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6440,10 +6465,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45867</v>
+        <v>44522</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6456,7 +6481,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6499,7 +6524,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21363-2023</t>
+          <t>A 35465-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6513,10 +6538,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45063</v>
+        <v>44798</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6529,7 +6554,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6572,7 +6597,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 40896-2022</t>
+          <t>A 65116-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6582,14 +6607,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44825</v>
+        <v>45287</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6602,7 +6627,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>11.3</v>
+        <v>0.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6645,7 +6670,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15658-2025</t>
+          <t>A 40896-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6659,10 +6684,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45748</v>
+        <v>44825</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6675,7 +6700,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>11.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6718,7 +6743,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 15000-2023</t>
+          <t>A 12329-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6732,10 +6757,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45015</v>
+        <v>45378</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6748,7 +6773,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6791,7 +6816,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 65254-2021</t>
+          <t>A 37371-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6805,10 +6830,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44515</v>
+        <v>45156</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6821,7 +6846,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6.4</v>
+        <v>2.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6864,7 +6889,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46364-2024</t>
+          <t>A 15704-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6878,10 +6903,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45582</v>
+        <v>45021</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6894,7 +6919,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6937,7 +6962,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 6251-2023</t>
+          <t>A 39116-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6951,10 +6976,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44965</v>
+        <v>44817</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6967,7 +6992,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>15.4</v>
+        <v>3.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7010,7 +7035,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 54526-2025</t>
+          <t>A 37305-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7024,10 +7049,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45965</v>
+        <v>44808</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7040,7 +7065,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.5</v>
+        <v>9.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7083,7 +7108,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 24127-2024</t>
+          <t>A 15181-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7097,10 +7122,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45456</v>
+        <v>45016</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7113,7 +7138,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7156,7 +7181,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 23451-2023</t>
+          <t>A 24129-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7170,10 +7195,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45076</v>
+        <v>45456</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7185,13 +7210,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7234,7 +7254,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3886-2025</t>
+          <t>A 53193-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7248,10 +7268,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45684</v>
+        <v>45229</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7263,13 +7283,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7312,7 +7327,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 56523-2025</t>
+          <t>A 62266-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7326,10 +7341,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45975</v>
+        <v>44923</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7342,7 +7357,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7385,7 +7400,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 57262-2025</t>
+          <t>A 3074-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7399,10 +7414,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45979</v>
+        <v>44946</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7415,7 +7430,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.9</v>
+        <v>6.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7458,7 +7473,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 57890-2025</t>
+          <t>A 20955-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7472,10 +7487,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45981</v>
+        <v>45777</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7488,7 +7503,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7531,7 +7546,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 41554-2024</t>
+          <t>A 7730-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7545,10 +7560,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45560</v>
+        <v>44973</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7561,7 +7576,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7604,7 +7619,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 57886-2025</t>
+          <t>A 10494-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7618,10 +7633,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45981</v>
+        <v>44623</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7634,7 +7649,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>8</v>
+        <v>13.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7677,7 +7692,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 57891-2025</t>
+          <t>A 46364-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7691,10 +7706,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45981</v>
+        <v>45582</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7707,7 +7722,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7750,7 +7765,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 61046-2024</t>
+          <t>A 10767-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7764,10 +7779,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45645</v>
+        <v>45369</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7780,7 +7795,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7823,7 +7838,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 59252-2025</t>
+          <t>A 33546-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7837,10 +7852,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45988</v>
+        <v>44789</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7853,7 +7868,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7896,7 +7911,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 60505-2025</t>
+          <t>A 60103-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7910,10 +7925,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45995</v>
+        <v>44909</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7926,7 +7941,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7969,7 +7984,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 61535-2025</t>
+          <t>A 9821-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7983,10 +7998,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46001</v>
+        <v>44620</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7999,7 +8014,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8042,7 +8057,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61539-2025</t>
+          <t>A 22016-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8056,10 +8071,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46001</v>
+        <v>45784</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8072,7 +8087,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8115,7 +8130,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32527-2024</t>
+          <t>A 38941-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8129,10 +8144,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45513</v>
+        <v>45163</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8144,13 +8159,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>8.699999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8193,7 +8203,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 32541-2024</t>
+          <t>A 13515-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8207,10 +8217,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45513</v>
+        <v>44648</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8222,13 +8232,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8271,7 +8276,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 53193-2023</t>
+          <t>A 4077-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8285,10 +8290,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45229</v>
+        <v>45684</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8301,7 +8306,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8344,7 +8349,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 14211-2026</t>
+          <t>A 49781-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8358,10 +8363,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46099</v>
+        <v>45597</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8374,7 +8379,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8417,7 +8422,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 39611-2022</t>
+          <t>A 2402-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8431,10 +8436,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44818</v>
+        <v>45310</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8446,13 +8451,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8495,7 +8495,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 29300-2024</t>
+          <t>A 61046-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45483</v>
+        <v>45645</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8568,7 +8568,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 7628-2022</t>
+          <t>A 73158-2021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8582,10 +8582,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44607</v>
+        <v>44550</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8641,7 +8641,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 15592-2026</t>
+          <t>A 13883-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8655,10 +8655,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46106</v>
+        <v>44650</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>8.4</v>
+        <v>6.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8714,7 +8714,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 53426-2022</t>
+          <t>A 37801-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8724,14 +8724,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44879</v>
+        <v>45543</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>13.2</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8787,7 +8787,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 62266-2022</t>
+          <t>A 29300-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8801,10 +8801,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44923</v>
+        <v>45483</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8860,7 +8860,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 39116-2022</t>
+          <t>A 11837-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44817</v>
+        <v>45728</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 16030-2026</t>
+          <t>A 15645-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46108</v>
+        <v>45404</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>15.8</v>
+        <v>2.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9006,7 +9006,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 57918-2022</t>
+          <t>A 3795-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44900</v>
+        <v>45321</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9079,7 +9079,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 41893-2022</t>
+          <t>A 16487-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44830</v>
+        <v>45029</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9108,13 +9108,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9157,7 +9152,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 17485-2026</t>
+          <t>A 11123-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9167,14 +9162,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46120</v>
+        <v>45371</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9187,7 +9182,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9230,7 +9225,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 18612-2025</t>
+          <t>A 24559-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9244,10 +9239,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45763</v>
+        <v>45798</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9260,7 +9255,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9303,7 +9298,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 7730-2023</t>
+          <t>A 34435-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9317,10 +9312,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44973</v>
+        <v>45525</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9333,7 +9328,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9376,7 +9371,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 18840-2026</t>
+          <t>A 42456-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9390,10 +9385,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46129</v>
+        <v>45565</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9406,7 +9401,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9449,7 +9444,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 19373-2026</t>
+          <t>A 59625-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9463,10 +9458,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46133</v>
+        <v>45254</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9479,7 +9474,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9522,7 +9517,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 20009-2026</t>
+          <t>A 55033-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9536,10 +9531,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46136</v>
+        <v>45237</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9552,7 +9547,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9595,7 +9590,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 68454-2021</t>
+          <t>A 53401-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9609,10 +9604,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44529</v>
+        <v>44879</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9625,7 +9620,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9668,7 +9663,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4307-2025</t>
+          <t>A 46533-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9682,10 +9677,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45685</v>
+        <v>45582</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9698,7 +9693,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9741,7 +9736,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 7781-2023</t>
+          <t>A 49062-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9755,10 +9750,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44973</v>
+        <v>45594</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9771,7 +9766,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9814,7 +9809,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 73158-2021</t>
+          <t>A 45519-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9828,10 +9823,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44550</v>
+        <v>45194</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9844,7 +9839,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9887,7 +9882,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 38941-2023</t>
+          <t>A 37562-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9901,10 +9896,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45163</v>
+        <v>45541</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9917,7 +9912,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9960,7 +9955,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 16473-2023</t>
+          <t>A 27652-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9974,10 +9969,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45029</v>
+        <v>44743</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9990,7 +9985,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5.5</v>
+        <v>9.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10033,7 +10028,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 16475-2023</t>
+          <t>A 15659-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10047,10 +10042,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45029</v>
+        <v>45748</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10063,7 +10058,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10106,7 +10101,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 3272-2025</t>
+          <t>A 27201-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10120,10 +10115,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45679</v>
+        <v>45812</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10136,7 +10131,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10179,7 +10174,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 34435-2024</t>
+          <t>A 30796-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10193,10 +10188,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45525</v>
+        <v>45497</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10209,7 +10204,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10252,7 +10247,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 30773-2024</t>
+          <t>A 16154-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10266,10 +10261,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45496</v>
+        <v>45406</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10282,7 +10277,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10325,7 +10320,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 42456-2024</t>
+          <t>A 16155-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10339,10 +10334,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45565</v>
+        <v>45406</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10355,7 +10350,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10398,7 +10393,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 20500-2026</t>
+          <t>A 7628-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10412,10 +10407,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46140</v>
+        <v>44607</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10428,7 +10423,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10471,7 +10466,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 19781-2025</t>
+          <t>A 35969-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10485,10 +10480,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45771</v>
+        <v>45533</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10501,7 +10496,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10544,7 +10539,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 12967-2024</t>
+          <t>A 59879-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10558,10 +10553,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45385</v>
+        <v>45640</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10574,7 +10569,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10617,7 +10612,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 20501-2026</t>
+          <t>A 30486-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10631,10 +10626,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46140</v>
+        <v>45829</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10647,7 +10642,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10690,7 +10685,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 20152-2026</t>
+          <t>A 31464-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10704,10 +10699,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46138</v>
+        <v>45833</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10720,7 +10715,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10763,7 +10758,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 37371-2023</t>
+          <t>A 16152-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10777,10 +10772,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45156</v>
+        <v>45406</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10793,7 +10788,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10836,7 +10831,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 35969-2024</t>
+          <t>A 11991-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10850,10 +10845,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45533</v>
+        <v>44635</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10866,7 +10861,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10909,7 +10904,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 28224-2023</t>
+          <t>A 41554-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10923,10 +10918,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45099</v>
+        <v>45560</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10939,7 +10934,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10982,7 +10977,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7921-2024</t>
+          <t>A 47755-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10996,10 +10991,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45350</v>
+        <v>44854</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11012,7 +11007,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11055,7 +11050,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 21929-2026</t>
+          <t>A 10768-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11069,10 +11064,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46150</v>
+        <v>45369</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11085,7 +11080,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11128,7 +11123,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 13515-2022</t>
+          <t>A 62299-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11142,10 +11137,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44648</v>
+        <v>44923</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11158,7 +11153,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11201,7 +11196,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 75-2025</t>
+          <t>A 45983-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11215,10 +11210,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45659</v>
+        <v>45580</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11231,7 +11226,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11274,7 +11269,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 3795-2024</t>
+          <t>A 32826-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11288,10 +11283,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45321</v>
+        <v>44784</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11304,7 +11299,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11347,7 +11342,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 22620-2026</t>
+          <t>A 53426-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11361,10 +11356,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46155</v>
+        <v>44879</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11377,7 +11372,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3</v>
+        <v>13.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11420,7 +11415,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 61884-2024</t>
+          <t>A 4906-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11434,10 +11429,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45652</v>
+        <v>45329</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11450,7 +11445,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11493,7 +11488,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 45521-2022</t>
+          <t>A 34671-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11507,10 +11502,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44845</v>
+        <v>45847</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11522,8 +11517,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11566,7 +11566,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 5927-2022</t>
+          <t>A 13220-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11580,10 +11580,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44598</v>
+        <v>44644</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11639,7 +11639,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 23984-2024</t>
+          <t>A 19447-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11653,10 +11653,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45456</v>
+        <v>45770</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11712,7 +11712,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24129-2024</t>
+          <t>A 64669-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11726,10 +11726,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45456</v>
+        <v>45281</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 10858-2026</t>
+          <t>A 47902-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11799,10 +11799,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46078</v>
+        <v>45589</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 35465-2022</t>
+          <t>A 16473-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11872,10 +11872,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44798</v>
+        <v>45029</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11931,7 +11931,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 65116-2023</t>
+          <t>A 16475-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11941,14 +11941,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45287</v>
+        <v>45029</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12004,7 +12004,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 59625-2023</t>
+          <t>A 53131-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12018,10 +12018,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45254</v>
+        <v>44876</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12077,7 +12077,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 19447-2025</t>
+          <t>A 10640-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45770</v>
+        <v>45721</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12150,7 +12150,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 131-2024</t>
+          <t>A 13510-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12164,10 +12164,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45294</v>
+        <v>44648</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>7.5</v>
+        <v>17.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12223,7 +12223,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 54087-2021</t>
+          <t>A 58330-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12237,10 +12237,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44470</v>
+        <v>44901</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12250,11 +12250,6 @@
       <c r="G157" t="inlineStr">
         <is>
           <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I157" t="n">
@@ -12301,7 +12296,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 27441-2026</t>
+          <t>A 36192-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12315,10 +12310,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46189</v>
+        <v>45867</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12331,7 +12326,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12374,7 +12369,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 27586-2026</t>
+          <t>A 13119-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12384,14 +12379,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46190</v>
+        <v>45002</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12404,7 +12399,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12447,7 +12442,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 27652-2022</t>
+          <t>A 64784-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12461,10 +12456,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44743</v>
+        <v>45282</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12477,7 +12472,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>9.1</v>
+        <v>2.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12520,7 +12515,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 45983-2024</t>
+          <t>A 68454-2021</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12534,10 +12529,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45580</v>
+        <v>44529</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12550,7 +12545,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12593,7 +12588,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 5242-2022</t>
+          <t>A 57259-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12607,10 +12602,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44594</v>
+        <v>44895</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12623,7 +12618,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12666,7 +12661,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 46529-2024</t>
+          <t>A 10777-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12680,10 +12675,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45582</v>
+        <v>45369</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12696,7 +12691,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>11.7</v>
+        <v>0.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12739,7 +12734,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 16154-2024</t>
+          <t>A 48788-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12753,10 +12748,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45406</v>
+        <v>45937</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12769,7 +12764,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12812,7 +12807,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 16155-2024</t>
+          <t>A 48790-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12826,10 +12821,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45406</v>
+        <v>45937</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12842,7 +12837,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12885,7 +12880,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 57259-2022</t>
+          <t>A 47708-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12899,10 +12894,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44895</v>
+        <v>45931</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12915,7 +12910,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12958,7 +12953,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 59879-2024</t>
+          <t>A 48787-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12972,10 +12967,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45640</v>
+        <v>45937</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12988,7 +12983,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13031,7 +13026,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 32826-2022</t>
+          <t>A 48791-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13045,10 +13040,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44784</v>
+        <v>45937</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13061,7 +13056,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13104,7 +13099,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 58330-2022</t>
+          <t>A 15648-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13118,10 +13113,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44901</v>
+        <v>45748</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13134,7 +13129,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13177,7 +13172,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 15704-2023</t>
+          <t>A 50209-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13191,10 +13186,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45021</v>
+        <v>45943</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13207,7 +13202,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13250,7 +13245,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 30796-2024</t>
+          <t>A 50337-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13264,10 +13259,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45497</v>
+        <v>45944</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13280,7 +13275,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13323,7 +13318,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 16152-2024</t>
+          <t>A 21979-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13337,10 +13332,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45406</v>
+        <v>45784</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13353,7 +13348,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13396,7 +13391,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 4906-2024</t>
+          <t>A 54526-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13410,10 +13405,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45329</v>
+        <v>45965</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13426,7 +13421,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13469,7 +13464,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 13883-2022</t>
+          <t>A 56523-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13483,10 +13478,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44650</v>
+        <v>45975</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13499,7 +13494,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>6.1</v>
+        <v>1.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13542,7 +13537,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 53401-2022</t>
+          <t>A 57262-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13556,10 +13551,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44879</v>
+        <v>45979</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13572,7 +13567,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13615,7 +13610,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 15181-2023</t>
+          <t>A 57890-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13629,10 +13624,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45016</v>
+        <v>45981</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13645,7 +13640,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13688,7 +13683,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 855-2023</t>
+          <t>A 57886-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13702,10 +13697,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44931</v>
+        <v>45981</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13718,7 +13713,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.1</v>
+        <v>8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13761,7 +13756,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 47755-2022</t>
+          <t>A 57891-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13775,10 +13770,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44854</v>
+        <v>45981</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13791,7 +13786,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13834,7 +13829,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 9821-2022</t>
+          <t>A 59252-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13848,10 +13843,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44620</v>
+        <v>45988</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13864,7 +13859,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13907,7 +13902,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 30505-2026</t>
+          <t>A 60505-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13921,10 +13916,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46210</v>
+        <v>45995</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13937,7 +13932,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13980,7 +13975,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 13220-2022</t>
+          <t>A 61535-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13994,10 +13989,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44644</v>
+        <v>46001</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14010,7 +14005,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14053,7 +14048,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 68400-2021</t>
+          <t>A 61539-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14067,10 +14062,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44529</v>
+        <v>46001</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14083,7 +14078,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14126,7 +14121,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 25514-2022</t>
+          <t>A 63884-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14140,10 +14135,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44732</v>
+        <v>46020</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14156,7 +14151,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14199,7 +14194,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 10494-2022</t>
+          <t>A 60-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14213,10 +14208,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44623</v>
+        <v>46024</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14229,7 +14224,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>13.3</v>
+        <v>3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14272,7 +14267,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 52688-2024</t>
+          <t>A 1525-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14286,10 +14281,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45610</v>
+        <v>46034</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14345,7 +14340,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 47902-2024</t>
+          <t>A 3256-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14359,10 +14354,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45589</v>
+        <v>46041</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14375,7 +14370,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14418,7 +14413,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 2263-2024</t>
+          <t>A 32527-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14432,10 +14427,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45310</v>
+        <v>45513</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14449,11 +14444,11 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14496,7 +14491,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37305-2022</t>
+          <t>A 32541-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14510,10 +14505,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44808</v>
+        <v>45513</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14525,8 +14520,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>9.9</v>
+        <v>0.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14569,7 +14569,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 60498-2024</t>
+          <t>A 14211-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45643</v>
+        <v>46099</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14642,7 +14642,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 36033-2026</t>
+          <t>A 15592-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14656,10 +14656,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46267</v>
+        <v>46106</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14715,7 +14715,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 37562-2024</t>
+          <t>A 16030-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14729,10 +14729,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45541</v>
+        <v>46108</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.2</v>
+        <v>15.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14788,7 +14788,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 15659-2025</t>
+          <t>A 17485-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14798,14 +14798,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45748</v>
+        <v>46120</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14861,7 +14861,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 19773-2025</t>
+          <t>A 18840-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14875,10 +14875,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45771</v>
+        <v>46129</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14934,7 +14934,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 20667-2026</t>
+          <t>A 19373-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14948,10 +14948,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46141</v>
+        <v>46133</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15007,7 +15007,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 8273-2024</t>
+          <t>A 20009-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15021,10 +15021,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45352</v>
+        <v>46136</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15080,7 +15080,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 2402-2024</t>
+          <t>A 3272-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15094,10 +15094,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45310</v>
+        <v>45679</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15153,7 +15153,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 3399-2024</t>
+          <t>A 20152-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15167,10 +15167,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45318</v>
+        <v>46138</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15226,7 +15226,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 10767-2024</t>
+          <t>A 30773-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15240,10 +15240,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45369</v>
+        <v>45496</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15299,7 +15299,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 24432-2022</t>
+          <t>A 28224-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15309,14 +15309,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44726</v>
+        <v>45099</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15372,7 +15372,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 16487-2023</t>
+          <t>A 4307-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15386,10 +15386,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45029</v>
+        <v>45685</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15445,7 +15445,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 64669-2023</t>
+          <t>A 20500-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45281</v>
+        <v>46140</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15518,7 +15518,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 32804-2026</t>
+          <t>A 20501-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15532,10 +15532,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46241</v>
+        <v>46140</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15547,13 +15547,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15596,7 +15591,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 55303-2022</t>
+          <t>A 21929-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15610,10 +15605,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44887</v>
+        <v>46150</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15626,7 +15621,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15669,7 +15664,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 38535-2026</t>
+          <t>A 22620-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15683,10 +15678,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46283</v>
+        <v>46155</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15699,7 +15694,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15742,7 +15737,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 32797-2026</t>
+          <t>A 10858-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15756,10 +15751,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46241</v>
+        <v>46078</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15771,13 +15766,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15820,7 +15810,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 12329-2024</t>
+          <t>A 27441-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15834,10 +15824,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45378</v>
+        <v>46189</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15850,7 +15840,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15893,7 +15883,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 4077-2025</t>
+          <t>A 27586-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15903,14 +15893,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45684</v>
+        <v>46190</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15923,7 +15913,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -15966,7 +15956,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 62294-2022</t>
+          <t>A 30505-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15980,10 +15970,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44923</v>
+        <v>46210</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15996,7 +15986,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16039,7 +16029,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 12264-2024</t>
+          <t>A 36033-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16053,10 +16043,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45378</v>
+        <v>46267</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16069,7 +16059,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16112,7 +16102,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 12266-2024</t>
+          <t>A 20667-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16126,10 +16116,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45378</v>
+        <v>46141</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16142,7 +16132,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16185,7 +16175,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 44708-2023</t>
+          <t>A 38535-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16199,10 +16189,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45190</v>
+        <v>46283</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16215,7 +16205,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16258,7 +16248,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 20955-2025</t>
+          <t>A 32804-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16272,10 +16262,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45777</v>
+        <v>46241</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16287,8 +16277,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16331,7 +16326,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 22016-2025</t>
+          <t>A 32797-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16345,10 +16340,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45784</v>
+        <v>46241</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16360,8 +16355,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16421,7 +16421,7 @@
         <v>46251</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>46251</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>46090</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/Översikt TROLLHÄTTAN.xlsx
+++ b/Översikt TROLLHÄTTAN.xlsx
@@ -601,7 +601,7 @@
         <v>44529</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44963</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 13131-2024</t>
+          <t>A 15069-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45386</v>
+        <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -835,25 +835,20 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -868,7 +863,7 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -881,145 +876,150 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Kortskaftad parasitspik
+Rostfläck</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/artfynd/A 15069-2026 artfynd.xlsx", "A 15069-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor/A 15069-2026 karta.png", "A 15069-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor_geotiff/A 15069-2026 georefererad karta.tif", "A 15069-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomål/A 15069-2026 FSC-klagomål.docx", "A 15069-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomålsmail/A 15069-2026 FSC-klagomål mail.docx", "A 15069-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsyn/A 15069-2026 tillsynsbegäran.docx", "A 15069-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsynsmail/A 15069-2026 tillsynsbegäran mail.docx", "A 15069-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 13131-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45386</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TROLLHÄTTAN</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Svinrot
 Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/artfynd/A 13131-2024 artfynd.xlsx", "A 13131-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor/A 13131-2024 karta.png", "A 13131-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor_geotiff/A 13131-2024 georefererad karta.tif", "A 13131-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomål/A 13131-2024 FSC-klagomål.docx", "A 13131-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomålsmail/A 13131-2024 FSC-klagomål mail.docx", "A 13131-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsyn/A 13131-2024 tillsynsbegäran.docx", "A 13131-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsynsmail/A 13131-2024 tillsynsbegäran mail.docx", "A 13131-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 15069-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46104</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TROLLHÄTTAN</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Kortskaftad parasitspik
-Rostfläck</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/artfynd/A 15069-2026 artfynd.xlsx", "A 15069-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor/A 15069-2026 karta.png", "A 15069-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/kartor_geotiff/A 15069-2026 georefererad karta.tif", "A 15069-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomål/A 15069-2026 FSC-klagomål.docx", "A 15069-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/klagomålsmail/A 15069-2026 FSC-klagomål mail.docx", "A 15069-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsyn/A 15069-2026 tillsynsbegäran.docx", "A 15069-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1488/tillsynsmail/A 15069-2026 tillsynsbegäran mail.docx", "A 15069-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44876</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>44572</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>44701</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 7747-2022</t>
+          <t>A 17194-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44608</v>
+        <v>44677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38000-2022</t>
+          <t>A 7747-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44811</v>
+        <v>44608</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2182,7 +2182,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 17194-2022</t>
+          <t>A 10150-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44677</v>
+        <v>44622</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2255,7 +2255,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18533-2022</t>
+          <t>A 38000-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44686</v>
+        <v>44811</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 19577-2022</t>
+          <t>A 18533-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44693</v>
+        <v>44686</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>44757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 10150-2022</t>
+          <t>A 19577-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44622</v>
+        <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 318-2022</t>
+          <t>A 67535-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44565</v>
+        <v>44524</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2576,8 +2576,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>8.6</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2620,7 +2625,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 67535-2021</t>
+          <t>A 66971-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2634,10 +2639,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44524</v>
+        <v>44522</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2649,13 +2654,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2698,7 +2698,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 66971-2021</t>
+          <t>A 318-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44522</v>
+        <v>44565</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>8.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 24127-2024</t>
+          <t>A 1295-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45456</v>
+        <v>44572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 23984-2024</t>
+          <t>A 37658-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45456</v>
+        <v>44810</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1295-2022</t>
+          <t>A 11123-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44572</v>
+        <v>45371</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11460-2024</t>
+          <t>A 10768-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45372</v>
+        <v>45369</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62294-2022</t>
+          <t>A 10777-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44923</v>
+        <v>45369</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3044-2022</t>
+          <t>A 33546-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44582</v>
+        <v>44789</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 15000-2023</t>
+          <t>A 63884-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45015</v>
+        <v>46020</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 55303-2022</t>
+          <t>A 60-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44887</v>
+        <v>46024</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12264-2024</t>
+          <t>A 37801-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3365,14 +3365,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45378</v>
+        <v>45543</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12266-2024</t>
+          <t>A 1525-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45378</v>
+        <v>46034</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 6251-2023</t>
+          <t>A 60103-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44965</v>
+        <v>44909</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>15.4</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6354-2025</t>
+          <t>A 3044-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45699</v>
+        <v>44582</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>19.3</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3647,7 +3647,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 36982-2024</t>
+          <t>A 56116-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45539</v>
+        <v>44889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3720,7 +3720,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 855-2023</t>
+          <t>A 64784-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44931</v>
+        <v>45282</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3793,7 +3793,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21363-2023</t>
+          <t>A 15648-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45063</v>
+        <v>45748</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3866,7 +3866,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2263-2024</t>
+          <t>A 3256-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45310</v>
+        <v>46041</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3895,13 +3895,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>8.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3944,7 +3939,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61884-2024</t>
+          <t>A 36982-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3958,10 +3953,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45652</v>
+        <v>45539</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3974,7 +3969,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4017,7 +4012,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19781-2025</t>
+          <t>A 21979-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4031,10 +4026,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45771</v>
+        <v>45784</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4047,7 +4042,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.1</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4090,7 +4085,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 23451-2023</t>
+          <t>A 24559-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4104,10 +4099,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45076</v>
+        <v>45798</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4119,13 +4114,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4168,7 +4158,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3886-2025</t>
+          <t>A 66960-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4182,10 +4172,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45684</v>
+        <v>44522</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4197,13 +4187,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4246,7 +4231,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19773-2025</t>
+          <t>A 11837-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4260,10 +4245,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45771</v>
+        <v>45728</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4276,7 +4261,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4319,7 +4304,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60498-2024</t>
+          <t>A 15645-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4333,10 +4318,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45643</v>
+        <v>45404</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4349,7 +4334,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4392,7 +4377,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5927-2022</t>
+          <t>A 11991-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4406,10 +4391,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44598</v>
+        <v>44635</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4422,7 +4407,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4465,7 +4450,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3399-2024</t>
+          <t>A 3074-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4479,10 +4464,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45318</v>
+        <v>44946</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4495,7 +4480,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4538,7 +4523,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 41893-2022</t>
+          <t>A 13119-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4552,10 +4537,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44830</v>
+        <v>45002</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4567,13 +4552,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4616,7 +4596,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7783-2023</t>
+          <t>A 17126-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4630,10 +4610,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44973</v>
+        <v>44677</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4646,7 +4626,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4689,7 +4669,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18612-2025</t>
+          <t>A 47708-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4703,10 +4683,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45763</v>
+        <v>45931</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4719,7 +4699,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4762,7 +4742,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8273-2024</t>
+          <t>A 48790-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4776,10 +4756,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45352</v>
+        <v>45937</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4792,7 +4772,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4835,7 +4815,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52688-2024</t>
+          <t>A 48791-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4849,10 +4829,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45610</v>
+        <v>45937</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4865,7 +4845,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4908,7 +4888,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 65254-2021</t>
+          <t>A 32527-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4922,10 +4902,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44515</v>
+        <v>45513</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4937,8 +4917,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>6.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4981,7 +4966,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5242-2022</t>
+          <t>A 48787-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4995,10 +4980,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44594</v>
+        <v>45937</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5011,7 +4996,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5054,7 +5039,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57918-2022</t>
+          <t>A 32541-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5068,10 +5053,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44900</v>
+        <v>45513</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5083,8 +5068,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5127,7 +5117,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39611-2022</t>
+          <t>A 48788-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5141,10 +5131,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44818</v>
+        <v>45937</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5156,13 +5146,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5205,7 +5190,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44708-2023</t>
+          <t>A 50337-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5219,10 +5204,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45190</v>
+        <v>45944</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5235,7 +5220,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5278,7 +5263,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25514-2022</t>
+          <t>A 50209-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5292,10 +5277,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44732</v>
+        <v>45943</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5308,7 +5293,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5351,7 +5336,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7781-2023</t>
+          <t>A 45519-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5365,10 +5350,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44973</v>
+        <v>45194</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5381,7 +5366,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5424,7 +5409,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12967-2024</t>
+          <t>A 49062-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5438,10 +5423,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45385</v>
+        <v>45594</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5454,7 +5439,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5497,7 +5482,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7921-2024</t>
+          <t>A 46533-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5511,10 +5496,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45350</v>
+        <v>45582</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5527,7 +5512,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5570,7 +5555,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 46529-2024</t>
+          <t>A 53131-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5584,10 +5569,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45582</v>
+        <v>44876</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5600,7 +5585,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>11.7</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5643,7 +5628,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24432-2022</t>
+          <t>A 7783-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5653,14 +5638,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44726</v>
+        <v>44973</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5673,7 +5658,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5716,7 +5701,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 45521-2022</t>
+          <t>A 14211-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5730,10 +5715,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44845</v>
+        <v>46099</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5746,7 +5731,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5789,7 +5774,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 131-2024</t>
+          <t>A 11460-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5803,10 +5788,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45294</v>
+        <v>45372</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5819,7 +5804,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>7.5</v>
+        <v>5.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5862,7 +5847,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 75-2025</t>
+          <t>A 62299-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5876,10 +5861,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45659</v>
+        <v>44923</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5892,7 +5877,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5935,7 +5920,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 68400-2021</t>
+          <t>A 49781-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5949,10 +5934,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44529</v>
+        <v>45597</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5965,7 +5950,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6008,7 +5993,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17126-2022</t>
+          <t>A 34909-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6022,10 +6007,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44677</v>
+        <v>45141</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6038,7 +6023,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6081,7 +6066,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 37658-2022</t>
+          <t>A 27201-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6095,10 +6080,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44810</v>
+        <v>45812</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6111,7 +6096,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6154,7 +6139,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34909-2023</t>
+          <t>A 55033-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6168,10 +6153,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45141</v>
+        <v>45237</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6184,7 +6169,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6227,7 +6212,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 54087-2021</t>
+          <t>A 6354-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6241,10 +6226,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44470</v>
+        <v>45699</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6256,13 +6241,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>19.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6305,7 +6285,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 56116-2022</t>
+          <t>A 15592-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6319,10 +6299,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44889</v>
+        <v>46106</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6335,7 +6315,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.2</v>
+        <v>8.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6378,7 +6358,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 15658-2025</t>
+          <t>A 21363-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6392,10 +6372,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45748</v>
+        <v>45063</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6408,7 +6388,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6451,7 +6431,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 66960-2021</t>
+          <t>A 16030-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6465,10 +6445,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44522</v>
+        <v>46108</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6481,7 +6461,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>15.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6524,7 +6504,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35465-2022</t>
+          <t>A 54526-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6538,10 +6518,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44798</v>
+        <v>45965</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6554,7 +6534,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6597,7 +6577,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 65116-2023</t>
+          <t>A 40896-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6607,14 +6587,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45287</v>
+        <v>44825</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6627,7 +6607,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.1</v>
+        <v>11.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6670,7 +6650,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 40896-2022</t>
+          <t>A 15658-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6684,10 +6664,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44825</v>
+        <v>45748</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6700,7 +6680,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>11.3</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6743,7 +6723,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12329-2024</t>
+          <t>A 15000-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6757,10 +6737,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45378</v>
+        <v>45015</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6773,7 +6753,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6816,7 +6796,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37371-2023</t>
+          <t>A 65254-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6830,10 +6810,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45156</v>
+        <v>44515</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6846,7 +6826,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6889,7 +6869,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15704-2023</t>
+          <t>A 17485-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6899,14 +6879,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45021</v>
+        <v>46120</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6919,7 +6899,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6962,7 +6942,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 39116-2022</t>
+          <t>A 56523-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6976,10 +6956,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44817</v>
+        <v>45975</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6992,7 +6972,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7035,7 +7015,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37305-2022</t>
+          <t>A 46364-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7049,10 +7029,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44808</v>
+        <v>45582</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7065,7 +7045,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>9.9</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7108,7 +7088,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 15181-2023</t>
+          <t>A 6251-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7122,10 +7102,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45016</v>
+        <v>44965</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7138,7 +7118,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.9</v>
+        <v>15.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7181,7 +7161,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 24129-2024</t>
+          <t>A 57262-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7195,10 +7175,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45456</v>
+        <v>45979</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7211,7 +7191,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7254,7 +7234,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 53193-2023</t>
+          <t>A 24127-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7268,10 +7248,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45229</v>
+        <v>45456</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7284,7 +7264,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7327,7 +7307,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62266-2022</t>
+          <t>A 57890-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7341,10 +7321,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44923</v>
+        <v>45981</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7357,7 +7337,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7400,7 +7380,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 3074-2023</t>
+          <t>A 18840-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7414,10 +7394,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44946</v>
+        <v>46129</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7430,7 +7410,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.1</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7473,7 +7453,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20955-2025</t>
+          <t>A 57886-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7487,10 +7467,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45777</v>
+        <v>45981</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7503,7 +7483,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7546,7 +7526,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 7730-2023</t>
+          <t>A 57891-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7560,10 +7540,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44973</v>
+        <v>45981</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7576,7 +7556,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7619,7 +7599,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 10494-2022</t>
+          <t>A 23451-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7633,10 +7613,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44623</v>
+        <v>45076</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7648,8 +7628,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>13.3</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7692,7 +7677,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46364-2024</t>
+          <t>A 19373-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7706,10 +7691,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45582</v>
+        <v>46133</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7722,7 +7707,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7765,7 +7750,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 10767-2024</t>
+          <t>A 3886-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7779,10 +7764,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45369</v>
+        <v>45684</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7794,8 +7779,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7838,7 +7828,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 33546-2022</t>
+          <t>A 59252-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7852,10 +7842,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44789</v>
+        <v>45988</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7868,7 +7858,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7901,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 60103-2022</t>
+          <t>A 20009-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7925,10 +7915,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44909</v>
+        <v>46136</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7941,7 +7931,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7984,7 +7974,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 9821-2022</t>
+          <t>A 41554-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7998,10 +7988,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44620</v>
+        <v>45560</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8014,7 +8004,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8057,7 +8047,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 22016-2025</t>
+          <t>A 61046-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8071,10 +8061,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45784</v>
+        <v>45645</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8087,7 +8077,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8130,7 +8120,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 38941-2023</t>
+          <t>A 4307-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8144,10 +8134,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45163</v>
+        <v>45685</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8160,7 +8150,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8203,7 +8193,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13515-2022</t>
+          <t>A 60505-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8217,10 +8207,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44648</v>
+        <v>45995</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8233,7 +8223,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8276,7 +8266,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 4077-2025</t>
+          <t>A 61535-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8290,10 +8280,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45684</v>
+        <v>46001</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8306,7 +8296,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8349,7 +8339,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 49781-2024</t>
+          <t>A 61539-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8363,10 +8353,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45597</v>
+        <v>46001</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8379,7 +8369,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8422,7 +8412,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 2402-2024</t>
+          <t>A 3272-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8436,10 +8426,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45310</v>
+        <v>45679</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8452,7 +8442,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8495,7 +8485,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61046-2024</t>
+          <t>A 30773-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8509,10 +8499,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45645</v>
+        <v>45496</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8525,7 +8515,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8568,7 +8558,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 73158-2021</t>
+          <t>A 30486-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8582,10 +8572,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44550</v>
+        <v>45829</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8598,7 +8588,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8641,7 +8631,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 13883-2022</t>
+          <t>A 31464-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8655,10 +8645,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44650</v>
+        <v>45833</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8671,7 +8661,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6.1</v>
+        <v>1.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8714,7 +8704,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 37801-2024</t>
+          <t>A 53193-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8724,14 +8714,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45543</v>
+        <v>45229</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8744,7 +8734,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8787,7 +8777,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 29300-2024</t>
+          <t>A 34671-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8801,10 +8791,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45483</v>
+        <v>45847</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8816,8 +8806,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8860,7 +8855,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 11837-2025</t>
+          <t>A 39611-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8874,10 +8869,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45728</v>
+        <v>44818</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8889,8 +8884,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 15645-2024</t>
+          <t>A 29300-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45404</v>
+        <v>45483</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9006,7 +9006,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 3795-2024</t>
+          <t>A 13510-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45321</v>
+        <v>44648</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.4</v>
+        <v>17.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9079,7 +9079,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 16487-2023</t>
+          <t>A 10640-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45029</v>
+        <v>45721</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9152,7 +9152,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 11123-2024</t>
+          <t>A 20500-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9166,10 +9166,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45371</v>
+        <v>46140</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>8.199999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9225,7 +9225,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 24559-2025</t>
+          <t>A 7628-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9239,10 +9239,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45798</v>
+        <v>44607</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9298,7 +9298,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 34435-2024</t>
+          <t>A 36192-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45525</v>
+        <v>45867</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9371,7 +9371,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 42456-2024</t>
+          <t>A 20501-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9385,10 +9385,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45565</v>
+        <v>46140</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9444,7 +9444,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 59625-2023</t>
+          <t>A 20152-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9458,10 +9458,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45254</v>
+        <v>46138</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9517,7 +9517,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 55033-2023</t>
+          <t>A 53426-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9531,10 +9531,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45237</v>
+        <v>44879</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.3</v>
+        <v>13.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9590,7 +9590,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 53401-2022</t>
+          <t>A 62266-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9604,10 +9604,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44879</v>
+        <v>44923</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 46533-2024</t>
+          <t>A 39116-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9677,10 +9677,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45582</v>
+        <v>44817</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 49062-2024</t>
+          <t>A 57918-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9750,10 +9750,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45594</v>
+        <v>44900</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9809,7 +9809,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 45519-2023</t>
+          <t>A 28224-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45194</v>
+        <v>45099</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9882,7 +9882,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 37562-2024</t>
+          <t>A 41893-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9896,10 +9896,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45541</v>
+        <v>44830</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9911,8 +9911,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -9955,7 +9960,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 27652-2022</t>
+          <t>A 18612-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9969,10 +9974,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44743</v>
+        <v>45763</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9985,7 +9990,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>9.1</v>
+        <v>2.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10028,7 +10033,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 15659-2025</t>
+          <t>A 7730-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10042,10 +10047,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45748</v>
+        <v>44973</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10058,7 +10063,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10101,7 +10106,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 27201-2025</t>
+          <t>A 21929-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10115,10 +10120,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45812</v>
+        <v>46150</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10131,7 +10136,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10174,7 +10179,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 30796-2024</t>
+          <t>A 22620-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10188,10 +10193,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45497</v>
+        <v>46155</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10204,7 +10209,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10247,7 +10252,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16154-2024</t>
+          <t>A 68454-2021</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10261,10 +10266,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45406</v>
+        <v>44529</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10277,7 +10282,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10320,7 +10325,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 16155-2024</t>
+          <t>A 7781-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10334,10 +10339,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45406</v>
+        <v>44973</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10350,7 +10355,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10393,7 +10398,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 7628-2022</t>
+          <t>A 73158-2021</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10407,10 +10412,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44607</v>
+        <v>44550</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10423,7 +10428,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10466,7 +10471,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 35969-2024</t>
+          <t>A 38941-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10480,10 +10485,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45533</v>
+        <v>45163</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10496,7 +10501,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10539,7 +10544,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 59879-2024</t>
+          <t>A 16473-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10553,10 +10558,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45640</v>
+        <v>45029</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10569,7 +10574,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10612,7 +10617,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 30486-2025</t>
+          <t>A 16475-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10626,10 +10631,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45829</v>
+        <v>45029</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10642,7 +10647,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10685,7 +10690,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 31464-2025</t>
+          <t>A 34435-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10699,10 +10704,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45833</v>
+        <v>45525</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10715,7 +10720,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10758,7 +10763,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 16152-2024</t>
+          <t>A 10858-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10772,10 +10777,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45406</v>
+        <v>46078</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10788,7 +10793,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.8</v>
+        <v>8.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10831,7 +10836,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 11991-2022</t>
+          <t>A 42456-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10845,10 +10850,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44635</v>
+        <v>45565</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10861,7 +10866,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -10904,7 +10909,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 41554-2024</t>
+          <t>A 19781-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10918,10 +10923,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45560</v>
+        <v>45771</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10934,7 +10939,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.7</v>
+        <v>6.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -10977,7 +10982,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 47755-2022</t>
+          <t>A 12967-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10991,10 +10996,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44854</v>
+        <v>45385</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11007,7 +11012,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11050,7 +11055,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 10768-2024</t>
+          <t>A 37371-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11064,10 +11069,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45369</v>
+        <v>45156</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11080,7 +11085,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11123,7 +11128,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 62299-2022</t>
+          <t>A 35969-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11137,10 +11142,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44923</v>
+        <v>45533</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11153,7 +11158,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11196,7 +11201,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 45983-2024</t>
+          <t>A 7921-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11210,10 +11215,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45580</v>
+        <v>45350</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11226,7 +11231,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11269,7 +11274,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 32826-2022</t>
+          <t>A 13515-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11283,10 +11288,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44784</v>
+        <v>44648</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11299,7 +11304,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11342,7 +11347,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 53426-2022</t>
+          <t>A 75-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11356,10 +11361,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44879</v>
+        <v>45659</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11372,7 +11377,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>13.2</v>
+        <v>5.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11415,7 +11420,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 4906-2024</t>
+          <t>A 3795-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11429,10 +11434,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45329</v>
+        <v>45321</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11445,7 +11450,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11488,7 +11493,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 34671-2025</t>
+          <t>A 27441-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11502,10 +11507,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45847</v>
+        <v>46189</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11517,13 +11522,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11566,7 +11566,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 13220-2022</t>
+          <t>A 27586-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11576,14 +11576,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44644</v>
+        <v>46190</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11639,7 +11639,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 19447-2025</t>
+          <t>A 61884-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11653,10 +11653,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45770</v>
+        <v>45652</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11712,7 +11712,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 64669-2023</t>
+          <t>A 45521-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11726,10 +11726,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45281</v>
+        <v>44845</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 47902-2024</t>
+          <t>A 5927-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11799,10 +11799,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45589</v>
+        <v>44598</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.8</v>
+        <v>6.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 16473-2023</t>
+          <t>A 23984-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11872,10 +11872,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45029</v>
+        <v>45456</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -11931,7 +11931,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 16475-2023</t>
+          <t>A 24129-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11945,10 +11945,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45029</v>
+        <v>45456</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12004,7 +12004,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 53131-2022</t>
+          <t>A 30505-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12018,10 +12018,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44876</v>
+        <v>46210</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12077,7 +12077,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 10640-2025</t>
+          <t>A 35465-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45721</v>
+        <v>44798</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12150,7 +12150,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 13510-2022</t>
+          <t>A 65116-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12160,14 +12160,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44648</v>
+        <v>45287</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>17.6</v>
+        <v>0.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12223,7 +12223,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 58330-2022</t>
+          <t>A 59625-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12237,10 +12237,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44901</v>
+        <v>45254</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12296,7 +12296,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 36192-2025</t>
+          <t>A 19447-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12310,10 +12310,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45867</v>
+        <v>45770</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.4</v>
+        <v>4.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12369,7 +12369,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 13119-2023</t>
+          <t>A 131-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45002</v>
+        <v>45294</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12442,7 +12442,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 64784-2023</t>
+          <t>A 36033-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12456,10 +12456,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45282</v>
+        <v>46267</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12515,7 +12515,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 68454-2021</t>
+          <t>A 27652-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44529</v>
+        <v>44743</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.6</v>
+        <v>9.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12588,7 +12588,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 57259-2022</t>
+          <t>A 45983-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12602,10 +12602,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44895</v>
+        <v>45580</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12661,7 +12661,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 10777-2024</t>
+          <t>A 5242-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12675,10 +12675,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45369</v>
+        <v>44594</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12734,7 +12734,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 48788-2025</t>
+          <t>A 46529-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12748,10 +12748,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45937</v>
+        <v>45582</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4.5</v>
+        <v>11.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12807,7 +12807,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 48790-2025</t>
+          <t>A 16154-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12821,10 +12821,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45937</v>
+        <v>45406</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 47708-2025</t>
+          <t>A 16155-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12894,10 +12894,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45931</v>
+        <v>45406</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -12953,7 +12953,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 48787-2025</t>
+          <t>A 57259-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12967,10 +12967,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45937</v>
+        <v>44895</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13026,7 +13026,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 48791-2025</t>
+          <t>A 59879-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13040,10 +13040,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45937</v>
+        <v>45640</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13099,7 +13099,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 15648-2025</t>
+          <t>A 32826-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13113,10 +13113,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45748</v>
+        <v>44784</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13172,7 +13172,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 50209-2025</t>
+          <t>A 58330-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13186,10 +13186,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45943</v>
+        <v>44901</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 50337-2025</t>
+          <t>A 15704-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13259,10 +13259,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45944</v>
+        <v>45021</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13318,7 +13318,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 21979-2025</t>
+          <t>A 30796-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13332,10 +13332,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45784</v>
+        <v>45497</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13391,7 +13391,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 54526-2025</t>
+          <t>A 16152-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13405,10 +13405,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45965</v>
+        <v>45406</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13464,7 +13464,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 56523-2025</t>
+          <t>A 4906-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13478,10 +13478,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45975</v>
+        <v>45329</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13537,7 +13537,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 57262-2025</t>
+          <t>A 13883-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13551,10 +13551,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45979</v>
+        <v>44650</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.9</v>
+        <v>6.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13610,7 +13610,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 57890-2025</t>
+          <t>A 53401-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13624,10 +13624,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45981</v>
+        <v>44879</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13683,7 +13683,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 57886-2025</t>
+          <t>A 15181-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13697,10 +13697,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45981</v>
+        <v>45016</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13756,7 +13756,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 57891-2025</t>
+          <t>A 855-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13770,10 +13770,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45981</v>
+        <v>44931</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13829,7 +13829,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 59252-2025</t>
+          <t>A 20667-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13843,10 +13843,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45988</v>
+        <v>46141</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -13902,7 +13902,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 60505-2025</t>
+          <t>A 47755-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13916,10 +13916,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45995</v>
+        <v>44854</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13975,7 +13975,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 61535-2025</t>
+          <t>A 9821-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13989,10 +13989,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46001</v>
+        <v>44620</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14048,7 +14048,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 61539-2025</t>
+          <t>A 13220-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14062,10 +14062,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46001</v>
+        <v>44644</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14121,7 +14121,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 63884-2025</t>
+          <t>A 68400-2021</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14135,10 +14135,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46020</v>
+        <v>44529</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14194,7 +14194,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 60-2026</t>
+          <t>A 25514-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14208,10 +14208,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46024</v>
+        <v>44732</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14267,7 +14267,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 1525-2026</t>
+          <t>A 10494-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46034</v>
+        <v>44623</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.4</v>
+        <v>13.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14340,7 +14340,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 3256-2026</t>
+          <t>A 32804-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14354,10 +14354,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46041</v>
+        <v>46241</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14369,8 +14369,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>8.1</v>
+        <v>1.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14413,7 +14418,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 32527-2024</t>
+          <t>A 38535-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14427,10 +14432,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45513</v>
+        <v>46283</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14442,13 +14447,8 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>8.699999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14491,7 +14491,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 32541-2024</t>
+          <t>A 32797-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14505,10 +14505,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45513</v>
+        <v>46241</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14569,7 +14569,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 14211-2026</t>
+          <t>A 52688-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46099</v>
+        <v>45610</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14642,7 +14642,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 15592-2026</t>
+          <t>A 47902-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14656,10 +14656,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46106</v>
+        <v>45589</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14715,7 +14715,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 16030-2026</t>
+          <t>A 2263-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14729,10 +14729,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46108</v>
+        <v>45310</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14744,8 +14744,13 @@
           <t>TROLLHÄTTAN</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>15.8</v>
+        <v>0.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -14788,7 +14793,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 17485-2026</t>
+          <t>A 37305-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14798,14 +14803,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46120</v>
+        <v>44808</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -14818,7 +14823,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.6</v>
+        <v>9.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -14861,7 +14866,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 18840-2026</t>
+          <t>A 60498-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14875,10 +14880,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46129</v>
+        <v>45643</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14891,7 +14896,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -14934,7 +14939,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 19373-2026</t>
+          <t>A 37562-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14948,10 +14953,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46133</v>
+        <v>45541</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14964,7 +14969,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15007,7 +15012,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 20009-2026</t>
+          <t>A 15659-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15021,10 +15026,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46136</v>
+        <v>45748</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15037,7 +15042,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15080,7 +15085,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 3272-2025</t>
+          <t>A 33830-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15094,10 +15099,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45679</v>
+        <v>46251</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15110,7 +15115,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.1</v>
+        <v>8.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15153,7 +15158,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 20152-2026</t>
+          <t>A 33782-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15167,10 +15172,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46138</v>
+        <v>46251</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15183,7 +15188,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15226,7 +15231,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 30773-2024</t>
+          <t>A 19773-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15240,10 +15245,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45496</v>
+        <v>45771</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15256,7 +15261,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15299,7 +15304,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 28224-2023</t>
+          <t>A 40725-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15313,10 +15318,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45099</v>
+        <v>46296</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15329,7 +15334,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15372,7 +15377,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 4307-2025</t>
+          <t>A 8273-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15386,10 +15391,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45685</v>
+        <v>45352</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15402,7 +15407,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15445,7 +15450,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 20500-2026</t>
+          <t>A 2402-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15459,10 +15464,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46140</v>
+        <v>45310</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15475,7 +15480,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15518,7 +15523,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 20501-2026</t>
+          <t>A 3399-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15532,10 +15537,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46140</v>
+        <v>45318</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15548,7 +15553,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15591,7 +15596,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 21929-2026</t>
+          <t>A 10767-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15605,10 +15610,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46150</v>
+        <v>45369</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15621,7 +15626,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15664,7 +15669,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 22620-2026</t>
+          <t>A 24432-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15674,14 +15679,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46155</v>
+        <v>44726</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15694,7 +15699,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15737,7 +15742,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 10858-2026</t>
+          <t>A 16487-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -15751,10 +15756,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46078</v>
+        <v>45029</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15767,7 +15772,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>8.5</v>
+        <v>0.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -15810,7 +15815,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 27441-2026</t>
+          <t>A 64669-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15824,10 +15829,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46189</v>
+        <v>45281</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15840,7 +15845,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -15883,7 +15888,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 27586-2026</t>
+          <t>A 55303-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15893,14 +15898,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46190</v>
+        <v>44887</v>
       </c>
       <c r="E20